--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -60,7 +60,7 @@
       <sz val="8.5"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -101,6 +101,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E4DFEC"/>
         <bgColor rgb="00E4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DAEEF3"/>
+        <bgColor rgb="00DAEEF3"/>
       </patternFill>
     </fill>
     <fill>
@@ -192,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -234,13 +240,16 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -249,7 +258,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -620,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1375,22 +1384,22 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>設計</t>
+          <t>会議</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1400,7 +1409,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>26 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1415,32 +1424,32 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>設計</t>
+          <t>会議</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項12項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>30段落 16表</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>44 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1455,37 +1464,37 @@
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>別スコープ</t>
+          <t>設計</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H24" s="15" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>18 KB</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1495,37 +1504,37 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>別スコープ</t>
+          <t>設計</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
-        </is>
-      </c>
-      <c r="H25" s="15" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1533,37 +1542,37 @@
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>別スコープ</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
-        </is>
-      </c>
-      <c r="H26" s="15" t="inlineStr">
+          <t>23 KB</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
@@ -1573,19 +1582,19 @@
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>別スコープ</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1600,10 +1609,10 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
-        </is>
-      </c>
-      <c r="H27" s="15" t="inlineStr">
+          <t>15 KB</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
@@ -1613,115 +1622,155 @@
       <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>別スコープ</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H28" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H29" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H28" s="15" t="inlineStr">
+      <c r="H30" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_素案_第10稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="n"/>
-      <c r="E32" s="17" t="n"/>
-      <c r="F32" s="17" t="n"/>
-      <c r="G32" s="17" t="n"/>
-      <c r="H32" s="18" t="n"/>
-    </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>必要事項の一覧、確認依頼書</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="17" t="n"/>
-      <c r="G33" s="17" t="n"/>
-      <c r="H33" s="18" t="n"/>
-    </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>工程管理</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
@@ -1729,135 +1778,196 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
+          <t>第10期介護保険事業計画_素案_第10稿、図表集_白黒</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="18" t="n"/>
+      <c r="G34" s="18" t="n"/>
+      <c r="H34" s="19" t="n"/>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>必要事項の一覧、確認依頼書</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="18" t="n"/>
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="19" t="n"/>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>工程管理</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
           <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
-      <c r="D34" s="17" t="n"/>
-      <c r="E34" s="17" t="n"/>
-      <c r="F34" s="17" t="n"/>
-      <c r="G34" s="17" t="n"/>
-      <c r="H34" s="18" t="n"/>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="18" t="n"/>
+      <c r="H36" s="19" t="n"/>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>第9期の評価</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B37" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
-      <c r="D35" s="17" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="17" t="n"/>
-      <c r="G35" s="17" t="n"/>
-      <c r="H35" s="18" t="n"/>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="18" t="n"/>
+      <c r="G37" s="18" t="n"/>
+      <c r="H37" s="19" t="n"/>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B38" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書</t>
         </is>
       </c>
-      <c r="D36" s="17" t="n"/>
-      <c r="E36" s="17" t="n"/>
-      <c r="F36" s="17" t="n"/>
-      <c r="G36" s="17" t="n"/>
-      <c r="H36" s="18" t="n"/>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="18" t="n"/>
+      <c r="G38" s="18" t="n"/>
+      <c r="H38" s="19" t="n"/>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>設計</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B39" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
-      <c r="D37" s="17" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="17" t="n"/>
-      <c r="G37" s="17" t="n"/>
-      <c r="H37" s="18" t="n"/>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="14" t="inlineStr">
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="18" t="n"/>
+      <c r="G39" s="18" t="n"/>
+      <c r="H39" s="19" t="n"/>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="n"/>
+      <c r="E40" s="18" t="n"/>
+      <c r="F40" s="18" t="n"/>
+      <c r="G40" s="18" t="n"/>
+      <c r="H40" s="19" t="n"/>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>別スコープ</t>
         </is>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B41" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
-      <c r="D38" s="17" t="n"/>
-      <c r="E38" s="17" t="n"/>
-      <c r="F38" s="17" t="n"/>
-      <c r="G38" s="17" t="n"/>
-      <c r="H38" s="18" t="n"/>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="18" t="n"/>
+      <c r="G41" s="18" t="n"/>
+      <c r="H41" s="19" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B39" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="C39" s="19" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの19件、別スコープ5件</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="17" t="n"/>
-      <c r="G39" s="17" t="n"/>
-      <c r="H39" s="18" t="n"/>
-    </row>
-    <row r="41" ht="100" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="B42" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの21件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="n"/>
+      <c r="E42" s="18" t="n"/>
+      <c r="F42" s="18" t="n"/>
+      <c r="G42" s="18" t="n"/>
+      <c r="H42" s="19" t="n"/>
+    </row>
+    <row r="44" ht="100" customHeight="1">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C32:H32"/>
+  <mergeCells count="12">
     <mergeCell ref="C38:H38"/>
-    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="C42:H42"/>
     <mergeCell ref="C36:H36"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C39:H39"/>
-    <mergeCell ref="A41:H41"/>
     <mergeCell ref="C35:H35"/>
+    <mergeCell ref="A44:H44"/>
     <mergeCell ref="C34:H34"/>
+    <mergeCell ref="A32:H32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1869,7 +1979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2088,29 +2198,56 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
+          <t>キックオフ会議に臨む</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>① キックオフ資料の点検結果 00_点検の結果
+② 同 02_青枠の注記の扱い
+③ キックオフ会議ヒアリングシート</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>修正が必要な箇所12件のうち重大3件は、事業所実態調査が業務範囲外であること、起点差の議論が解消したこと、H01の指標が変更済みであることです。ヒアリングシートは会議中にご記入いただく形式です。</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>30分</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="76" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>委員会の資料を作る</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>① 必要事項の一覧 02_方針の決定（策定委員会の付議5件）
 ② 計画素案 第3章・第6章
 ③ 図表集</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>委員会にお諮りする事項は、施設整備方針、圏域設定、給付水準の評価の枠組み、代表KPIの評価表現、地域内還流の5件です。</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="100" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
+    <row r="14" ht="100" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>注1）はじめてご覧いただく場合は、目的1（いま何をお願いしているか）からお読みいただくのが早いと思われます。注2）計画素案は、第1章から順にお読みいただく必要はありません。第3章（第9期の評価）と第6章（見込み）が議論の中心となります。注3）分析資料は、計画素案の記述の根拠を示すものです。計画素案の各節に「（第2章第2節）」のように参照を付しています。</t>
         </is>
@@ -2119,7 +2256,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2208,7 +2345,7 @@
           <t>本文の頁数と章別配分、図表の点数、図表のレイアウト。第6章の見込量・給付費・保険料。</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
@@ -2239,7 +2376,7 @@
           <t>概要版の頁数、体裁、掲載内容。</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -2269,7 +2406,7 @@
           <t>推計資料のうちサービス見込量・給付費・保険料算定表が未作成。</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
@@ -2299,7 +2436,7 @@
           <t>キックオフ会議資料及び委員会資料原案は日程確定後に作成。</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
@@ -2329,7 +2466,7 @@
           <t>骨子案を素案とは別に作成する必要があるかの確認。</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
@@ -2359,7 +2496,7 @@
           <t>第6章の見込量・保険料。図表レイアウトの確認結果。</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
@@ -2389,7 +2526,7 @@
           <t>パブリックコメントの意見反映後に作成。</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -2401,7 +2538,7 @@
       </c>
     </row>
     <row r="13" ht="100" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>注1）成果品は編集可能な電子データ及びPDF形式により提出いたします。図表、グラフ及び統計資料についても発注者が加工可能な形式で納品いたします。現時点の分析資料はすべてExcelであり、計算式と元数値を保持しております。注2）健康とくらしの調査の個票データは個人情報を含むため、納品物には集計値のみを収録する扱いとしております。この扱いでよいかご確認をお願いいたします（計画素案の別管理表 成果品No.7）。注3）PDFは最終組版時に一括して作成いたします。現時点ではWord・Excelのみをお渡ししております。</t>
         </is>
@@ -2798,7 +2935,7 @@
       </c>
     </row>
     <row r="21" ht="100" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>注1）計画素案の第6章第2節から第7節は、いずれも資料の受領又は決定を待っています。第6章が計画の中心であるため、必要事項の一覧01シートの資料No.1・No.2・No.14の受領を最優先でお願いしております。注2）確定している箇所（第2章第1節から第4節）は、いずれも受領済のデータにより裏付けられています。根拠の水準は「主張の根拠水準の棚卸しと再レビュー」01シートに主張ごとに示しております。注3）本表は令和8年7月31日現在です。資料の受領及び決定により随時更新いたします。</t>
         </is>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1389,32 +1389,32 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第3稿.docx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシートへ移した。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>94段落 18表</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>26 KB</t>
+          <t>51 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第3稿</t>
         </is>
       </c>
     </row>
@@ -1429,27 +1429,27 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項12項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>30段落 16表</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>44 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1462,34 +1462,34 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項12項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>30段落 16表</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>44 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -1509,17 +1509,17 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1542,39 +1542,39 @@
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1589,27 +1589,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H27" s="16" t="inlineStr">
@@ -1629,12 +1629,12 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H28" s="16" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1709,88 +1709,108 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H30" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="52" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="H31" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="17" t="inlineStr">
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_素案_第10稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="n"/>
-      <c r="E34" s="18" t="n"/>
-      <c r="F34" s="18" t="n"/>
-      <c r="G34" s="18" t="n"/>
-      <c r="H34" s="19" t="n"/>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
@@ -1798,7 +1818,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_素案_第10稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D35" s="18" t="n"/>
@@ -1808,9 +1828,9 @@
       <c r="H35" s="19" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
@@ -1818,7 +1838,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
+          <t>必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D36" s="18" t="n"/>
@@ -1828,17 +1848,17 @@
       <c r="H36" s="19" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D37" s="18" t="n"/>
@@ -1848,17 +1868,17 @@
       <c r="H37" s="19" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書</t>
+          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D38" s="18" t="n"/>
@@ -1868,17 +1888,17 @@
       <c r="H38" s="19" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書</t>
         </is>
       </c>
       <c r="D39" s="18" t="n"/>
@@ -1888,9 +1908,9 @@
       <c r="H39" s="19" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
@@ -1898,7 +1918,7 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D40" s="18" t="n"/>
@@ -1908,17 +1928,17 @@
       <c r="H40" s="19" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_第3稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D41" s="18" t="n"/>
@@ -1927,18 +1947,18 @@
       <c r="G41" s="18" t="n"/>
       <c r="H41" s="19" t="n"/>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="C42" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの21件、別スコープ5件</t>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D42" s="18" t="n"/>
@@ -1947,8 +1967,28 @@
       <c r="G42" s="18" t="n"/>
       <c r="H42" s="19" t="n"/>
     </row>
-    <row r="44" ht="100" customHeight="1">
-      <c r="A44" s="21" t="inlineStr">
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの22件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="n"/>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="18" t="n"/>
+      <c r="G43" s="18" t="n"/>
+      <c r="H43" s="19" t="n"/>
+    </row>
+    <row r="45" ht="100" customHeight="1">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -1956,6 +1996,7 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A45:H45"/>
     <mergeCell ref="C38:H38"/>
     <mergeCell ref="C41:H41"/>
     <mergeCell ref="C42:H42"/>
@@ -1964,10 +2005,9 @@
     <mergeCell ref="C37:H37"/>
     <mergeCell ref="C40:H40"/>
     <mergeCell ref="C39:H39"/>
+    <mergeCell ref="A33:H33"/>
     <mergeCell ref="C35:H35"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="C43:H43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2203,14 +2243,14 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>① キックオフ資料の点検結果 00_点検の結果
-② 同 02_青枠の注記の扱い
-③ キックオフ会議ヒアリングシート</t>
+          <t>① キックオフ会議資料 第3稿
+② キックオフ会議ヒアリングシート
+③ キックオフ資料の点検結果 00_点検の結果（反映の経緯）</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>修正が必要な箇所12件のうち重大3件は、事業所実態調査が業務範囲外であること、起点差の議論が解消したこと、H01の指標が変更済みであることです。ヒアリングシートは会議中にご記入いただく形式です。</t>
+          <t>第3稿は、点検結果12件と青枠の仕分けを反映済みです。重大3件（事業所実態調査が業務範囲外、起点差の解消、H01の指標の変更）はいずれも本文に反映しました。ヒアリングシートは会議中にご記入いただく形式です。</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1404,7 +1404,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>94段落 18表</t>
+          <t>96段落 18表</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
@@ -1444,12 +1444,12 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>33 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -889,7 +889,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>49 KB</t>
+          <t>50 KB</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用が令和8年7月30日に決定した。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>31 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>51 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>44 KB</t>
+          <t>45 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>成果品一覧（令和8年7月31日現在）</t>
+          <t>成果品一覧（令和8年8月4日現在）</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>101段落 19表</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -1382,39 +1382,39 @@
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第3稿.docx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映したもの。13章18表。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシートへ移した。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項29件（重大3件）、09シートに計画本文への反映方針。個票データは収録せず集計値のみ。10シート。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>96段落 18表</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>第3稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1429,32 +1429,32 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第4稿.docx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシートへ移した。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>96段落 18表</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>33 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第4稿</t>
         </is>
       </c>
     </row>
@@ -1469,27 +1469,27 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項12項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>30段落 16表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>45 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -1502,34 +1502,34 @@
       <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項13項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>31段落 17表</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>45 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1582,39 +1582,39 @@
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1629,27 +1629,27 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H28" s="16" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H29" s="16" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1749,88 +1749,108 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="52" customHeight="1">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="H32" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="17" t="inlineStr">
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_素案_第10稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="n"/>
-      <c r="E35" s="18" t="n"/>
-      <c r="F35" s="18" t="n"/>
-      <c r="G35" s="18" t="n"/>
-      <c r="H35" s="19" t="n"/>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
@@ -1838,7 +1858,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_素案_第10稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D36" s="18" t="n"/>
@@ -1848,9 +1868,9 @@
       <c r="H36" s="19" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
@@ -1858,7 +1878,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
+          <t>必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D37" s="18" t="n"/>
@@ -1868,17 +1888,17 @@
       <c r="H37" s="19" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D38" s="18" t="n"/>
@@ -1888,17 +1908,17 @@
       <c r="H38" s="19" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書</t>
+          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D39" s="18" t="n"/>
@@ -1908,17 +1928,17 @@
       <c r="H39" s="19" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計</t>
         </is>
       </c>
       <c r="D40" s="18" t="n"/>
@@ -1928,17 +1948,17 @@
       <c r="H40" s="19" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_第3稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D41" s="18" t="n"/>
@@ -1948,17 +1968,17 @@
       <c r="H41" s="19" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_第4稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D42" s="18" t="n"/>
@@ -1967,18 +1987,18 @@
       <c r="G42" s="18" t="n"/>
       <c r="H42" s="19" t="n"/>
     </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B43" s="20" t="n">
-        <v>27</v>
-      </c>
-      <c r="C43" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの22件、別スコープ5件</t>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D43" s="18" t="n"/>
@@ -1987,8 +2007,28 @@
       <c r="G43" s="18" t="n"/>
       <c r="H43" s="19" t="n"/>
     </row>
-    <row r="45" ht="100" customHeight="1">
-      <c r="A45" s="21" t="inlineStr">
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの23件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="n"/>
+      <c r="E44" s="18" t="n"/>
+      <c r="F44" s="18" t="n"/>
+      <c r="G44" s="18" t="n"/>
+      <c r="H44" s="19" t="n"/>
+    </row>
+    <row r="46" ht="100" customHeight="1">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -1996,18 +2036,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A45:H45"/>
     <mergeCell ref="C38:H38"/>
     <mergeCell ref="C41:H41"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C36:H36"/>
+    <mergeCell ref="C44:H44"/>
+    <mergeCell ref="C37:H37"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C37:H37"/>
     <mergeCell ref="C40:H40"/>
     <mergeCell ref="C39:H39"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="C35:H35"/>
     <mergeCell ref="C43:H43"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2243,14 +2283,14 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>① キックオフ会議資料 第3稿
+          <t>① キックオフ会議資料 第4稿
 ② キックオフ会議ヒアリングシート
 ③ キックオフ資料の点検結果 00_点検の結果（反映の経緯）</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>第3稿は、点検結果12件と青枠の仕分けを反映済みです。重大3件（事業所実態調査が業務範囲外、起点差の解消、H01の指標の変更）はいずれも本文に反映しました。ヒアリングシートは会議中にご記入いただく形式です。</t>
+          <t>第4稿は、点検結果12件と青枠の仕分けに加え、人口推計の基礎の記述の修正と3調査の受領・点検の結果を反映済みです。重大3件（事業所実態調査が業務範囲外、起点差の解消、H01の指標の変更）はいずれも本文に反映しました。ヒアリングシートは会議中にご記入いただく形式です。</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1399,17 +1399,17 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項29件（重大3件）、09シートに計画本文への反映方針。個票データは収録せず集計値のみ。10シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項31件（重大4件）、09シートに計画本文への反映方針。10シートに見える化システムのK系列・M2系列との突合。個票データは収録せず集計値のみ。11シート。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>11シート</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>60 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -889,7 +889,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>51 KB</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>45 KB</t>
+          <t>46 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -809,7 +809,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>38 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -1399,17 +1399,17 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項31件（重大4件）、09シートに計画本文への反映方針。10シートに見える化システムのK系列・M2系列との突合。個票データは収録せず集計値のみ。11シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項31件（重大4件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>11シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>60 KB</t>
+          <t>88 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1422,39 +1422,39 @@
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第4稿.docx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映したもの。13章18表。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシートへ移した。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>96段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>第4稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1469,32 +1469,32 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第4稿.docx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシートへ移した。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>96段落 18表</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第4稿</t>
         </is>
       </c>
     </row>
@@ -1509,27 +1509,27 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項13項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>31段落 17表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>46 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1542,34 +1542,34 @@
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項13項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>31段落 17表</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>46 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1589,17 +1589,17 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1622,39 +1622,39 @@
       <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1669,27 +1669,27 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H29" s="16" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H30" s="16" t="inlineStr">
@@ -1749,12 +1749,12 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1789,88 +1789,108 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="52" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="H33" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="17" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_素案_第10稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="n"/>
-      <c r="E36" s="18" t="n"/>
-      <c r="F36" s="18" t="n"/>
-      <c r="G36" s="18" t="n"/>
-      <c r="H36" s="19" t="n"/>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
@@ -1878,7 +1898,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_素案_第10稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D37" s="18" t="n"/>
@@ -1888,9 +1908,9 @@
       <c r="H37" s="19" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
@@ -1898,7 +1918,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
+          <t>必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D38" s="18" t="n"/>
@@ -1908,17 +1928,17 @@
       <c r="H38" s="19" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D39" s="18" t="n"/>
@@ -1928,17 +1948,17 @@
       <c r="H39" s="19" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計</t>
+          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D40" s="18" t="n"/>
@@ -1948,17 +1968,17 @@
       <c r="H40" s="19" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認</t>
         </is>
       </c>
       <c r="D41" s="18" t="n"/>
@@ -1968,17 +1988,17 @@
       <c r="H41" s="19" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_第4稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D42" s="18" t="n"/>
@@ -1988,17 +2008,17 @@
       <c r="H42" s="19" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_第4稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D43" s="18" t="n"/>
@@ -2007,18 +2027,18 @@
       <c r="G43" s="18" t="n"/>
       <c r="H43" s="19" t="n"/>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B44" s="20" t="n">
-        <v>28</v>
-      </c>
-      <c r="C44" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの23件、別スコープ5件</t>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D44" s="18" t="n"/>
@@ -2027,8 +2047,28 @@
       <c r="G44" s="18" t="n"/>
       <c r="H44" s="19" t="n"/>
     </row>
-    <row r="46" ht="100" customHeight="1">
-      <c r="A46" s="21" t="inlineStr">
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの24件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="n"/>
+      <c r="E45" s="18" t="n"/>
+      <c r="F45" s="18" t="n"/>
+      <c r="G45" s="18" t="n"/>
+      <c r="H45" s="19" t="n"/>
+    </row>
+    <row r="47" ht="100" customHeight="1">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2039,15 +2079,15 @@
     <mergeCell ref="C38:H38"/>
     <mergeCell ref="C41:H41"/>
     <mergeCell ref="C42:H42"/>
-    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="C44:H44"/>
     <mergeCell ref="C37:H37"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C40:H40"/>
+    <mergeCell ref="C45:H45"/>
     <mergeCell ref="C39:H39"/>
+    <mergeCell ref="A47:H47"/>
     <mergeCell ref="C43:H43"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1462,39 +1462,39 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第4稿.docx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映したもの。13章18表。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシートへ移した。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>96段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>第4稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1509,32 +1509,32 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第4稿.docx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシートへ移した。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>96段落 18表</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第4稿</t>
         </is>
       </c>
     </row>
@@ -1549,27 +1549,27 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項13項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>31段落 17表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>46 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1582,34 +1582,34 @@
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項13項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>31段落 17表</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>46 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -1662,39 +1662,39 @@
       <c r="A29" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1709,27 +1709,27 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H30" s="16" t="inlineStr">
@@ -1749,12 +1749,12 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H31" s="16" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -1829,88 +1829,108 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H33" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="52" customHeight="1">
+      <c r="A34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="H34" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr"/>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_素案_第10稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D37" s="18" t="n"/>
-      <c r="E37" s="18" t="n"/>
-      <c r="F37" s="18" t="n"/>
-      <c r="G37" s="18" t="n"/>
-      <c r="H37" s="19" t="n"/>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
@@ -1918,7 +1938,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_素案_第10稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D38" s="18" t="n"/>
@@ -1928,9 +1948,9 @@
       <c r="H38" s="19" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
@@ -1938,7 +1958,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
+          <t>必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D39" s="18" t="n"/>
@@ -1948,17 +1968,17 @@
       <c r="H39" s="19" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D40" s="18" t="n"/>
@@ -1968,17 +1988,17 @@
       <c r="H40" s="19" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認</t>
+          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D41" s="18" t="n"/>
@@ -1988,17 +2008,17 @@
       <c r="H41" s="19" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認</t>
         </is>
       </c>
       <c r="D42" s="18" t="n"/>
@@ -2008,17 +2028,17 @@
       <c r="H42" s="19" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_第4稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D43" s="18" t="n"/>
@@ -2028,17 +2048,17 @@
       <c r="H43" s="19" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_第4稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D44" s="18" t="n"/>
@@ -2047,18 +2067,18 @@
       <c r="G44" s="18" t="n"/>
       <c r="H44" s="19" t="n"/>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="C45" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの24件、別スコープ5件</t>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D45" s="18" t="n"/>
@@ -2067,8 +2087,28 @@
       <c r="G45" s="18" t="n"/>
       <c r="H45" s="19" t="n"/>
     </row>
-    <row r="47" ht="100" customHeight="1">
-      <c r="A47" s="21" t="inlineStr">
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの25件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="n"/>
+      <c r="E46" s="18" t="n"/>
+      <c r="F46" s="18" t="n"/>
+      <c r="G46" s="18" t="n"/>
+      <c r="H46" s="19" t="n"/>
+    </row>
+    <row r="48" ht="100" customHeight="1">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2076,17 +2116,17 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C46:H46"/>
     <mergeCell ref="C38:H38"/>
     <mergeCell ref="C41:H41"/>
     <mergeCell ref="C42:H42"/>
-    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A48:H48"/>
     <mergeCell ref="C44:H44"/>
-    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C40:H40"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C45:H45"/>
     <mergeCell ref="C39:H39"/>
-    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="C43:H43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -809,7 +809,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -1502,39 +1502,39 @@
       <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第4稿.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映したもの。13章18表。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシートへ移した。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>96段落 18表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>第4稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1549,32 +1549,32 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第5稿.docx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシートへ移した。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>96段落 18表</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第5稿</t>
         </is>
       </c>
     </row>
@@ -1589,27 +1589,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項13項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>31段落 17表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>46 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1622,34 +1622,34 @@
       <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項13項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>31段落 17表</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>46 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1702,39 +1702,39 @@
       <c r="A30" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1749,27 +1749,27 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H31" s="16" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H32" s="16" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1869,88 +1869,108 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H34" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="52" customHeight="1">
+      <c r="A35" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="H35" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr"/>
+      <c r="E38" s="3" t="inlineStr"/>
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_素案_第10稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="n"/>
-      <c r="E38" s="18" t="n"/>
-      <c r="F38" s="18" t="n"/>
-      <c r="G38" s="18" t="n"/>
-      <c r="H38" s="19" t="n"/>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
@@ -1958,7 +1978,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_素案_第10稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D39" s="18" t="n"/>
@@ -1968,9 +1988,9 @@
       <c r="H39" s="19" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
@@ -1978,7 +1998,7 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
+          <t>必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D40" s="18" t="n"/>
@@ -1988,17 +2008,17 @@
       <c r="H40" s="19" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D41" s="18" t="n"/>
@@ -2008,17 +2028,17 @@
       <c r="H41" s="19" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認</t>
+          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D42" s="18" t="n"/>
@@ -2028,17 +2048,17 @@
       <c r="H42" s="19" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量</t>
         </is>
       </c>
       <c r="D43" s="18" t="n"/>
@@ -2048,17 +2068,17 @@
       <c r="H43" s="19" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_第4稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D44" s="18" t="n"/>
@@ -2068,17 +2088,17 @@
       <c r="H44" s="19" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_第5稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D45" s="18" t="n"/>
@@ -2087,18 +2107,18 @@
       <c r="G45" s="18" t="n"/>
       <c r="H45" s="19" t="n"/>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B46" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="C46" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの25件、別スコープ5件</t>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D46" s="18" t="n"/>
@@ -2107,8 +2127,28 @@
       <c r="G46" s="18" t="n"/>
       <c r="H46" s="19" t="n"/>
     </row>
-    <row r="48" ht="100" customHeight="1">
-      <c r="A48" s="21" t="inlineStr">
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの26件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="n"/>
+      <c r="E47" s="18" t="n"/>
+      <c r="F47" s="18" t="n"/>
+      <c r="G47" s="18" t="n"/>
+      <c r="H47" s="19" t="n"/>
+    </row>
+    <row r="49" ht="100" customHeight="1">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2117,17 +2157,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C46:H46"/>
-    <mergeCell ref="C38:H38"/>
     <mergeCell ref="C41:H41"/>
     <mergeCell ref="C42:H42"/>
-    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="C47:H47"/>
     <mergeCell ref="C44:H44"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="C40:H40"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="C45:H45"/>
     <mergeCell ref="C39:H39"/>
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A49:H49"/>
     <mergeCell ref="C43:H43"/>
+    <mergeCell ref="A37:H37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2363,14 +2403,14 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>① キックオフ会議資料 第4稿
+          <t>① キックオフ会議資料 第5稿
 ② キックオフ会議ヒアリングシート
 ③ キックオフ資料の点検結果 00_点検の結果（反映の経緯）</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>第4稿は、点検結果12件と青枠の仕分けに加え、人口推計の基礎の記述の修正と3調査の受領・点検の結果を反映済みです。重大3件（事業所実態調査が業務範囲外、起点差の解消、H01の指標の変更）はいずれも本文に反映しました。ヒアリングシートは会議中にご記入いただく形式です。</t>
+          <t>第5稿は、点検結果12件と青枠の仕分けに加え、人口推計の基礎の記述の修正、3調査の受領・点検の結果、及び将来推計の第2段階の試算を反映済みです。重大3件（事業所実態調査が業務範囲外、起点差の解消、H01の指標の変更）はいずれも本文に反映しました。ヒアリングシートは会議中にご記入いただく形式です。</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -889,7 +889,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>51 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項31件（重大4件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項32件（重大5件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>88 KB</t>
+          <t>91 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1542,39 +1542,39 @@
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第5稿.docx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映したもの。13章18表。</t>
+          <t>北海道が公表する5つの名簿（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム）から区域内の施設・住まいを抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシートへ移した。</t>
+          <t>第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設であることを確認した。7シート。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>96段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>26 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>第5稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1589,32 +1589,32 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第5稿.docx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシートへ移した。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>96段落 18表</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第5稿</t>
         </is>
       </c>
     </row>
@@ -1629,27 +1629,27 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項13項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>31段落 17表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>46 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -1662,34 +1662,34 @@
       <c r="A29" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項13項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>31段落 17表</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>46 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1709,17 +1709,17 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -1742,39 +1742,39 @@
       <c r="A31" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1789,27 +1789,27 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H32" s="16" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H33" s="16" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -1909,88 +1909,108 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H35" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="52" customHeight="1">
+      <c r="A36" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H35" s="16" t="inlineStr">
+      <c r="H36" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr"/>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="3" t="inlineStr"/>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_素案_第10稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D39" s="18" t="n"/>
-      <c r="E39" s="18" t="n"/>
-      <c r="F39" s="18" t="n"/>
-      <c r="G39" s="18" t="n"/>
-      <c r="H39" s="19" t="n"/>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
@@ -1998,7 +2018,7 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_素案_第10稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D40" s="18" t="n"/>
@@ -2008,9 +2028,9 @@
       <c r="H40" s="19" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
@@ -2018,7 +2038,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
+          <t>必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D41" s="18" t="n"/>
@@ -2028,17 +2048,17 @@
       <c r="H41" s="19" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D42" s="18" t="n"/>
@@ -2048,17 +2068,17 @@
       <c r="H42" s="19" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量</t>
+          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D43" s="18" t="n"/>
@@ -2068,17 +2088,17 @@
       <c r="H43" s="19" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、住まいと施設の公表名簿との突合</t>
         </is>
       </c>
       <c r="D44" s="18" t="n"/>
@@ -2088,17 +2108,17 @@
       <c r="H44" s="19" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_第5稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D45" s="18" t="n"/>
@@ -2108,17 +2128,17 @@
       <c r="H45" s="19" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_第5稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D46" s="18" t="n"/>
@@ -2127,18 +2147,18 @@
       <c r="G46" s="18" t="n"/>
       <c r="H46" s="19" t="n"/>
     </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B47" s="20" t="n">
-        <v>31</v>
-      </c>
-      <c r="C47" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの26件、別スコープ5件</t>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D47" s="18" t="n"/>
@@ -2147,8 +2167,28 @@
       <c r="G47" s="18" t="n"/>
       <c r="H47" s="19" t="n"/>
     </row>
-    <row r="49" ht="100" customHeight="1">
-      <c r="A49" s="21" t="inlineStr">
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの27件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="n"/>
+      <c r="E48" s="18" t="n"/>
+      <c r="F48" s="18" t="n"/>
+      <c r="G48" s="18" t="n"/>
+      <c r="H48" s="19" t="n"/>
+    </row>
+    <row r="50" ht="100" customHeight="1">
+      <c r="A50" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2156,18 +2196,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A50:H50"/>
     <mergeCell ref="C46:H46"/>
     <mergeCell ref="C41:H41"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C47:H47"/>
     <mergeCell ref="C44:H44"/>
+    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C40:H40"/>
     <mergeCell ref="C45:H45"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="C48:H48"/>
     <mergeCell ref="C43:H43"/>
-    <mergeCell ref="A37:H37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -809,7 +809,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>41 KB</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>91 KB</t>
+          <t>92 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1554,22 +1554,22 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する5つの名簿（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム）から区域内の施設・住まいを抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員が58人ではなく156人であること、住宅型有料老人ホームが3施設ではなく9施設であることを確認した。7シート。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シート。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>26 KB</t>
+          <t>38 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1559,17 +1559,17 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シート。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シート。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>11シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>38 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1589,32 +1589,32 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第5稿.docx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映したもの。13章18表。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシートへ移した。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（14項目）へ移した。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>96段落 18表</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>第5稿</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項13項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項14項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>31段落 17表</t>
+          <t>32段落 18表</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>46 KB</t>
+          <t>48 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_第5稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D46" s="18" t="n"/>
@@ -2443,14 +2443,14 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>① キックオフ会議資料 第5稿
+          <t>① キックオフ会議資料 第6稿
 ② キックオフ会議ヒアリングシート
 ③ キックオフ資料の点検結果 00_点検の結果（反映の経緯）</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>第5稿は、点検結果12件と青枠の仕分けに加え、人口推計の基礎の記述の修正、3調査の受領・点検の結果、及び将来推計の第2段階の試算を反映済みです。重大3件（事業所実態調査が業務範囲外、起点差の解消、H01の指標の変更）はいずれも本文に反映しました。ヒアリングシートは会議中にご記入いただく形式です。</t>
+          <t>第6稿は、点検結果12件と青枠の仕分けに加え、人口推計の基礎の記述の修正、3調査の受領・点検の結果、将来推計の第2段階の試算、及び北海道の施設・住まいの名簿との突合を反映済みです。重大3件（事業所実態調査が業務範囲外、起点差の解消、H01の指標の変更）はいずれも本文に反映しました。ヒアリングシートは会議中にご記入いただく形式です。</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_素案_第10稿.docx</t>
+          <t>第10期介護保険事業計画_素案_第11稿.docx</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第11稿で第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映した。</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>585段落 102表</t>
+          <t>620段落 108表</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>第10稿（6次）</t>
+          <t>第11稿（7次）</t>
         </is>
       </c>
     </row>
@@ -1549,27 +1549,27 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シート。</t>
+          <t>仕様書４（3）の成果品。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>11シート</t>
+          <t>14シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>43 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1582,39 +1582,39 @@
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（14項目）へ移した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シート。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>11シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>45 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1629,32 +1629,32 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（14項目）へ移した。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -1669,27 +1669,27 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項14項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>32段落 18表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>48 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1702,34 +1702,34 @@
       <c r="A30" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項14項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>32段落 18表</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>48 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -1749,17 +1749,17 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1782,39 +1782,39 @@
       <c r="A32" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1829,27 +1829,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H33" s="16" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H34" s="16" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -1949,88 +1949,108 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H36" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="52" customHeight="1">
+      <c r="A37" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H36" s="16" t="inlineStr">
+      <c r="H37" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr"/>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_素案_第10稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D40" s="18" t="n"/>
-      <c r="E40" s="18" t="n"/>
-      <c r="F40" s="18" t="n"/>
-      <c r="G40" s="18" t="n"/>
-      <c r="H40" s="19" t="n"/>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
@@ -2038,7 +2058,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D41" s="18" t="n"/>
@@ -2048,9 +2068,9 @@
       <c r="H41" s="19" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B42" s="6" t="n">
@@ -2058,7 +2078,7 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
+          <t>必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D42" s="18" t="n"/>
@@ -2068,17 +2088,17 @@
       <c r="H42" s="19" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D43" s="18" t="n"/>
@@ -2088,17 +2108,17 @@
       <c r="H43" s="19" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、住まいと施設の公表名簿との突合</t>
+          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D44" s="18" t="n"/>
@@ -2108,17 +2128,17 @@
       <c r="H44" s="19" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合</t>
         </is>
       </c>
       <c r="D45" s="18" t="n"/>
@@ -2128,17 +2148,17 @@
       <c r="H45" s="19" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D46" s="18" t="n"/>
@@ -2148,17 +2168,17 @@
       <c r="H46" s="19" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D47" s="18" t="n"/>
@@ -2167,18 +2187,18 @@
       <c r="G47" s="18" t="n"/>
       <c r="H47" s="19" t="n"/>
     </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B48" s="20" t="n">
-        <v>32</v>
-      </c>
-      <c r="C48" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの27件、別スコープ5件</t>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D48" s="18" t="n"/>
@@ -2187,8 +2207,28 @@
       <c r="G48" s="18" t="n"/>
       <c r="H48" s="19" t="n"/>
     </row>
-    <row r="50" ht="100" customHeight="1">
-      <c r="A50" s="21" t="inlineStr">
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの28件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="n"/>
+      <c r="E49" s="18" t="n"/>
+      <c r="F49" s="18" t="n"/>
+      <c r="G49" s="18" t="n"/>
+      <c r="H49" s="19" t="n"/>
+    </row>
+    <row r="51" ht="100" customHeight="1">
+      <c r="A51" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2196,16 +2236,16 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A50:H50"/>
     <mergeCell ref="C46:H46"/>
     <mergeCell ref="C41:H41"/>
     <mergeCell ref="C42:H42"/>
+    <mergeCell ref="A39:H39"/>
     <mergeCell ref="C47:H47"/>
     <mergeCell ref="C44:H44"/>
-    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="A51:H51"/>
     <mergeCell ref="C45:H45"/>
+    <mergeCell ref="C49:H49"/>
     <mergeCell ref="C48:H48"/>
     <mergeCell ref="C43:H43"/>
   </mergeCells>
@@ -2577,7 +2617,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_素案_第10稿.docx（585段落102表34図）</t>
+          <t>第10期介護保険事業計画_素案_第11稿.docx（585段落102表34図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -2698,7 +2738,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>計画素案（第10稿）に統合して先行作成</t>
+          <t>計画素案（第11稿）に統合して先行作成</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -2728,7 +2768,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_素案_第10稿.docx</t>
+          <t>第10期介護保険事業計画_素案_第11稿.docx</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1549,27 +1549,27 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の成果品。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。8章41表。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>14シート</t>
+          <t>308段落 41表</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>64 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1589,27 +1589,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シート。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>11シート</t>
+          <t>14シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>45 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1622,39 +1622,39 @@
       <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（14項目）へ移した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シート。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>11シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>45 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1669,32 +1669,32 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（14項目）へ移した。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -1709,27 +1709,27 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項14項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>32段落 18表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>48 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -1742,34 +1742,34 @@
       <c r="A31" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項14項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>32段落 18表</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>48 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1789,17 +1789,17 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1822,39 +1822,39 @@
       <c r="A33" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1869,27 +1869,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H34" s="16" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H35" s="16" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -1989,88 +1989,108 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H37" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="52" customHeight="1">
+      <c r="A38" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H37" s="16" t="inlineStr">
+      <c r="H38" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="17" t="inlineStr">
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr"/>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D41" s="18" t="n"/>
-      <c r="E41" s="18" t="n"/>
-      <c r="F41" s="18" t="n"/>
-      <c r="G41" s="18" t="n"/>
-      <c r="H41" s="19" t="n"/>
-    </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B42" s="6" t="n">
@@ -2078,7 +2098,7 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D42" s="18" t="n"/>
@@ -2088,9 +2108,9 @@
       <c r="H42" s="19" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
@@ -2098,7 +2118,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
+          <t>必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D43" s="18" t="n"/>
@@ -2108,17 +2128,17 @@
       <c r="H43" s="19" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D44" s="18" t="n"/>
@@ -2128,17 +2148,17 @@
       <c r="H44" s="19" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合</t>
+          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D45" s="18" t="n"/>
@@ -2148,17 +2168,17 @@
       <c r="H45" s="19" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合</t>
         </is>
       </c>
       <c r="D46" s="18" t="n"/>
@@ -2168,17 +2188,17 @@
       <c r="H46" s="19" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D47" s="18" t="n"/>
@@ -2188,17 +2208,17 @@
       <c r="H47" s="19" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D48" s="18" t="n"/>
@@ -2207,18 +2227,18 @@
       <c r="G48" s="18" t="n"/>
       <c r="H48" s="19" t="n"/>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="C49" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの28件、別スコープ5件</t>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D49" s="18" t="n"/>
@@ -2227,8 +2247,28 @@
       <c r="G49" s="18" t="n"/>
       <c r="H49" s="19" t="n"/>
     </row>
-    <row r="51" ht="100" customHeight="1">
-      <c r="A51" s="21" t="inlineStr">
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの29件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="n"/>
+      <c r="E50" s="18" t="n"/>
+      <c r="F50" s="18" t="n"/>
+      <c r="G50" s="18" t="n"/>
+      <c r="H50" s="19" t="n"/>
+    </row>
+    <row r="52" ht="100" customHeight="1">
+      <c r="A52" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2237,17 +2277,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C46:H46"/>
-    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="C47:H47"/>
     <mergeCell ref="C42:H42"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="C47:H47"/>
+    <mergeCell ref="C50:H50"/>
     <mergeCell ref="C44:H44"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A52:H52"/>
     <mergeCell ref="C45:H45"/>
     <mergeCell ref="C49:H49"/>
     <mergeCell ref="C48:H48"/>
     <mergeCell ref="C43:H43"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1559,17 +1559,17 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。8章41表。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章41表39図。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>308段落 41表</t>
+          <t>394段落 41表</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>64 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1564,7 +1564,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>394段落 41表</t>
+          <t>401段落 41表</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1399,7 +1399,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項32件（重大5件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項33件（重大5件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>45 KB</t>
+          <t>46 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1679,7 +1679,7 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（14項目）へ移した。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項14項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>32段落 18表</t>
+          <t>34段落 20表</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>48 KB</t>
+          <t>51 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1399,7 +1399,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項33件（重大5件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項34件（重大5件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>92 KB</t>
+          <t>93 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>401段落 41表</t>
+          <t>439段落 46表</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1409,7 +1409,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>93 KB</t>
+          <t>95 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>439段落 46表</t>
+          <t>456段落 48表</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -889,7 +889,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項34件（重大5件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章41表39図。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章48表39図。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -198,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -259,9 +259,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -629,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -709,32 +706,32 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_素案_第11稿.docx</t>
+          <t>第10期介護保険事業計画_骨子案.docx</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>計画素案の本文。第1章から第6章及び資料編。</t>
+          <t>計画の構成、基本理念・基本目標、施策の体系、成果指標の枠組み、サービス見込量と保険料の算定の枠組み、各章の記載内容と根拠資料の対照、決定・確認を要する事項12件。</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第11稿で第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映した。</t>
+          <t>計画本文を書き始める前に「各章に何を、どの資料に基づいて記載するか」を確定させる文書。第8節の章立てと根拠資料の対照表が中核である。第10節に、ご決定・ご確認をお願いする12件を優先順に整理している。</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>620段落 108表</t>
+          <t>123段落 22表</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>2.3 MB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>第11稿（7次）</t>
+          <t>第1稿</t>
         </is>
       </c>
     </row>
@@ -749,32 +746,32 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_図表集_白黒.xlsx</t>
+          <t>第10期介護保険事業計画_素案_第11稿.docx</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>本文及び資料編に用いる図表。白黒印刷を前提に濃淡・ハッチング・線種で系列を区別している。</t>
+          <t>計画素案の本文。第1章から第6章及び資料編。</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>本文に掲載する図の実体。掲載区分（本文／資料編／参考）を各シートに付している。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第11稿で第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映した。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>33シート</t>
+          <t>620段落 108表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>277 KB</t>
+          <t>2.3 MB</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>33シート133点</t>
+          <t>第11稿（7次）</t>
         </is>
       </c>
     </row>
@@ -782,39 +779,39 @@
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>計画本体</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_図表集_白黒.xlsx</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
+          <t>本文及び資料編に用いる図表。白黒印刷を前提に濃淡・ハッチング・線種で系列を区別している。</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
+          <t>本文に掲載する図の実体。掲載区分（本文／資料編／参考）を各シートに付している。</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>33シート</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>41 KB</t>
+          <t>277 KB</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>33シート133点</t>
         </is>
       </c>
     </row>
@@ -829,32 +826,32 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>第1回委員会に向けた確認事項の依頼文書。</t>
+          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
+          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>第9版</t>
+          <t>7シート</t>
         </is>
       </c>
     </row>
@@ -862,34 +859,34 @@
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>41 KB</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -902,39 +899,39 @@
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>第1回委員会に向けた確認事項の依頼文書。</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第9版</t>
         </is>
       </c>
     </row>
@@ -942,34 +939,34 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
@@ -982,34 +979,34 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -1029,27 +1026,27 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
@@ -1062,34 +1059,34 @@
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -1102,34 +1099,34 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -1149,27 +1146,27 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -1189,27 +1186,27 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -1229,27 +1226,27 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1269,17 +1266,17 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1289,7 +1286,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -1309,27 +1306,27 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -1349,27 +1346,27 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1389,27 +1386,27 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>95 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1429,27 +1426,27 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1469,27 +1466,27 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>95 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -1509,27 +1506,27 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1549,27 +1546,27 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章48表39図。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>456段落 48表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1589,27 +1586,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>14シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1629,27 +1626,27 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章48表39図。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>11シート</t>
+          <t>456段落 48表</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>46 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -1662,39 +1659,39 @@
       <c r="A29" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>14シート</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1702,34 +1699,34 @@
       <c r="A30" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シート。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>11シート</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>46 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -1749,32 +1746,32 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>34段落 20表</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>51 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -1782,34 +1779,34 @@
       <c r="A32" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1822,34 +1819,34 @@
       <c r="A33" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>34段落 20表</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>51 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -1862,39 +1859,39 @@
       <c r="A34" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>18 KB</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1902,39 +1899,39 @@
       <c r="A35" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
-        </is>
-      </c>
-      <c r="H35" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1949,27 +1946,27 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H36" s="16" t="inlineStr">
@@ -1989,12 +1986,12 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -2009,7 +2006,7 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H37" s="16" t="inlineStr">
@@ -2029,116 +2026,156 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H38" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="52" customHeight="1">
+      <c r="A39" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H39" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="52" customHeight="1">
+      <c r="A40" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H38" s="16" t="inlineStr">
+      <c r="H40" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="17" t="inlineStr">
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
         </is>
       </c>
-      <c r="B42" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D42" s="18" t="n"/>
-      <c r="E42" s="18" t="n"/>
-      <c r="F42" s="18" t="n"/>
-      <c r="G42" s="18" t="n"/>
-      <c r="H42" s="19" t="n"/>
-    </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>必要事項の一覧、確認依頼書</t>
-        </is>
-      </c>
-      <c r="D43" s="18" t="n"/>
-      <c r="E43" s="18" t="n"/>
-      <c r="F43" s="18" t="n"/>
-      <c r="G43" s="18" t="n"/>
-      <c r="H43" s="19" t="n"/>
-    </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>工程管理</t>
-        </is>
-      </c>
       <c r="B44" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D44" s="18" t="n"/>
@@ -2148,9 +2185,9 @@
       <c r="H44" s="19" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
@@ -2158,7 +2195,7 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D45" s="18" t="n"/>
@@ -2168,17 +2205,17 @@
       <c r="H45" s="19" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D46" s="18" t="n"/>
@@ -2188,17 +2225,17 @@
       <c r="H46" s="19" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D47" s="18" t="n"/>
@@ -2208,17 +2245,17 @@
       <c r="H47" s="19" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合</t>
         </is>
       </c>
       <c r="D48" s="18" t="n"/>
@@ -2228,17 +2265,17 @@
       <c r="H48" s="19" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D49" s="18" t="n"/>
@@ -2247,18 +2284,18 @@
       <c r="G49" s="18" t="n"/>
       <c r="H49" s="19" t="n"/>
     </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B50" s="20" t="n">
-        <v>34</v>
-      </c>
-      <c r="C50" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの29件、別スコープ5件</t>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D50" s="18" t="n"/>
@@ -2267,8 +2304,48 @@
       <c r="G50" s="18" t="n"/>
       <c r="H50" s="19" t="n"/>
     </row>
-    <row r="52" ht="100" customHeight="1">
-      <c r="A52" s="21" t="inlineStr">
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="n"/>
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="18" t="n"/>
+      <c r="G51" s="18" t="n"/>
+      <c r="H51" s="19" t="n"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの31件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="n"/>
+      <c r="E52" s="18" t="n"/>
+      <c r="F52" s="18" t="n"/>
+      <c r="G52" s="18" t="n"/>
+      <c r="H52" s="19" t="n"/>
+    </row>
+    <row r="54" ht="100" customHeight="1">
+      <c r="A54" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2276,18 +2353,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C51:H51"/>
     <mergeCell ref="C46:H46"/>
     <mergeCell ref="C47:H47"/>
-    <mergeCell ref="C42:H42"/>
     <mergeCell ref="C50:H50"/>
     <mergeCell ref="C44:H44"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="C52:H52"/>
+    <mergeCell ref="A54:H54"/>
     <mergeCell ref="C45:H45"/>
+    <mergeCell ref="A42:H42"/>
     <mergeCell ref="C49:H49"/>
     <mergeCell ref="C48:H48"/>
-    <mergeCell ref="C43:H43"/>
-    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2657,7 +2734,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_素案_第11稿.docx（585段落102表34図）</t>
+          <t>第10期介護保険事業計画_素案_第11稿.docx（620段落108表34図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -2778,17 +2855,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>計画素案（第11稿）に統合して先行作成</t>
+          <t>第10期介護保険事業計画_骨子案.docx（11節22表）</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>骨子案を素案とは別に作成する必要があるかの確認。</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+          <t>第10節の決定・確認を要する事項12件。とくにNo.1（第9期の施策・事業実績）とNo.2（調査の点検事項）。</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>123段落 22表</t>
+          <t>124段落 22表</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -81,6 +81,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E4DFEC"/>
+        <bgColor rgb="00E4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
       </patternFill>
@@ -95,12 +101,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2DCDB"/>
         <bgColor rgb="00F2DCDB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E4DFEC"/>
-        <bgColor rgb="00E4DFEC"/>
       </patternFill>
     </fill>
     <fill>
@@ -255,7 +255,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -721,12 +721,12 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>124段落 22表</t>
+          <t>130段落 23表</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
@@ -821,37 +821,37 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>発注者への依頼</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
+          <t>サービス見込量の4つの前提（認定者数、利用率、1人当たりの利用日数・回数、要介護度別の構成比）について、低位・標準・高位の3シナリオを示したもの。レバーごとの感度、サービス種別・年度別の幅、定員制約との突合、調査結果による上振れ材料と加算しない理由、採用値の決定に要すること。</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
+          <t>第6章第2節の見込量の採用値を決める資料。標準は将来推計 第2段階の基本ケースと同じである。低位・高位は前提を同時に片側へ置いた包絡であり確率的な区間ではない。07シートに受託者案と決定を要する7件を示している。</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
     </row>
@@ -859,39 +859,39 @@
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
+          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
+          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>41 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>7シート</t>
         </is>
       </c>
     </row>
@@ -899,39 +899,39 @@
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>第1回委員会に向けた確認事項の依頼文書。</t>
+          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
+          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>41 KB</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>第9版</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -941,37 +941,37 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>工程管理</t>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>第1回委員会に向けた確認事項の依頼文書。</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第9版</t>
         </is>
       </c>
     </row>
@@ -979,34 +979,34 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>工程管理</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>第9期の評価</t>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
@@ -1059,34 +1059,34 @@
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>第9期の評価</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -1099,34 +1099,34 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>第9期の評価</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -1141,32 +1141,32 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -1179,34 +1179,34 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -1219,34 +1219,34 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1259,34 +1259,34 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -1299,34 +1299,34 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -1339,34 +1339,34 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1379,34 +1379,34 @@
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1419,34 +1419,34 @@
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1459,34 +1459,34 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>95 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -1499,34 +1499,34 @@
       <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>95 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1539,24 +1539,24 @@
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1579,34 +1579,34 @@
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1619,34 +1619,34 @@
       <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章48表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>456段落 48表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -1659,34 +1659,34 @@
       <c r="A29" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章48表39図。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>14シート</t>
+          <t>456段落 48表</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1699,34 +1699,34 @@
       <c r="A30" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シート。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>11シート</t>
+          <t>14シート</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>46 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -1739,39 +1739,39 @@
       <c r="A31" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シート。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>11シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>46 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1786,32 +1786,32 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -1826,27 +1826,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>34段落 20表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>51 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -1859,34 +1859,34 @@
       <c r="A34" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>34段落 20表</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>51 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -1906,17 +1906,17 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -1939,39 +1939,39 @@
       <c r="A36" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H36" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1986,27 +1986,27 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H37" s="16" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H38" s="16" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -2106,88 +2106,108 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H40" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="52" customHeight="1">
+      <c r="A41" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H40" s="16" t="inlineStr">
+      <c r="H41" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D44" s="18" t="n"/>
-      <c r="E44" s="18" t="n"/>
-      <c r="F44" s="18" t="n"/>
-      <c r="G44" s="18" t="n"/>
-      <c r="H44" s="19" t="n"/>
-    </row>
-    <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
@@ -2195,7 +2215,7 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D45" s="18" t="n"/>
@@ -2207,15 +2227,15 @@
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>工程管理</t>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D46" s="18" t="n"/>
@@ -2227,15 +2247,15 @@
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>第9期の評価</t>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D47" s="18" t="n"/>
@@ -2247,15 +2267,15 @@
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合</t>
+          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D48" s="18" t="n"/>
@@ -2265,17 +2285,17 @@
       <c r="H48" s="19" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>将来推計_需要3シナリオの感度表、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合</t>
         </is>
       </c>
       <c r="D49" s="18" t="n"/>
@@ -2285,17 +2305,17 @@
       <c r="H49" s="19" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D50" s="18" t="n"/>
@@ -2305,17 +2325,17 @@
       <c r="H50" s="19" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D51" s="18" t="n"/>
@@ -2324,18 +2344,18 @@
       <c r="G51" s="18" t="n"/>
       <c r="H51" s="19" t="n"/>
     </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B52" s="20" t="n">
-        <v>36</v>
-      </c>
-      <c r="C52" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの31件、別スコープ5件</t>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D52" s="18" t="n"/>
@@ -2344,8 +2364,28 @@
       <c r="G52" s="18" t="n"/>
       <c r="H52" s="19" t="n"/>
     </row>
-    <row r="54" ht="100" customHeight="1">
-      <c r="A54" s="21" t="inlineStr">
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの32件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D53" s="18" t="n"/>
+      <c r="E53" s="18" t="n"/>
+      <c r="F53" s="18" t="n"/>
+      <c r="G53" s="18" t="n"/>
+      <c r="H53" s="19" t="n"/>
+    </row>
+    <row r="55" ht="100" customHeight="1">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2356,13 +2396,13 @@
     <mergeCell ref="C51:H51"/>
     <mergeCell ref="C46:H46"/>
     <mergeCell ref="C47:H47"/>
+    <mergeCell ref="A55:H55"/>
     <mergeCell ref="C50:H50"/>
-    <mergeCell ref="C44:H44"/>
+    <mergeCell ref="A43:H43"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C52:H52"/>
-    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="C53:H53"/>
     <mergeCell ref="C45:H45"/>
-    <mergeCell ref="A42:H42"/>
     <mergeCell ref="C49:H49"/>
     <mergeCell ref="C48:H48"/>
   </mergeCells>
@@ -3017,7 +3057,7 @@
           <t>圏域を統計単位と整備単位に分ける案。訪問・通所困難地域の定義。自給率の3町間の差が3町単位を裏付ける。</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>事業所の実施地域の受領待ち</t>
         </is>
@@ -3039,7 +3079,7 @@
           <t>特定地域の指定基準の判定。3町のうち美瑛町が該当の見込み。</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>告示待ち</t>
         </is>
@@ -3149,7 +3189,7 @@
           <t>令和22年度・令和32年度の人口と認定者数。</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>給付費は第3段階待ち</t>
         </is>
@@ -3171,7 +3211,7 @@
           <t>代表KPIの3軸評価。交付金評価。長期でみた到達点。</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>事業実績の受領待ち（プロセス評価）</t>
         </is>
@@ -3193,7 +3233,7 @@
           <t>代表KPI16項目のデータ源と基準値。</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>3調査の第10期分の受領待ち</t>
         </is>
@@ -3215,7 +3255,7 @@
           <t>5基本目標の5層構成。アウトプットとアウトカムの分離。</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>事業実績の受領待ち</t>
         </is>
@@ -3237,7 +3277,7 @@
           <t>階級別人口×階級別認定率。3シナリオ。</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>シナリオの決定待ち</t>
         </is>
@@ -3259,7 +3299,7 @@
           <t>要介護度別の利用率と単価により算定する。</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>要介護度別認定者数と給付実績の受領待ち</t>
         </is>
@@ -3281,7 +3321,7 @@
           <t>24時間対応サービスの確保方策。区域外の施設への依存。</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>定員・稼働の実績の受領待ち</t>
         </is>
@@ -3303,7 +3343,7 @@
           <t>第9期の剰余の確定。管内比較。16段階の妥当性。</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>決算・基金と政令改正待ち</t>
         </is>
@@ -3325,7 +3365,7 @@
           <t>基本指針の新別表11事項への対応表。図表番号一覧。</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>告示待ち</t>
         </is>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -87,6 +87,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DAEEF3"/>
+        <bgColor rgb="00DAEEF3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
       </patternFill>
@@ -101,12 +107,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2DCDB"/>
         <bgColor rgb="00F2DCDB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DAEEF3"/>
-        <bgColor rgb="00DAEEF3"/>
       </patternFill>
     </fill>
     <fill>
@@ -255,7 +255,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -861,37 +861,37 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>発注者への依頼</t>
+          <t>会議</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_キックオフ会議_トークスクリプト_60分.docx</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
+          <t>60分のキックオフ会議の進行台本。網掛けの枠がそのまま読み上げる台本で、枠外は進行のための注記。決定4件・確認1件に絞り、残る8項目は書面確認とする。</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
+          <t>会議の当日に手元に置く。冒頭で「本日は6件の決定に絞る」合意をとる構成としている。0:05–0:12にキックオフ会議資料（更新版）との差の対照表を置いている。</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>80段落 12表</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>46 KB</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>第1稿</t>
         </is>
       </c>
     </row>
@@ -901,37 +901,37 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>発注者への依頼</t>
+          <t>会議</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
+          <t>トークスクリプトと対で用いる進行者の手元資料。想定される回答ごとの応答、記録すること、決まらなかった場合の着地点。会議運営上の分岐と想定問答。</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
+          <t>決定ごとに5〜6の分岐を用意している。00シートに時間が押した場合の切り方（優先順位）、07シートに会議資料（更新版）との差の説明を置いている。</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>34 KB</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
           <t>8シート</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>41 KB</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>最新</t>
         </is>
       </c>
     </row>
@@ -939,39 +939,39 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>第1回委員会に向けた確認事項の依頼文書。</t>
+          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
+          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>第9版</t>
+          <t>7シート</t>
         </is>
       </c>
     </row>
@@ -981,32 +981,32 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>工程管理</t>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>41 KB</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -1021,37 +1021,37 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>工程管理</t>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>第1回委員会に向けた確認事項の依頼文書。</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第9版</t>
         </is>
       </c>
     </row>
@@ -1061,32 +1061,32 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>第9期の評価</t>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -1101,32 +1101,32 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>第9期の評価</t>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -1139,34 +1139,34 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>第9期の評価</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -1179,34 +1179,34 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -1219,34 +1219,34 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1266,27 +1266,27 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -1306,27 +1306,27 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -1346,27 +1346,27 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1386,17 +1386,17 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1426,27 +1426,27 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -1506,27 +1506,27 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>95 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1546,27 +1546,27 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1586,27 +1586,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>95 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1626,27 +1626,27 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -1666,27 +1666,27 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章48表39図。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>456段落 48表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1706,27 +1706,27 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>14シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -1746,27 +1746,27 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章48表39図。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>11シート</t>
+          <t>456段落 48表</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>46 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1779,39 +1779,39 @@
       <c r="A32" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>14シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1819,34 +1819,34 @@
       <c r="A33" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シート。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>11シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>46 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -1859,39 +1859,39 @@
       <c r="A34" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>会議</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>34段落 20表</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>51 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -1899,34 +1899,34 @@
       <c r="A35" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -1939,34 +1939,34 @@
       <c r="A36" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -1979,39 +1979,39 @@
       <c r="A37" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H37" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>18 KB</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2019,39 +2019,39 @@
       <c r="A38" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
-        </is>
-      </c>
-      <c r="H38" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2066,27 +2066,27 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H39" s="16" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H40" s="16" t="inlineStr">
@@ -2146,116 +2146,156 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H41" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="52" customHeight="1">
+      <c r="A42" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H42" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="52" customHeight="1">
+      <c r="A43" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H41" s="16" t="inlineStr">
+      <c r="H43" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr"/>
-    </row>
-    <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr"/>
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
         </is>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B47" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D45" s="18" t="n"/>
-      <c r="E45" s="18" t="n"/>
-      <c r="F45" s="18" t="n"/>
-      <c r="G45" s="18" t="n"/>
-      <c r="H45" s="19" t="n"/>
-    </row>
-    <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
-        </is>
-      </c>
-      <c r="D46" s="18" t="n"/>
-      <c r="E46" s="18" t="n"/>
-      <c r="F46" s="18" t="n"/>
-      <c r="G46" s="18" t="n"/>
-      <c r="H46" s="19" t="n"/>
-    </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>工程管理</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D47" s="18" t="n"/>
@@ -2265,9 +2305,9 @@
       <c r="H47" s="19" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B48" s="6" t="n">
@@ -2275,7 +2315,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D48" s="18" t="n"/>
@@ -2285,17 +2325,17 @@
       <c r="H48" s="19" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D49" s="18" t="n"/>
@@ -2305,17 +2345,17 @@
       <c r="H49" s="19" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D50" s="18" t="n"/>
@@ -2325,17 +2365,17 @@
       <c r="H50" s="19" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
-      <c r="A51" s="13" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>将来推計_需要3シナリオの感度表、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合</t>
         </is>
       </c>
       <c r="D51" s="18" t="n"/>
@@ -2345,17 +2385,17 @@
       <c r="H51" s="19" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B52" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D52" s="18" t="n"/>
@@ -2364,18 +2404,18 @@
       <c r="G52" s="18" t="n"/>
       <c r="H52" s="19" t="n"/>
     </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B53" s="20" t="n">
-        <v>37</v>
-      </c>
-      <c r="C53" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの32件、別スコープ5件</t>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D53" s="18" t="n"/>
@@ -2384,8 +2424,48 @@
       <c r="G53" s="18" t="n"/>
       <c r="H53" s="19" t="n"/>
     </row>
-    <row r="55" ht="100" customHeight="1">
-      <c r="A55" s="21" t="inlineStr">
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+        </is>
+      </c>
+      <c r="D54" s="18" t="n"/>
+      <c r="E54" s="18" t="n"/>
+      <c r="F54" s="18" t="n"/>
+      <c r="G54" s="18" t="n"/>
+      <c r="H54" s="19" t="n"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="n">
+        <v>39</v>
+      </c>
+      <c r="C55" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの34件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D55" s="18" t="n"/>
+      <c r="E55" s="18" t="n"/>
+      <c r="F55" s="18" t="n"/>
+      <c r="G55" s="18" t="n"/>
+      <c r="H55" s="19" t="n"/>
+    </row>
+    <row r="57" ht="100" customHeight="1">
+      <c r="A57" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2394,17 +2474,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C51:H51"/>
-    <mergeCell ref="C46:H46"/>
     <mergeCell ref="C47:H47"/>
-    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="C54:H54"/>
+    <mergeCell ref="C55:H55"/>
     <mergeCell ref="C50:H50"/>
-    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A57:H57"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C52:H52"/>
     <mergeCell ref="C53:H53"/>
-    <mergeCell ref="C45:H45"/>
     <mergeCell ref="C49:H49"/>
     <mergeCell ref="C48:H48"/>
+    <mergeCell ref="A45:H45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3057,7 +3137,7 @@
           <t>圏域を統計単位と整備単位に分ける案。訪問・通所困難地域の定義。自給率の3町間の差が3町単位を裏付ける。</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>事業所の実施地域の受領待ち</t>
         </is>
@@ -3079,7 +3159,7 @@
           <t>特定地域の指定基準の判定。3町のうち美瑛町が該当の見込み。</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>告示待ち</t>
         </is>
@@ -3189,7 +3269,7 @@
           <t>令和22年度・令和32年度の人口と認定者数。</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>給付費は第3段階待ち</t>
         </is>
@@ -3211,7 +3291,7 @@
           <t>代表KPIの3軸評価。交付金評価。長期でみた到達点。</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>事業実績の受領待ち（プロセス評価）</t>
         </is>
@@ -3233,7 +3313,7 @@
           <t>代表KPI16項目のデータ源と基準値。</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>3調査の第10期分の受領待ち</t>
         </is>
@@ -3255,7 +3335,7 @@
           <t>5基本目標の5層構成。アウトプットとアウトカムの分離。</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>事業実績の受領待ち</t>
         </is>
@@ -3277,7 +3357,7 @@
           <t>階級別人口×階級別認定率。3シナリオ。</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>シナリオの決定待ち</t>
         </is>
@@ -3299,7 +3379,7 @@
           <t>要介護度別の利用率と単価により算定する。</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>要介護度別認定者数と給付実績の受領待ち</t>
         </is>
@@ -3321,7 +3401,7 @@
           <t>24時間対応サービスの確保方策。区域外の施設への依存。</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>定員・稼働の実績の受領待ち</t>
         </is>
@@ -3343,7 +3423,7 @@
           <t>第9期の剰余の確定。管内比較。16段階の妥当性。</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>決算・基金と政令改正待ち</t>
         </is>
@@ -3365,7 +3445,7 @@
           <t>基本指針の新別表11事項への対応表。図表番号一覧。</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>告示待ち</t>
         </is>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -866,32 +866,32 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議_トークスクリプト_60分.docx</t>
+          <t>第10期計画_キックオフ会議資料（更新版）の校正結果.xlsx</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>60分のキックオフ会議の進行台本。網掛けの枠がそのまま読み上げる台本で、枠外は進行のための注記。決定4件・確認1件に絞り、残る8項目は書面確認とする。</t>
+          <t>発注者ご作成のキックオフ会議資料（更新版・令和8年8月6日現在）の校正結果。誤字脱字4件、事業所調査の修正漏れ9件、調査の状況が古いもの3件、記載の不足・不整合4件、表記の統一5件、ご確認事項5件の計30件。</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>会議の当日に手元に置く。冒頭で「本日は6件の決定に絞る」合意をとる構成としている。0:05–0:12にキックオフ会議資料（更新版）との差の対照表を置いている。</t>
+          <t>01シートに箇所・現在の記載・修正案・理由。02シートに前版（令和8年7月27日現在）からの変更点22件と、変更に伴って生じた不整合の対応を示している。</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>80段落 12表</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>46 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>第1稿</t>
+          <t>3シート</t>
         </is>
       </c>
     </row>
@@ -906,32 +906,32 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx</t>
+          <t>第10期計画_キックオフ会議_トークスクリプト_60分.docx</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>トークスクリプトと対で用いる進行者の手元資料。想定される回答ごとの応答、記録すること、決まらなかった場合の着地点。会議運営上の分岐と想定問答。</t>
+          <t>60分のキックオフ会議の進行台本。網掛けの枠がそのまま読み上げる台本で、枠外は進行のための注記。決定4件・確認1件に絞り、残る8項目は書面確認とする。</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>決定ごとに5〜6の分岐を用意している。00シートに時間が押した場合の切り方（優先順位）、07シートに会議資料（更新版）との差の説明を置いている。</t>
+          <t>会議の当日に手元に置く。冒頭で「本日は6件の決定に絞る」合意をとる構成としている。0:05–0:12にキックオフ会議資料（更新版）との差の対照表を置いている。</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>81段落 12表</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>46 KB</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>第1稿</t>
         </is>
       </c>
     </row>
@@ -939,39 +939,39 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
+          <t>トークスクリプトと対で用いる進行者の手元資料。想定される回答ごとの応答、記録すること、決まらなかった場合の着地点。会議運営上の分岐と想定問答。</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
+          <t>決定ごとに5〜6の分岐を用意している。00シートに時間が押した場合の切り方（優先順位）、07シートに会議資料（更新版）との差の説明を置いている。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
     </row>
@@ -986,32 +986,32 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
+          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
+          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>41 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>7シート</t>
         </is>
       </c>
     </row>
@@ -1026,32 +1026,32 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>第1回委員会に向けた確認事項の依頼文書。</t>
+          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
+          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>41 KB</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>第9版</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1059,39 +1059,39 @@
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>第1回委員会に向けた確認事項の依頼文書。</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第9版</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -1139,34 +1139,34 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -1186,27 +1186,27 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -1226,27 +1226,27 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1259,34 +1259,34 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -1306,27 +1306,27 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -1346,27 +1346,27 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1386,27 +1386,27 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1426,27 +1426,27 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -1506,27 +1506,27 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1546,27 +1546,27 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1586,27 +1586,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>95 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1626,27 +1626,27 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>95 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -1666,17 +1666,17 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1706,27 +1706,27 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -1746,27 +1746,27 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章48表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>456段落 48表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1786,27 +1786,27 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章48表39図。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>14シート</t>
+          <t>456段落 48表</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1826,27 +1826,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シート。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>11シート</t>
+          <t>14シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>46 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -1859,39 +1859,39 @@
       <c r="A34" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シート。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>11シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>46 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1906,32 +1906,32 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -1946,27 +1946,27 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -1979,34 +1979,34 @@
       <c r="A37" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2059,39 +2059,39 @@
       <c r="A39" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H39" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2106,27 +2106,27 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H40" s="16" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H41" s="16" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -2226,88 +2226,108 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H43" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="52" customHeight="1">
+      <c r="A44" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H43" s="16" t="inlineStr">
+      <c r="H44" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="17" t="inlineStr">
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr"/>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="3" t="inlineStr"/>
-    </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D47" s="18" t="n"/>
-      <c r="E47" s="18" t="n"/>
-      <c r="F47" s="18" t="n"/>
-      <c r="G47" s="18" t="n"/>
-      <c r="H47" s="19" t="n"/>
-    </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B48" s="6" t="n">
@@ -2315,7 +2335,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D48" s="18" t="n"/>
@@ -2325,17 +2345,17 @@
       <c r="H48" s="19" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D49" s="18" t="n"/>
@@ -2345,17 +2365,17 @@
       <c r="H49" s="19" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D50" s="18" t="n"/>
@@ -2365,17 +2385,17 @@
       <c r="H50" s="19" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合</t>
+          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D51" s="18" t="n"/>
@@ -2385,17 +2405,17 @@
       <c r="H51" s="19" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B52" s="6" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>将来推計_需要3シナリオの感度表、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合</t>
         </is>
       </c>
       <c r="D52" s="18" t="n"/>
@@ -2405,17 +2425,17 @@
       <c r="H52" s="19" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D53" s="18" t="n"/>
@@ -2425,17 +2445,17 @@
       <c r="H53" s="19" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B54" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料（更新版）の校正結果、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D54" s="18" t="n"/>
@@ -2444,18 +2464,18 @@
       <c r="G54" s="18" t="n"/>
       <c r="H54" s="19" t="n"/>
     </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B55" s="20" t="n">
-        <v>39</v>
-      </c>
-      <c r="C55" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの34件、別スコープ5件</t>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D55" s="18" t="n"/>
@@ -2464,8 +2484,28 @@
       <c r="G55" s="18" t="n"/>
       <c r="H55" s="19" t="n"/>
     </row>
-    <row r="57" ht="100" customHeight="1">
-      <c r="A57" s="21" t="inlineStr">
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B56" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="C56" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの35件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="n"/>
+      <c r="E56" s="18" t="n"/>
+      <c r="F56" s="18" t="n"/>
+      <c r="G56" s="18" t="n"/>
+      <c r="H56" s="19" t="n"/>
+    </row>
+    <row r="58" ht="100" customHeight="1">
+      <c r="A58" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2474,17 +2514,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C51:H51"/>
-    <mergeCell ref="C47:H47"/>
+    <mergeCell ref="C56:H56"/>
     <mergeCell ref="C54:H54"/>
     <mergeCell ref="C55:H55"/>
     <mergeCell ref="C50:H50"/>
-    <mergeCell ref="A57:H57"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C52:H52"/>
     <mergeCell ref="C53:H53"/>
     <mergeCell ref="C49:H49"/>
     <mergeCell ref="C48:H48"/>
-    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A58:H58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -866,32 +866,32 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料（更新版）の校正結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料（更新版）_校正反映.docx</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>発注者ご作成のキックオフ会議資料（更新版・令和8年8月6日現在）の校正結果。誤字脱字4件、事業所調査の修正漏れ9件、調査の状況が古いもの3件、記載の不足・不整合4件、表記の統一5件、ご確認事項5件の計30件。</t>
+          <t>発注者ご作成のキックオフ会議資料（更新版）に、校正結果30件と令和8年8月6日のご指示を反映した版。原本の書式を保つため、python-docxにより文字列を置換している。</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>01シートに箇所・現在の記載・修正案・理由。02シートに前版（令和8年7月27日現在）からの変更点22件と、変更に伴って生じた不整合の対応を示している。</t>
+          <t>事業所実態調査を実施済みとして記載を統一し、誤字4件・不整合・表記を修正した。受領した事業所票に含まれない項目（欠員・受入困難・ICT・BCP）は、受領内容に合わせて書き改めている。</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>117段落 14表</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>60 KB</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>校正反映版</t>
         </is>
       </c>
     </row>
@@ -906,32 +906,32 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議_トークスクリプト_60分.docx</t>
+          <t>第10期計画_キックオフ会議資料（更新版）の校正結果.xlsx</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>60分のキックオフ会議の進行台本。網掛けの枠がそのまま読み上げる台本で、枠外は進行のための注記。決定4件・確認1件に絞り、残る8項目は書面確認とする。</t>
+          <t>発注者ご作成のキックオフ会議資料（更新版・令和8年8月6日現在）の校正結果。誤字脱字4件、事業所調査の修正漏れ9件、調査の状況が古いもの3件、記載の不足・不整合4件、表記の統一5件、ご確認事項5件の計30件。</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>会議の当日に手元に置く。冒頭で「本日は6件の決定に絞る」合意をとる構成としている。0:05–0:12にキックオフ会議資料（更新版）との差の対照表を置いている。</t>
+          <t>01シートに箇所・現在の記載・修正案・理由。02シートに前版（令和8年7月27日現在）からの変更点22件と、変更に伴って生じた不整合の対応を示している。</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>81段落 12表</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>46 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>第1稿</t>
+          <t>3シート</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx</t>
+          <t>第10期計画_キックオフ会議_トークスクリプト_60分.docx</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>トークスクリプトと対で用いる進行者の手元資料。想定される回答ごとの応答、記録すること、決まらなかった場合の着地点。会議運営上の分岐と想定問答。</t>
+          <t>60分のキックオフ会議の進行台本。網掛けの枠がそのまま読み上げる台本で、枠外は進行のための注記。決定4件・確認1件に絞り、残る8項目は書面確認とする。</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>決定ごとに5〜6の分岐を用意している。00シートに時間が押した場合の切り方（優先順位）、07シートに会議資料（更新版）との差の説明を置いている。</t>
+          <t>会議の当日に手元に置く。冒頭で「本日は6件の決定に絞る」合意をとる構成としている。0:05–0:12にキックオフ会議資料（更新版）との差の対照表を置いている。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>81段落 12表</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>47 KB</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>第1稿</t>
         </is>
       </c>
     </row>
@@ -979,39 +979,39 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
+          <t>トークスクリプトと対で用いる進行者の手元資料。想定される回答ごとの応答、記録すること、決まらなかった場合の着地点。会議運営上の分岐と想定問答。</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
+          <t>決定ごとに5〜6の分岐を用意している。00シートに時間が押した場合の切り方（優先順位）、07シートに会議資料（更新版）との差の説明を置いている。</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
     </row>
@@ -1026,32 +1026,32 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
+          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
+          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>41 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>7シート</t>
         </is>
       </c>
     </row>
@@ -1066,32 +1066,32 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>第1回委員会に向けた確認事項の依頼文書。</t>
+          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
+          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>41 KB</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>第9版</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1099,39 +1099,39 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>第1回委員会に向けた確認事項の依頼文書。</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第9版</t>
         </is>
       </c>
     </row>
@@ -1146,27 +1146,27 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -1179,34 +1179,34 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -1226,27 +1226,27 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1266,27 +1266,27 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -1299,34 +1299,34 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -1346,27 +1346,27 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1386,27 +1386,27 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1426,27 +1426,27 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -1506,27 +1506,27 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1546,27 +1546,27 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1586,27 +1586,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1626,27 +1626,27 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>95 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -1666,27 +1666,27 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>95 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1706,17 +1706,17 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1746,27 +1746,27 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1786,27 +1786,27 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章48表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>456段落 48表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1826,27 +1826,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章48表39図。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>14シート</t>
+          <t>456段落 48表</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シート。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>11シート</t>
+          <t>14シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>46 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -1899,39 +1899,39 @@
       <c r="A35" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シート。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>11シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>46 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1946,32 +1946,32 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -1986,27 +1986,27 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2019,34 +2019,34 @@
       <c r="A38" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2099,39 +2099,39 @@
       <c r="A40" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H40" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2146,27 +2146,27 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H41" s="16" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H42" s="16" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -2266,88 +2266,108 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H44" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="52" customHeight="1">
+      <c r="A45" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H44" s="16" t="inlineStr">
+      <c r="H45" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="17" t="inlineStr">
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="3" t="inlineStr"/>
-      <c r="H47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D48" s="18" t="n"/>
-      <c r="E48" s="18" t="n"/>
-      <c r="F48" s="18" t="n"/>
-      <c r="G48" s="18" t="n"/>
-      <c r="H48" s="19" t="n"/>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B49" s="6" t="n">
@@ -2355,7 +2375,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D49" s="18" t="n"/>
@@ -2365,17 +2385,17 @@
       <c r="H49" s="19" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D50" s="18" t="n"/>
@@ -2385,17 +2405,17 @@
       <c r="H50" s="19" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
-      <c r="A51" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D51" s="18" t="n"/>
@@ -2405,17 +2425,17 @@
       <c r="H51" s="19" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B52" s="6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合</t>
+          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D52" s="18" t="n"/>
@@ -2425,17 +2445,17 @@
       <c r="H52" s="19" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>将来推計_需要3シナリオの感度表、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合</t>
         </is>
       </c>
       <c r="D53" s="18" t="n"/>
@@ -2445,17 +2465,17 @@
       <c r="H53" s="19" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B54" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の校正結果、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D54" s="18" t="n"/>
@@ -2465,17 +2485,17 @@
       <c r="H54" s="19" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D55" s="18" t="n"/>
@@ -2484,18 +2504,18 @@
       <c r="G55" s="18" t="n"/>
       <c r="H55" s="19" t="n"/>
     </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B56" s="20" t="n">
-        <v>40</v>
-      </c>
-      <c r="C56" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの35件、別スコープ5件</t>
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D56" s="18" t="n"/>
@@ -2504,8 +2524,28 @@
       <c r="G56" s="18" t="n"/>
       <c r="H56" s="19" t="n"/>
     </row>
-    <row r="58" ht="100" customHeight="1">
-      <c r="A58" s="21" t="inlineStr">
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="n">
+        <v>41</v>
+      </c>
+      <c r="C57" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの36件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D57" s="18" t="n"/>
+      <c r="E57" s="18" t="n"/>
+      <c r="F57" s="18" t="n"/>
+      <c r="G57" s="18" t="n"/>
+      <c r="H57" s="19" t="n"/>
+    </row>
+    <row r="59" ht="100" customHeight="1">
+      <c r="A59" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2514,17 +2554,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C51:H51"/>
-    <mergeCell ref="C56:H56"/>
     <mergeCell ref="C54:H54"/>
+    <mergeCell ref="C57:H57"/>
     <mergeCell ref="C55:H55"/>
     <mergeCell ref="C50:H50"/>
+    <mergeCell ref="A59:H59"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C52:H52"/>
     <mergeCell ref="C53:H53"/>
     <mergeCell ref="C49:H49"/>
-    <mergeCell ref="C48:H48"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="C56:H56"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>456段落 48表</t>
+          <t>458段落 48表</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>46 KB</t>
+          <t>48 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>458段落 48表</t>
+          <t>464段落 49表</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>11シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>48 KB</t>
+          <t>51 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章48表39図。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章50表39図。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>464段落 49表</t>
+          <t>468段落 50表</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>51 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>95 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>468段落 50表</t>
+          <t>469段落 50表</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章50表39図。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>469段落 50表</t>
+          <t>474段落 51表</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>56 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>474段落 51表</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>56 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シート。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1939,39 +1939,39 @@
       <c r="A36" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1986,32 +1986,32 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -2026,27 +2026,27 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2059,34 +2059,34 @@
       <c r="A39" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2106,17 +2106,17 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2139,39 +2139,39 @@
       <c r="A41" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H41" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2186,27 +2186,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H42" s="16" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H43" s="16" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -2306,88 +2306,108 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H45" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="52" customHeight="1">
+      <c r="A46" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H45" s="16" t="inlineStr">
+      <c r="H46" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="17" t="inlineStr">
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr"/>
-      <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="3" t="inlineStr"/>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D49" s="18" t="n"/>
-      <c r="E49" s="18" t="n"/>
-      <c r="F49" s="18" t="n"/>
-      <c r="G49" s="18" t="n"/>
-      <c r="H49" s="19" t="n"/>
-    </row>
-    <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B50" s="6" t="n">
@@ -2395,7 +2415,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D50" s="18" t="n"/>
@@ -2405,17 +2425,17 @@
       <c r="H50" s="19" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
-      <c r="A51" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D51" s="18" t="n"/>
@@ -2425,17 +2445,17 @@
       <c r="H51" s="19" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B52" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D52" s="18" t="n"/>
@@ -2445,17 +2465,17 @@
       <c r="H52" s="19" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合</t>
+          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D53" s="18" t="n"/>
@@ -2465,17 +2485,17 @@
       <c r="H53" s="19" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B54" s="6" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>将来推計_需要3シナリオの感度表、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D54" s="18" t="n"/>
@@ -2485,17 +2505,17 @@
       <c r="H54" s="19" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D55" s="18" t="n"/>
@@ -2505,17 +2525,17 @@
       <c r="H55" s="19" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B56" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D56" s="18" t="n"/>
@@ -2524,18 +2544,18 @@
       <c r="G56" s="18" t="n"/>
       <c r="H56" s="19" t="n"/>
     </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B57" s="20" t="n">
-        <v>41</v>
-      </c>
-      <c r="C57" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの36件、別スコープ5件</t>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D57" s="18" t="n"/>
@@ -2544,8 +2564,28 @@
       <c r="G57" s="18" t="n"/>
       <c r="H57" s="19" t="n"/>
     </row>
-    <row r="59" ht="100" customHeight="1">
-      <c r="A59" s="21" t="inlineStr">
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B58" s="20" t="n">
+        <v>42</v>
+      </c>
+      <c r="C58" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの37件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="n"/>
+      <c r="E58" s="18" t="n"/>
+      <c r="F58" s="18" t="n"/>
+      <c r="G58" s="18" t="n"/>
+      <c r="H58" s="19" t="n"/>
+    </row>
+    <row r="60" ht="100" customHeight="1">
+      <c r="A60" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2554,16 +2594,16 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C51:H51"/>
+    <mergeCell ref="A48:H48"/>
     <mergeCell ref="C54:H54"/>
     <mergeCell ref="C57:H57"/>
     <mergeCell ref="C55:H55"/>
     <mergeCell ref="C50:H50"/>
-    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="C58:H58"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C52:H52"/>
     <mergeCell ref="C53:H53"/>
-    <mergeCell ref="C49:H49"/>
-    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A60:H60"/>
     <mergeCell ref="C56:H56"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -946,32 +946,32 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議_トークスクリプト_60分.docx</t>
+          <t>第10期計画_キックオフ会議議事録の校正結果.xlsx</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>60分のキックオフ会議の進行台本。網掛けの枠がそのまま読み上げる台本で、枠外は進行のための注記。決定4件・確認1件に絞り、残る8項目は書面確認とする。</t>
+          <t>発注者ご作成のキックオフ会議議事録（令和8年8月6日開催）の校正結果25件。誤字脱字・表記の誤り10件を反映し、文体・呼称等の提案9件、実質の論点6件を掲げている。</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>会議の当日に手元に置く。冒頭で「本日は6件の決定に絞る」合意をとる構成としている。0:05–0:12にキックオフ会議資料（更新版）との差の対照表を置いている。</t>
+          <t>反映済みの版は第10期計画_キックオフ会議議事録_校正反映.odt。要協議6件には、人口推計に総合戦略の目標値を用いる方針が3町一律には成立しないこと、代表KPI4項目（H07・H08・H12・H16）が現在のデータでは算定できないことを含む。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>81段落 12表</t>
+          <t>1シート</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>47 KB</t>
+          <t>10 KB</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>第1稿</t>
+          <t>1シート</t>
         </is>
       </c>
     </row>
@@ -986,32 +986,32 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx</t>
+          <t>第10期計画_キックオフ会議議事録_校正反映.odt</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>トークスクリプトと対で用いる進行者の手元資料。想定される回答ごとの応答、記録すること、決まらなかった場合の着地点。会議運営上の分岐と想定問答。</t>
+          <t>上記の校正結果のうち、誤字脱字及び明らかな表記の誤り10件を反映した議事録。原本の書式は変えていない。</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>決定ごとに5〜6の分岐を用意している。00シートに時間が押した場合の切り方（優先順位）、07シートに会議資料（更新版）との差の説明を置いている。</t>
+          <t>「保険慮→保険料」「居宅変更実態調査→居所変更実態調査」「大雪広域連合→大雪地区広域連合」「第10計画→第10期計画」等。介護予防・日常生活圏域ニーズ調査と健康とくらしの調査が同一の調査であることによる重複の記載も整理した。</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>ODF形式</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>19 KB</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>ODF形式</t>
         </is>
       </c>
     </row>
@@ -1019,39 +1019,39 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_キックオフ会議_トークスクリプト_60分.docx</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
+          <t>60分のキックオフ会議の進行台本。網掛けの枠がそのまま読み上げる台本で、枠外は進行のための注記。決定4件・確認1件に絞り、残る8項目は書面確認とする。</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
+          <t>会議の当日に手元に置く。冒頭で「本日は6件の決定に絞る」合意をとる構成としている。0:05–0:12にキックオフ会議資料（更新版）との差の対照表を置いている。</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>81段落 12表</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>47 KB</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>第1稿</t>
         </is>
       </c>
     </row>
@@ -1059,39 +1059,39 @@
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
+          <t>トークスクリプトと対で用いる進行者の手元資料。想定される回答ごとの応答、記録すること、決まらなかった場合の着地点。会議運営上の分岐と想定問答。</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
+          <t>決定ごとに5〜6の分岐を用意している。00シートに時間が押した場合の切り方（優先順位）、07シートに会議資料（更新版）との差の説明を置いている。</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>35 KB</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
           <t>8シート</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>41 KB</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1106,32 +1106,32 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>第1回委員会に向けた確認事項の依頼文書。</t>
+          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
+          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>第9版</t>
+          <t>7シート</t>
         </is>
       </c>
     </row>
@@ -1139,34 +1139,34 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>41 KB</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -1179,39 +1179,39 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>第1回委員会に向けた確認事項の依頼文書。</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第9版</t>
         </is>
       </c>
     </row>
@@ -1219,34 +1219,34 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1259,34 +1259,34 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -1306,27 +1306,27 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -1339,34 +1339,34 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1379,34 +1379,34 @@
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1426,27 +1426,27 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -1506,27 +1506,27 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1586,27 +1586,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1626,27 +1626,27 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -1666,27 +1666,27 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1706,27 +1706,27 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -1746,27 +1746,27 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1786,27 +1786,27 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1826,27 +1826,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>14シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -1906,27 +1906,27 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -1946,27 +1946,27 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>14シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -1979,39 +1979,39 @@
       <c r="A37" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2019,34 +2019,34 @@
       <c r="A38" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2066,32 +2066,32 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -2099,34 +2099,34 @@
       <c r="A40" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2139,34 +2139,34 @@
       <c r="A41" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2179,39 +2179,39 @@
       <c r="A42" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H42" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>18 KB</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2219,39 +2219,39 @@
       <c r="A43" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
-        </is>
-      </c>
-      <c r="H43" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2266,27 +2266,27 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H44" s="16" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H45" s="16" t="inlineStr">
@@ -2346,116 +2346,156 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H46" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="52" customHeight="1">
+      <c r="A47" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H47" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="52" customHeight="1">
+      <c r="A48" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H46" s="16" t="inlineStr">
+      <c r="H48" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="17" t="inlineStr">
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr"/>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
         </is>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B52" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D50" s="18" t="n"/>
-      <c r="E50" s="18" t="n"/>
-      <c r="F50" s="18" t="n"/>
-      <c r="G50" s="18" t="n"/>
-      <c r="H50" s="19" t="n"/>
-    </row>
-    <row r="51" ht="32" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
-        </is>
-      </c>
-      <c r="D51" s="18" t="n"/>
-      <c r="E51" s="18" t="n"/>
-      <c r="F51" s="18" t="n"/>
-      <c r="G51" s="18" t="n"/>
-      <c r="H51" s="19" t="n"/>
-    </row>
-    <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D52" s="18" t="n"/>
@@ -2465,9 +2505,9 @@
       <c r="H52" s="19" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B53" s="6" t="n">
@@ -2475,7 +2515,7 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D53" s="18" t="n"/>
@@ -2485,17 +2525,17 @@
       <c r="H53" s="19" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B54" s="6" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D54" s="18" t="n"/>
@@ -2505,17 +2545,17 @@
       <c r="H54" s="19" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D55" s="18" t="n"/>
@@ -2525,17 +2565,17 @@
       <c r="H55" s="19" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B56" s="6" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>将来推計_需要3シナリオの感度表、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D56" s="18" t="n"/>
@@ -2545,17 +2585,17 @@
       <c r="H56" s="19" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D57" s="18" t="n"/>
@@ -2564,18 +2604,18 @@
       <c r="G57" s="18" t="n"/>
       <c r="H57" s="19" t="n"/>
     </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B58" s="20" t="n">
-        <v>42</v>
-      </c>
-      <c r="C58" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの37件、別スコープ5件</t>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D58" s="18" t="n"/>
@@ -2584,8 +2624,48 @@
       <c r="G58" s="18" t="n"/>
       <c r="H58" s="19" t="n"/>
     </row>
-    <row r="60" ht="100" customHeight="1">
-      <c r="A60" s="21" t="inlineStr">
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+        </is>
+      </c>
+      <c r="D59" s="18" t="n"/>
+      <c r="E59" s="18" t="n"/>
+      <c r="F59" s="18" t="n"/>
+      <c r="G59" s="18" t="n"/>
+      <c r="H59" s="19" t="n"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B60" s="20" t="n">
+        <v>44</v>
+      </c>
+      <c r="C60" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの39件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="n"/>
+      <c r="E60" s="18" t="n"/>
+      <c r="F60" s="18" t="n"/>
+      <c r="G60" s="18" t="n"/>
+      <c r="H60" s="19" t="n"/>
+    </row>
+    <row r="62" ht="100" customHeight="1">
+      <c r="A62" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2593,18 +2673,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C51:H51"/>
-    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A62:H62"/>
     <mergeCell ref="C54:H54"/>
     <mergeCell ref="C57:H57"/>
     <mergeCell ref="C55:H55"/>
-    <mergeCell ref="C50:H50"/>
     <mergeCell ref="C58:H58"/>
+    <mergeCell ref="C60:H60"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C52:H52"/>
     <mergeCell ref="C53:H53"/>
-    <mergeCell ref="A60:H60"/>
     <mergeCell ref="C56:H56"/>
+    <mergeCell ref="C59:H59"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -951,12 +951,12 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>発注者ご作成のキックオフ会議議事録（令和8年8月6日開催）の校正結果25件。誤字脱字・表記の誤り10件を反映し、文体・呼称等の提案9件、実質の論点6件を掲げている。</t>
+          <t>発注者ご作成のキックオフ会議議事録（令和8年8月6日開催）の校正結果35件。誤字脱字・表記の誤り及び令和8年8月6日のご指示による修正26件を反映し、見送り・要確認3件と、ご指示への回答6件を掲げている。</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>反映済みの版は第10期計画_キックオフ会議議事録_校正反映.odt。要協議6件には、人口推計に総合戦略の目標値を用いる方針が3町一律には成立しないこと、代表KPI4項目（H07・H08・H12・H16）が現在のデータでは算定できないことを含む。</t>
+          <t>反映済みの版は第10期計画_キックオフ会議議事録_校正反映.odt。ご指示への回答6件には、人口推計を総合戦略ベースの補正とすること、乖離の確認を65歳以上・75歳以上で行うこと、「令和8年実績」を年報・月報に改めること、農業収入と基金取崩しの因果を切り離すこと、算定できない代表KPI4項目（H07・H08・H12・H16）の扱い、事業所実態調査が受領済みであることを含む。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>10 KB</t>
+          <t>12 KB</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>上記の校正結果のうち、誤字脱字及び明らかな表記の誤り10件を反映した議事録。原本の書式は変えていない。</t>
+          <t>上記の校正結果のうち26件を反映した議事録。原本の書式は変えていない。</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>「保険慮→保険料」「居宅変更実態調査→居所変更実態調査」「大雪広域連合→大雪地区広域連合」「第10計画→第10期計画」等。介護予防・日常生活圏域ニーズ調査と健康とくらしの調査が同一の調査であることによる重複の記載も整理した。</t>
+          <t>「保険慮→保険料」「居宅変更実態調査→居所変更実態調査」「大雪広域連合→大雪地区広域連合」「第10計画→第10期計画」等の誤字脱字に加え、介護予防・日常生活圏域ニーズ調査と健康とくらしの調査が同一の調査であることによる重複の記載を整理し、「令和8年実績」を「年報・月報の実績」に、会議体の呼称を「協議会」に統一した。「福祉の中でも上位に位置する計画」はご指示により原本のままである。</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1099,39 +1099,39 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_3町ヒアリング資料.docx</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
+          <t>構成3町へのヒアリングに用いる説明資料。現在の試算（人口・認定者数・サービス見込量・保険料）、人口推計を総合戦略ベースに補正する考え方、町別の現在地と論点、ご提供をお願いする資料7件、お伺いしたいこと6区分。</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
+          <t>キックオフ会議のご指示（人口推計は3町の地方創生総合戦略の人口推計をベースに補正）を受けた資料。第3節に補正の4段階と、総人口の乖離が給付費に直結しないこと（総人口は住基が622人多いが65歳以上は144人・75歳以上は256人少ない）を示している。第4節に3町の現在地13項目の対照表。</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>128段落 10表</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>49 KB</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>第1稿</t>
         </is>
       </c>
     </row>
@@ -1139,39 +1139,39 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
+          <t>代表KPI16項目をすべて明示し、算定できない4項目（H07・H08・H12・H16）の代理指標への振替案を示す。あわせて方針の決定19件・資料の提供13件・調査の点検事項35件の現在地を精査する。</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
+          <t>キックオフ会議の確認事項③への回答。4項目とも削除せずに算定できる見込みであり、H07は健康とくらしの調査で3.4％、H08は同8.7％、H12は在宅生活改善調査の新規提案で20.4％、H16は業務継続計画未策定減算の算定状況による。05シートに3町ヒアリングで確認することを町別に整理している。</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>41 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第1稿</t>
         </is>
       </c>
     </row>
@@ -1186,32 +1186,32 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>第1回委員会に向けた確認事項の依頼文書。</t>
+          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
+          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>第9版</t>
+          <t>7シート</t>
         </is>
       </c>
     </row>
@@ -1219,34 +1219,34 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>41 KB</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1259,39 +1259,39 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>第1回委員会に向けた確認事項の依頼文書。</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第9版</t>
         </is>
       </c>
     </row>
@@ -1299,34 +1299,34 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -1339,34 +1339,34 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1386,27 +1386,27 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1419,34 +1419,34 @@
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1459,34 +1459,34 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -1506,27 +1506,27 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1546,27 +1546,27 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1586,27 +1586,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1626,17 +1626,17 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -1666,27 +1666,27 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1706,27 +1706,27 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -1746,27 +1746,27 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1786,27 +1786,27 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1826,27 +1826,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -1906,27 +1906,27 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -1946,27 +1946,27 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>14シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -1986,27 +1986,27 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2026,27 +2026,27 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>14シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2059,39 +2059,39 @@
       <c r="A39" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2099,34 +2099,34 @@
       <c r="A40" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2146,32 +2146,32 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -2179,34 +2179,34 @@
       <c r="A42" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2219,34 +2219,34 @@
       <c r="A43" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2259,39 +2259,39 @@
       <c r="A44" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H44" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>18 KB</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2299,39 +2299,39 @@
       <c r="A45" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
-        </is>
-      </c>
-      <c r="H45" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2346,27 +2346,27 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H46" s="16" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H47" s="16" t="inlineStr">
@@ -2426,116 +2426,156 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H48" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="52" customHeight="1">
+      <c r="A49" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H49" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="52" customHeight="1">
+      <c r="A50" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H48" s="16" t="inlineStr">
+      <c r="H50" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="17" t="inlineStr">
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr"/>
-      <c r="G51" s="3" t="inlineStr"/>
-      <c r="H51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
         </is>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B54" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D52" s="18" t="n"/>
-      <c r="E52" s="18" t="n"/>
-      <c r="F52" s="18" t="n"/>
-      <c r="G52" s="18" t="n"/>
-      <c r="H52" s="19" t="n"/>
-    </row>
-    <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
-        </is>
-      </c>
-      <c r="D53" s="18" t="n"/>
-      <c r="E53" s="18" t="n"/>
-      <c r="F53" s="18" t="n"/>
-      <c r="G53" s="18" t="n"/>
-      <c r="H53" s="19" t="n"/>
-    </row>
-    <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D54" s="18" t="n"/>
@@ -2545,9 +2585,9 @@
       <c r="H54" s="19" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
@@ -2555,7 +2595,7 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D55" s="18" t="n"/>
@@ -2565,17 +2605,17 @@
       <c r="H55" s="19" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B56" s="6" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D56" s="18" t="n"/>
@@ -2585,17 +2625,17 @@
       <c r="H56" s="19" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D57" s="18" t="n"/>
@@ -2605,17 +2645,17 @@
       <c r="H57" s="19" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B58" s="6" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>将来推計_需要3シナリオの感度表、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D58" s="18" t="n"/>
@@ -2625,17 +2665,17 @@
       <c r="H58" s="19" t="n"/>
     </row>
     <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D59" s="18" t="n"/>
@@ -2644,18 +2684,18 @@
       <c r="G59" s="18" t="n"/>
       <c r="H59" s="19" t="n"/>
     </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B60" s="20" t="n">
-        <v>44</v>
-      </c>
-      <c r="C60" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの39件、別スコープ5件</t>
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D60" s="18" t="n"/>
@@ -2664,8 +2704,48 @@
       <c r="G60" s="18" t="n"/>
       <c r="H60" s="19" t="n"/>
     </row>
-    <row r="62" ht="100" customHeight="1">
-      <c r="A62" s="21" t="inlineStr">
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+        </is>
+      </c>
+      <c r="D61" s="18" t="n"/>
+      <c r="E61" s="18" t="n"/>
+      <c r="F61" s="18" t="n"/>
+      <c r="G61" s="18" t="n"/>
+      <c r="H61" s="19" t="n"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B62" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="C62" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの41件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="n"/>
+      <c r="E62" s="18" t="n"/>
+      <c r="F62" s="18" t="n"/>
+      <c r="G62" s="18" t="n"/>
+      <c r="H62" s="19" t="n"/>
+    </row>
+    <row r="64" ht="100" customHeight="1">
+      <c r="A64" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2673,16 +2753,16 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="C62:H62"/>
     <mergeCell ref="C54:H54"/>
     <mergeCell ref="C57:H57"/>
     <mergeCell ref="C55:H55"/>
     <mergeCell ref="C58:H58"/>
     <mergeCell ref="C60:H60"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C52:H52"/>
-    <mergeCell ref="C53:H53"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="C61:H61"/>
     <mergeCell ref="C56:H56"/>
     <mergeCell ref="C59:H59"/>
   </mergeCells>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -93,6 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F2DCDB"/>
+        <bgColor rgb="00F2DCDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
       </patternFill>
@@ -101,12 +107,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00DEEBF7"/>
         <bgColor rgb="00DEEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2DCDB"/>
-        <bgColor rgb="00F2DCDB"/>
       </patternFill>
     </fill>
     <fill>
@@ -255,7 +255,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1181,22 +1181,22 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>発注者への依頼</t>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
+          <t>第9期計画 第5章の19施策を洗い出し、実施済み4調査の設問及び代表KPI16項目と紐付けたうえで、レッドチーム方式（自らの整理を否定する立場）で点検した。</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
+          <t>代表KPIが対応しない施策が9施策（47.4％）、調査の裏づけがない施策が6施策（31.6％）、いずれもない施策が5施策（26.3％）である。05シートに、調査で強い所見があるのに施策がない5領域（移動・経済・意思決定支援・身寄りのない高齢者・未利用認定者）と、評価できない5施策の扱いを示している。04シートのレッドチームレビュー12件には、本表の枠組みそのものへの指摘2件を含む。</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>36 KB</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>第1稿</t>
         </is>
       </c>
     </row>
@@ -1219,39 +1219,39 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
+          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
+          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>41 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>7シート</t>
         </is>
       </c>
     </row>
@@ -1259,39 +1259,39 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>第1回委員会に向けた確認事項の依頼文書。</t>
+          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
+          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>41 KB</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>第9版</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1301,37 +1301,37 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>工程管理</t>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>第1回委員会に向けた確認事項の依頼文書。</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第9版</t>
         </is>
       </c>
     </row>
@@ -1339,34 +1339,34 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>工程管理</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1381,32 +1381,32 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>第9期の評価</t>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1419,34 +1419,34 @@
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>第9期の評価</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1459,34 +1459,34 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>第9期の評価</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -1499,34 +1499,34 @@
       <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1546,27 +1546,27 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1586,27 +1586,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1626,27 +1626,27 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -1666,27 +1666,27 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1706,27 +1706,27 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -1746,27 +1746,27 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1786,27 +1786,27 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1826,27 +1826,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -1906,17 +1906,17 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1946,27 +1946,27 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -1986,27 +1986,27 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2026,27 +2026,27 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>14シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2066,22 +2066,22 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>14シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -2106,27 +2106,27 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2139,39 +2139,39 @@
       <c r="A41" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2186,32 +2186,32 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -2226,27 +2226,27 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2259,34 +2259,34 @@
       <c r="A44" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2339,39 +2339,39 @@
       <c r="A46" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H46" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2386,27 +2386,27 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H47" s="16" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H48" s="16" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -2506,88 +2506,108 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H50" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="52" customHeight="1">
+      <c r="A51" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G50" s="7" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H50" s="16" t="inlineStr">
+      <c r="H51" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="17" t="inlineStr">
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr"/>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr"/>
+      <c r="E54" s="3" t="inlineStr"/>
+      <c r="F54" s="3" t="inlineStr"/>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D54" s="18" t="n"/>
-      <c r="E54" s="18" t="n"/>
-      <c r="F54" s="18" t="n"/>
-      <c r="G54" s="18" t="n"/>
-      <c r="H54" s="19" t="n"/>
-    </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
@@ -2595,7 +2615,7 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D55" s="18" t="n"/>
@@ -2607,15 +2627,15 @@
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>工程管理</t>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B56" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D56" s="18" t="n"/>
@@ -2627,15 +2647,15 @@
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>第9期の評価</t>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D57" s="18" t="n"/>
@@ -2645,17 +2665,17 @@
       <c r="H57" s="19" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B58" s="6" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D58" s="18" t="n"/>
@@ -2665,17 +2685,17 @@
       <c r="H58" s="19" t="n"/>
     </row>
     <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>将来推計_需要3シナリオの感度表、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D59" s="18" t="n"/>
@@ -2685,17 +2705,17 @@
       <c r="H59" s="19" t="n"/>
     </row>
     <row r="60" ht="32" customHeight="1">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B60" s="6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D60" s="18" t="n"/>
@@ -2705,17 +2725,17 @@
       <c r="H60" s="19" t="n"/>
     </row>
     <row r="61" ht="32" customHeight="1">
-      <c r="A61" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D61" s="18" t="n"/>
@@ -2724,18 +2744,18 @@
       <c r="G61" s="18" t="n"/>
       <c r="H61" s="19" t="n"/>
     </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B62" s="20" t="n">
-        <v>46</v>
-      </c>
-      <c r="C62" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの41件、別スコープ5件</t>
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D62" s="18" t="n"/>
@@ -2744,8 +2764,28 @@
       <c r="G62" s="18" t="n"/>
       <c r="H62" s="19" t="n"/>
     </row>
-    <row r="64" ht="100" customHeight="1">
-      <c r="A64" s="21" t="inlineStr">
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B63" s="20" t="n">
+        <v>47</v>
+      </c>
+      <c r="C63" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの42件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D63" s="18" t="n"/>
+      <c r="E63" s="18" t="n"/>
+      <c r="F63" s="18" t="n"/>
+      <c r="G63" s="18" t="n"/>
+      <c r="H63" s="19" t="n"/>
+    </row>
+    <row r="65" ht="100" customHeight="1">
+      <c r="A65" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2753,15 +2793,15 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C63:H63"/>
     <mergeCell ref="C62:H62"/>
-    <mergeCell ref="C54:H54"/>
     <mergeCell ref="C57:H57"/>
+    <mergeCell ref="A53:H53"/>
     <mergeCell ref="C55:H55"/>
     <mergeCell ref="C58:H58"/>
     <mergeCell ref="C60:H60"/>
+    <mergeCell ref="A65:H65"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A64:H64"/>
     <mergeCell ref="C61:H61"/>
     <mergeCell ref="C56:H56"/>
     <mergeCell ref="C59:H59"/>
@@ -3417,7 +3457,7 @@
           <t>圏域を統計単位と整備単位に分ける案。訪問・通所困難地域の定義。自給率の3町間の差が3町単位を裏付ける。</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>事業所の実施地域の受領待ち</t>
         </is>
@@ -3439,7 +3479,7 @@
           <t>特定地域の指定基準の判定。3町のうち美瑛町が該当の見込み。</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>告示待ち</t>
         </is>
@@ -3549,7 +3589,7 @@
           <t>令和22年度・令和32年度の人口と認定者数。</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>給付費は第3段階待ち</t>
         </is>
@@ -3571,7 +3611,7 @@
           <t>代表KPIの3軸評価。交付金評価。長期でみた到達点。</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>事業実績の受領待ち（プロセス評価）</t>
         </is>
@@ -3593,7 +3633,7 @@
           <t>代表KPI16項目のデータ源と基準値。</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>3調査の第10期分の受領待ち</t>
         </is>
@@ -3615,7 +3655,7 @@
           <t>5基本目標の5層構成。アウトプットとアウトカムの分離。</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>事業実績の受領待ち</t>
         </is>
@@ -3637,7 +3677,7 @@
           <t>階級別人口×階級別認定率。3シナリオ。</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>シナリオの決定待ち</t>
         </is>
@@ -3659,7 +3699,7 @@
           <t>要介護度別の利用率と単価により算定する。</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>要介護度別認定者数と給付実績の受領待ち</t>
         </is>
@@ -3681,7 +3721,7 @@
           <t>24時間対応サービスの確保方策。区域外の施設への依存。</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>定員・稼働の実績の受領待ち</t>
         </is>
@@ -3703,7 +3743,7 @@
           <t>第9期の剰余の確定。管内比較。16段階の妥当性。</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>決算・基金と政令改正待ち</t>
         </is>
@@ -3725,7 +3765,7 @@
           <t>基本指針の新別表11事項への対応表。図表番号一覧。</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>告示待ち</t>
         </is>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1219,24 +1219,24 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
+          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の受け皿、判定ルールとレッドチームレビュー。</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
+          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率で、75歳以上は社人研が年0.39ポイント速く、3年で1.15％の下方補正となる。影響は認定者22人（1.1％）・保険料月額22円にとどまる。町別は住民基本台帳の年齢5歳階級別（町別・年次）の受領後に確定する。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>第1稿</t>
         </is>
       </c>
     </row>
@@ -1266,32 +1266,32 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
+          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
+          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>41 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>7シート</t>
         </is>
       </c>
     </row>
@@ -1306,32 +1306,32 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>第1回委員会に向けた確認事項の依頼文書。</t>
+          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
+          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>41 KB</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>第9版</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1339,39 +1339,39 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>第1回委員会に向けた確認事項の依頼文書。</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第9版</t>
         </is>
       </c>
     </row>
@@ -1386,27 +1386,27 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1419,34 +1419,34 @@
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -1506,27 +1506,27 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1539,34 +1539,34 @@
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1586,27 +1586,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1626,27 +1626,27 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -1666,27 +1666,27 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1706,27 +1706,27 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -1746,27 +1746,27 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1786,27 +1786,27 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1826,27 +1826,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -1906,27 +1906,27 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -1986,27 +1986,27 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2026,27 +2026,27 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2066,27 +2066,27 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>14シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2106,22 +2106,22 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>14シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -2146,27 +2146,27 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2179,39 +2179,39 @@
       <c r="A42" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2226,32 +2226,32 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -2266,27 +2266,27 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2299,34 +2299,34 @@
       <c r="A45" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2346,17 +2346,17 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2379,39 +2379,39 @@
       <c r="A47" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H47" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H48" s="16" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H49" s="16" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -2546,88 +2546,108 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H51" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="52" customHeight="1">
+      <c r="A52" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H51" s="16" t="inlineStr">
+      <c r="H52" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="17" t="inlineStr">
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr"/>
-      <c r="E54" s="3" t="inlineStr"/>
-      <c r="F54" s="3" t="inlineStr"/>
-      <c r="G54" s="3" t="inlineStr"/>
-      <c r="H54" s="3" t="inlineStr"/>
-    </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr"/>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D55" s="18" t="n"/>
-      <c r="E55" s="18" t="n"/>
-      <c r="F55" s="18" t="n"/>
-      <c r="G55" s="18" t="n"/>
-      <c r="H55" s="19" t="n"/>
-    </row>
-    <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="12" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B56" s="6" t="n">
@@ -2635,7 +2655,7 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D56" s="18" t="n"/>
@@ -2645,17 +2665,17 @@
       <c r="H56" s="19" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="13" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D57" s="18" t="n"/>
@@ -2665,17 +2685,17 @@
       <c r="H57" s="19" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B58" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D58" s="18" t="n"/>
@@ -2685,17 +2705,17 @@
       <c r="H58" s="19" t="n"/>
     </row>
     <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D59" s="18" t="n"/>
@@ -2705,17 +2725,17 @@
       <c r="H59" s="19" t="n"/>
     </row>
     <row r="60" ht="32" customHeight="1">
-      <c r="A60" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B60" s="6" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>将来推計_需要3シナリオの感度表、人口推計の補正_65歳以上75歳以上の突合、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D60" s="18" t="n"/>
@@ -2725,17 +2745,17 @@
       <c r="H60" s="19" t="n"/>
     </row>
     <row r="61" ht="32" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D61" s="18" t="n"/>
@@ -2745,17 +2765,17 @@
       <c r="H61" s="19" t="n"/>
     </row>
     <row r="62" ht="32" customHeight="1">
-      <c r="A62" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B62" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D62" s="18" t="n"/>
@@ -2764,18 +2784,18 @@
       <c r="G62" s="18" t="n"/>
       <c r="H62" s="19" t="n"/>
     </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B63" s="20" t="n">
-        <v>47</v>
-      </c>
-      <c r="C63" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの42件、別スコープ5件</t>
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D63" s="18" t="n"/>
@@ -2784,8 +2804,28 @@
       <c r="G63" s="18" t="n"/>
       <c r="H63" s="19" t="n"/>
     </row>
-    <row r="65" ht="100" customHeight="1">
-      <c r="A65" s="21" t="inlineStr">
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B64" s="20" t="n">
+        <v>48</v>
+      </c>
+      <c r="C64" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの43件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="n"/>
+      <c r="E64" s="18" t="n"/>
+      <c r="F64" s="18" t="n"/>
+      <c r="G64" s="18" t="n"/>
+      <c r="H64" s="19" t="n"/>
+    </row>
+    <row r="66" ht="100" customHeight="1">
+      <c r="A66" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2796,13 +2836,13 @@
     <mergeCell ref="C63:H63"/>
     <mergeCell ref="C62:H62"/>
     <mergeCell ref="C57:H57"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="C55:H55"/>
     <mergeCell ref="C58:H58"/>
     <mergeCell ref="C60:H60"/>
-    <mergeCell ref="A65:H65"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A54:H54"/>
     <mergeCell ref="C61:H61"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="C64:H64"/>
     <mergeCell ref="C56:H56"/>
     <mergeCell ref="C59:H59"/>
   </mergeCells>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1121,12 +1121,12 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>128段落 10表</t>
+          <t>135段落 11表</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>49 KB</t>
+          <t>50 KB</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -1231,22 +1231,22 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の受け皿、判定ルールとレッドチームレビュー。</t>
+          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールとレッドチームレビュー。</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率で、75歳以上は社人研が年0.39ポイント速く、3年で1.15％の下方補正となる。影響は認定者22人（1.1％）・保険料月額22円にとどまる。町別は住民基本台帳の年齢5歳階級別（町別・年次）の受領後に確定する。</t>
+          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率のみである。住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）により、社人研 令和5年推計の基準年から最初の推計年までの5年で突合した。3町計では65〜74歳を3年で3.8％上方に、75歳以上を0.7％下方に補正する。社人研は前期高齢者の減少を実績より速く見込んでいる。町別では75歳以上の向きが逆で、東川町が上方（＋3.2％）・東神楽町が下方（▲4.2％）・美瑛町が境界である。町別の適用は、町別の第1号被保険者数の受領まで保留する。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -99,6 +99,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FDE9D9"/>
+        <bgColor rgb="00FDE9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
       </patternFill>
@@ -107,12 +113,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00DEEBF7"/>
         <bgColor rgb="00DEEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE9D9"/>
-        <bgColor rgb="00FDE9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -255,7 +255,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1219,34 +1219,34 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールとレッドチームレビュー。</t>
+          <t>概要版の頁数・体裁・掲載内容を定めるための構成案。位置付けと制約、3案の比較、推奨案の頁割、掲載する図表の候補、本編との対応と用語の言い換え、パブリックコメントとの関係と2版構成、決定を要する事項、レッドチームレビュー。</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率のみである。住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）により、社人研 令和5年推計の基準年から最初の推計年までの5年で突合した。3町計では65〜74歳を3年で3.8％上方に、75歳以上を0.7％下方に補正する。社人研は前期高齢者の減少を実績より速く見込んでいる。町別では75歳以上の向きが逆で、東川町が上方（＋3.2％）・東神楽町が下方（▲4.2％）・美瑛町が境界である。町別の適用は、町別の第1号被保険者数の受領まで保留する。</t>
+          <t>概要版はパブリックコメント（令和9年1月・2週間・WEB）に用いるため、「計画の要約」ではなく「何を決めようとしているのかが分かる文書」として設計する。A4判8頁（表紙＋本文6頁＋裏表紙）を推奨し、本編6章を1章1頁で割り付ける。パブリックコメントの時点では保険料が確定しないため、パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版構成とする。決定を要する事項6件を07シートに整理した。08シートのレッドチームレビュー8件には、本案の前提そのものへの指摘3件を含む。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1259,39 +1259,39 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
+          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールとレッドチームレビュー。</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
+          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率のみである。住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）により、社人研 令和5年推計の基準年から最初の推計年までの5年で突合した。3町計では65〜74歳を3年で3.8％上方に、75歳以上を0.7％下方に補正する。社人研は前期高齢者の減少を実績より速く見込んでいる。町別では75歳以上の向きが逆で、東川町が上方（＋3.2％）・東神楽町が下方（▲4.2％）・美瑛町が境界である。町別の適用は、町別の第1号被保険者数の受領まで保留する。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>第1稿</t>
         </is>
       </c>
     </row>
@@ -1299,39 +1299,39 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
+          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
+          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>41 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>7シート</t>
         </is>
       </c>
     </row>
@@ -1339,39 +1339,39 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>第1回委員会に向けた確認事項の依頼文書。</t>
+          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
+          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>41 KB</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>第9版</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1381,37 +1381,37 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>工程管理</t>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>第1回委員会に向けた確認事項の依頼文書。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第9版</t>
         </is>
       </c>
     </row>
@@ -1419,34 +1419,34 @@
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>工程管理</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1459,34 +1459,34 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -1506,27 +1506,27 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1546,27 +1546,27 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1579,34 +1579,34 @@
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1626,27 +1626,27 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -1666,27 +1666,27 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1706,27 +1706,27 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -1746,27 +1746,27 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1786,27 +1786,27 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1826,27 +1826,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -1906,27 +1906,27 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -1946,27 +1946,27 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -1986,17 +1986,17 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2026,27 +2026,27 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2066,27 +2066,27 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2106,27 +2106,27 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>14シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2146,22 +2146,22 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>14シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -2186,27 +2186,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2219,39 +2219,39 @@
       <c r="A43" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2266,32 +2266,32 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -2306,27 +2306,27 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2339,34 +2339,34 @@
       <c r="A46" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2379,24 +2379,24 @@
       <c r="A47" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>設計</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2419,39 +2419,39 @@
       <c r="A48" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H48" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2466,27 +2466,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H49" s="16" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H50" s="16" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -2586,88 +2586,108 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H52" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="52" customHeight="1">
+      <c r="A53" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G52" s="7" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H52" s="16" t="inlineStr">
+      <c r="H53" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="17" t="inlineStr">
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr"/>
-      <c r="G55" s="3" t="inlineStr"/>
-      <c r="H55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr"/>
+      <c r="E56" s="3" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr"/>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D56" s="18" t="n"/>
-      <c r="E56" s="18" t="n"/>
-      <c r="F56" s="18" t="n"/>
-      <c r="G56" s="18" t="n"/>
-      <c r="H56" s="19" t="n"/>
-    </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B57" s="6" t="n">
@@ -2675,7 +2695,7 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D57" s="18" t="n"/>
@@ -2687,15 +2707,15 @@
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>工程管理</t>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B58" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D58" s="18" t="n"/>
@@ -2705,17 +2725,17 @@
       <c r="H58" s="19" t="n"/>
     </row>
     <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D59" s="18" t="n"/>
@@ -2725,17 +2745,17 @@
       <c r="H59" s="19" t="n"/>
     </row>
     <row r="60" ht="32" customHeight="1">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B60" s="6" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、人口推計の補正_65歳以上75歳以上の突合、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D60" s="18" t="n"/>
@@ -2745,17 +2765,17 @@
       <c r="H60" s="19" t="n"/>
     </row>
     <row r="61" ht="32" customHeight="1">
-      <c r="A61" s="14" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>将来推計_需要3シナリオの感度表、人口推計の補正_65歳以上75歳以上の突合、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D61" s="18" t="n"/>
@@ -2765,17 +2785,17 @@
       <c r="H61" s="19" t="n"/>
     </row>
     <row r="62" ht="32" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B62" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D62" s="18" t="n"/>
@@ -2785,17 +2805,17 @@
       <c r="H62" s="19" t="n"/>
     </row>
     <row r="63" ht="32" customHeight="1">
-      <c r="A63" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D63" s="18" t="n"/>
@@ -2804,18 +2824,18 @@
       <c r="G63" s="18" t="n"/>
       <c r="H63" s="19" t="n"/>
     </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B64" s="20" t="n">
-        <v>48</v>
-      </c>
-      <c r="C64" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの43件、別スコープ5件</t>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D64" s="18" t="n"/>
@@ -2824,8 +2844,28 @@
       <c r="G64" s="18" t="n"/>
       <c r="H64" s="19" t="n"/>
     </row>
-    <row r="66" ht="100" customHeight="1">
-      <c r="A66" s="21" t="inlineStr">
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B65" s="20" t="n">
+        <v>49</v>
+      </c>
+      <c r="C65" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの44件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D65" s="18" t="n"/>
+      <c r="E65" s="18" t="n"/>
+      <c r="F65" s="18" t="n"/>
+      <c r="G65" s="18" t="n"/>
+      <c r="H65" s="19" t="n"/>
+    </row>
+    <row r="67" ht="100" customHeight="1">
+      <c r="A67" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2834,16 +2874,16 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C63:H63"/>
+    <mergeCell ref="C65:H65"/>
     <mergeCell ref="C62:H62"/>
     <mergeCell ref="C57:H57"/>
     <mergeCell ref="C58:H58"/>
+    <mergeCell ref="A55:H55"/>
     <mergeCell ref="C60:H60"/>
+    <mergeCell ref="A67:H67"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A54:H54"/>
     <mergeCell ref="C61:H61"/>
-    <mergeCell ref="A66:H66"/>
     <mergeCell ref="C64:H64"/>
-    <mergeCell ref="C56:H56"/>
     <mergeCell ref="C59:H59"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3497,7 +3537,7 @@
           <t>圏域を統計単位と整備単位に分ける案。訪問・通所困難地域の定義。自給率の3町間の差が3町単位を裏付ける。</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>事業所の実施地域の受領待ち</t>
         </is>
@@ -3519,7 +3559,7 @@
           <t>特定地域の指定基準の判定。3町のうち美瑛町が該当の見込み。</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>告示待ち</t>
         </is>
@@ -3629,7 +3669,7 @@
           <t>令和22年度・令和32年度の人口と認定者数。</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>給付費は第3段階待ち</t>
         </is>
@@ -3651,7 +3691,7 @@
           <t>代表KPIの3軸評価。交付金評価。長期でみた到達点。</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>事業実績の受領待ち（プロセス評価）</t>
         </is>
@@ -3673,7 +3713,7 @@
           <t>代表KPI16項目のデータ源と基準値。</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>3調査の第10期分の受領待ち</t>
         </is>
@@ -3695,7 +3735,7 @@
           <t>5基本目標の5層構成。アウトプットとアウトカムの分離。</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>事業実績の受領待ち</t>
         </is>
@@ -3717,7 +3757,7 @@
           <t>階級別人口×階級別認定率。3シナリオ。</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>シナリオの決定待ち</t>
         </is>
@@ -3739,7 +3779,7 @@
           <t>要介護度別の利用率と単価により算定する。</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>要介護度別認定者数と給付実績の受領待ち</t>
         </is>
@@ -3761,7 +3801,7 @@
           <t>24時間対応サービスの確保方策。区域外の施設への依存。</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>定員・稼働の実績の受領待ち</t>
         </is>
@@ -3783,7 +3823,7 @@
           <t>第9期の剰余の確定。管内比較。16段階の妥当性。</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>決算・基金と政令改正待ち</t>
         </is>
@@ -3805,7 +3845,7 @@
           <t>基本指針の新別表11事項への対応表。図表番号一覧。</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>告示待ち</t>
         </is>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -99,6 +99,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DEEBF7"/>
+        <bgColor rgb="00DEEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FDE9D9"/>
         <bgColor rgb="00FDE9D9"/>
       </patternFill>
@@ -107,12 +113,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DEEBF7"/>
-        <bgColor rgb="00DEEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -255,7 +255,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -746,7 +746,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_素案_第11稿.docx</t>
+          <t>第10期介護保険事業計画_素案_第12稿.docx</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>620段落 108表</t>
+          <t>667段落 114表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1221,32 +1221,32 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>設計</t>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画素案_第11稿→第12稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>概要版の頁数・体裁・掲載内容を定めるための構成案。位置付けと制約、3案の比較、推奨案の頁割、掲載する図表の候補、本編との対応と用語の言い換え、パブリックコメントとの関係と2版構成、決定を要する事項、レッドチームレビュー。</t>
+          <t>計画素案 第11稿から第12稿への修正の記録。修正の一覧、第9期評価の精緻化、アンケート集計分析の反映、人口推計の補正の反映、解消した確認事項、残る確認事項と次の作業。</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>概要版はパブリックコメント（令和9年1月・2週間・WEB）に用いるため、「計画の要約」ではなく「何を決めようとしているのかが分かる文書」として設計する。A4判8頁（表紙＋本文6頁＋裏表紙）を推奨し、本編6章を1章1頁で割り付ける。パブリックコメントの時点では保険料が確定しないため、パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版構成とする。決定を要する事項6件を07シートに整理した。08シートのレッドチームレビュー8件には、本案の前提そのものへの指摘3件を含む。</t>
+          <t>修正9件（差替2・是正1・追加6）。第9期19施策に調査の裏づけと代表KPIの対応で判定を付し（強5・中5・弱4・なし5）、施策の空白5領域を明らかにした。算定不可としていた代表KPI4項目（H07・H08・H12・H16）はいずれも代理指標により算定できることを確認し、削除する項目はない。訪問介護13事業所を全数把握（181人）し、高齢者世帯の記述を是正した。解消した確認事項5件、前提が変わった確認事項3件。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1259,34 +1259,34 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールとレッドチームレビュー。</t>
+          <t>概要版の頁数・体裁・掲載内容を定めるための構成案。位置付けと制約、3案の比較、推奨案の頁割、掲載する図表の候補、本編との対応と用語の言い換え、パブリックコメントとの関係と2版構成、決定を要する事項、レッドチームレビュー。</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率のみである。住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）により、社人研 令和5年推計の基準年から最初の推計年までの5年で突合した。3町計では65〜74歳を3年で3.8％上方に、75歳以上を0.7％下方に補正する。社人研は前期高齢者の減少を実績より速く見込んでいる。町別では75歳以上の向きが逆で、東川町が上方（＋3.2％）・東神楽町が下方（▲4.2％）・美瑛町が境界である。町別の適用は、町別の第1号被保険者数の受領まで保留する。</t>
+          <t>概要版はパブリックコメント（令和9年1月・2週間・WEB）に用いるため、「計画の要約」ではなく「何を決めようとしているのかが分かる文書」として設計する。A4判8頁（表紙＋本文6頁＋裏表紙）を推奨し、本編6章を1章1頁で割り付ける。パブリックコメントの時点では保険料が確定しないため、パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版構成とする。決定を要する事項6件を07シートに整理した。08シートのレッドチームレビュー8件には、本案の前提そのものへの指摘3件を含む。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -1299,39 +1299,39 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
+          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールとレッドチームレビュー。</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
+          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率のみである。住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）により、社人研 令和5年推計の基準年から最初の推計年までの5年で突合した。3町計では65〜74歳を3年で3.8％上方に、75歳以上を0.7％下方に補正する。社人研は前期高齢者の減少を実績より速く見込んでいる。町別では75歳以上の向きが逆で、東川町が上方（＋3.2％）・東神楽町が下方（▲4.2％）・美瑛町が境界である。町別の適用は、町別の第1号被保険者数の受領まで保留する。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>第1稿</t>
         </is>
       </c>
     </row>
@@ -1339,39 +1339,39 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
+          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
+          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>41 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>7シート</t>
         </is>
       </c>
     </row>
@@ -1379,39 +1379,39 @@
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>第1回委員会に向けた確認事項の依頼文書。</t>
+          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
+          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>第9版</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1421,37 +1421,37 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>工程管理</t>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>第1回委員会に向けた確認事項の依頼文書。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第9版</t>
         </is>
       </c>
     </row>
@@ -1459,34 +1459,34 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>工程管理</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -1499,34 +1499,34 @@
       <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1546,27 +1546,27 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1586,27 +1586,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1619,34 +1619,34 @@
       <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -1666,27 +1666,27 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1706,27 +1706,27 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -1746,27 +1746,27 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1786,27 +1786,27 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1826,27 +1826,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -1906,27 +1906,27 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -1946,27 +1946,27 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -1986,27 +1986,27 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -2066,27 +2066,27 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2106,27 +2106,27 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2146,27 +2146,27 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>14シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2186,27 +2186,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2226,27 +2226,27 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2259,39 +2259,39 @@
       <c r="A44" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2306,32 +2306,32 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -2346,27 +2346,27 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2379,34 +2379,34 @@
       <c r="A47" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="12" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2419,24 +2419,24 @@
       <c r="A48" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>設計</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2459,39 +2459,39 @@
       <c r="A49" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H49" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2506,27 +2506,27 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H50" s="16" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H51" s="16" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -2626,88 +2626,108 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H53" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="52" customHeight="1">
+      <c r="A54" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H53" s="16" t="inlineStr">
+      <c r="H54" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="17" t="inlineStr">
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr"/>
-      <c r="E56" s="3" t="inlineStr"/>
-      <c r="F56" s="3" t="inlineStr"/>
-      <c r="G56" s="3" t="inlineStr"/>
-      <c r="H56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr"/>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第11稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D57" s="18" t="n"/>
-      <c r="E57" s="18" t="n"/>
-      <c r="F57" s="18" t="n"/>
-      <c r="G57" s="18" t="n"/>
-      <c r="H57" s="19" t="n"/>
-    </row>
-    <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="13" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B58" s="6" t="n">
@@ -2715,7 +2735,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第12稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D58" s="18" t="n"/>
@@ -2727,15 +2747,15 @@
     <row r="59" ht="32" customHeight="1">
       <c r="A59" s="14" t="inlineStr">
         <is>
-          <t>工程管理</t>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D59" s="18" t="n"/>
@@ -2745,17 +2765,17 @@
       <c r="H59" s="19" t="n"/>
     </row>
     <row r="60" ht="32" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B60" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>第10期計画素案_第11稿→第12稿_修正指示書、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D60" s="18" t="n"/>
@@ -2765,17 +2785,17 @@
       <c r="H60" s="19" t="n"/>
     </row>
     <row r="61" ht="32" customHeight="1">
-      <c r="A61" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、人口推計の補正_65歳以上75歳以上の突合、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D61" s="18" t="n"/>
@@ -2785,17 +2805,17 @@
       <c r="H61" s="19" t="n"/>
     </row>
     <row r="62" ht="32" customHeight="1">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B62" s="6" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>将来推計_需要3シナリオの感度表、人口推計の補正_65歳以上75歳以上の突合、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D62" s="18" t="n"/>
@@ -2805,17 +2825,17 @@
       <c r="H62" s="19" t="n"/>
     </row>
     <row r="63" ht="32" customHeight="1">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D63" s="18" t="n"/>
@@ -2825,17 +2845,17 @@
       <c r="H63" s="19" t="n"/>
     </row>
     <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B64" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D64" s="18" t="n"/>
@@ -2844,18 +2864,18 @@
       <c r="G64" s="18" t="n"/>
       <c r="H64" s="19" t="n"/>
     </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B65" s="20" t="n">
-        <v>49</v>
-      </c>
-      <c r="C65" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの44件、別スコープ5件</t>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D65" s="18" t="n"/>
@@ -2864,8 +2884,28 @@
       <c r="G65" s="18" t="n"/>
       <c r="H65" s="19" t="n"/>
     </row>
-    <row r="67" ht="100" customHeight="1">
-      <c r="A67" s="21" t="inlineStr">
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B66" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="C66" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの45件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="n"/>
+      <c r="E66" s="18" t="n"/>
+      <c r="F66" s="18" t="n"/>
+      <c r="G66" s="18" t="n"/>
+      <c r="H66" s="19" t="n"/>
+    </row>
+    <row r="68" ht="100" customHeight="1">
+      <c r="A68" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2873,16 +2913,16 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A56:H56"/>
     <mergeCell ref="C63:H63"/>
     <mergeCell ref="C65:H65"/>
     <mergeCell ref="C62:H62"/>
-    <mergeCell ref="C57:H57"/>
+    <mergeCell ref="C60:H60"/>
     <mergeCell ref="C58:H58"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="C60:H60"/>
-    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="C66:H66"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C61:H61"/>
+    <mergeCell ref="A68:H68"/>
     <mergeCell ref="C64:H64"/>
     <mergeCell ref="C59:H59"/>
   </mergeCells>
@@ -3254,7 +3294,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_素案_第11稿.docx（620段落108表34図）</t>
+          <t>第10期介護保険事業計画_素案_第12稿.docx（620段落108表34図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -3405,7 +3445,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_素案_第11稿.docx</t>
+          <t>第10期介護保険事業計画_素案_第12稿.docx</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -3537,7 +3577,7 @@
           <t>圏域を統計単位と整備単位に分ける案。訪問・通所困難地域の定義。自給率の3町間の差が3町単位を裏付ける。</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>事業所の実施地域の受領待ち</t>
         </is>
@@ -3559,7 +3599,7 @@
           <t>特定地域の指定基準の判定。3町のうち美瑛町が該当の見込み。</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>告示待ち</t>
         </is>
@@ -3669,7 +3709,7 @@
           <t>令和22年度・令和32年度の人口と認定者数。</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>給付費は第3段階待ち</t>
         </is>
@@ -3691,7 +3731,7 @@
           <t>代表KPIの3軸評価。交付金評価。長期でみた到達点。</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>事業実績の受領待ち（プロセス評価）</t>
         </is>
@@ -3713,7 +3753,7 @@
           <t>代表KPI16項目のデータ源と基準値。</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>3調査の第10期分の受領待ち</t>
         </is>
@@ -3735,7 +3775,7 @@
           <t>5基本目標の5層構成。アウトプットとアウトカムの分離。</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>事業実績の受領待ち</t>
         </is>
@@ -3757,7 +3797,7 @@
           <t>階級別人口×階級別認定率。3シナリオ。</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>シナリオの決定待ち</t>
         </is>
@@ -3779,7 +3819,7 @@
           <t>要介護度別の利用率と単価により算定する。</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>要介護度別認定者数と給付実績の受領待ち</t>
         </is>
@@ -3801,7 +3841,7 @@
           <t>24時間対応サービスの確保方策。区域外の施設への依存。</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>定員・稼働の実績の受領待ち</t>
         </is>
@@ -3823,7 +3863,7 @@
           <t>第9期の剰余の確定。管内比較。16段階の妥当性。</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>決算・基金と政令改正待ち</t>
         </is>
@@ -3845,7 +3885,7 @@
           <t>基本指針の新別表11事項への対応表。図表番号一覧。</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>告示待ち</t>
         </is>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -3355,7 +3355,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>分析9件（妥当性検証・調査クロス集計・認定率の年齢調整・地域差・人口推計の基礎・将来推計・保険料2件・追加調査）、図表集33シート133点</t>
+          <t>分析9件（妥当性検証・調査クロス集計・認定率の年齢調整・地域差・人口推計の基礎・将来推計・保険料2件・追加調査）、図表集33シート133点。あわせてエビデンス集（統計データ・事業所と公表情報・調査の集計値のExcel3冊と索引、図表の画像79点）を添える。</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="13" ht="100" customHeight="1">
       <c r="A13" s="21" t="inlineStr">
         <is>
-          <t>注1）成果品は編集可能な電子データ及びPDF形式により提出いたします。図表、グラフ及び統計資料についても発注者が加工可能な形式で納品いたします。現時点の分析資料はすべてExcelであり、計算式と元数値を保持しております。注2）健康とくらしの調査の個票データは個人情報を含むため、納品物には集計値のみを収録する扱いとしております。この扱いでよいかご確認をお願いいたします（計画素案の別管理表 成果品No.7）。注3）PDFは最終組版時に一括して作成いたします。現時点ではWord・Excelのみをお渡ししております。</t>
+          <t>注1）成果品は編集可能な電子データ及びPDF形式により提出いたします。図表、グラフ及び統計資料についても発注者が加工可能な形式で納品いたします。現時点の分析資料はすべてExcelであり、計算式と元数値を保持しております。注2）健康とくらしの調査の個票データは個人情報を含むため、納品物には集計値のみを収録する扱いとしております。この扱いでよいかご確認をお願いいたします（計画素案の別管理表 成果品No.7）。注3）PDFは最終組版時に一括して作成いたします。現時点ではWord・Excelのみをお渡ししております。注4）納品データは、成果物（本一覧の50件）とエビデンス（成果物の数値の根拠となるデータ）に分けてお渡しいたします。エビデンス集は納品物そのものではなく、上記No.3の「分析資料等の電子データ」の一部として、数値の検証と第11期への引継ぎのために添えるものです。成果物ZIP3本・エビデンスZIP2本の構成です。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -642,7 +642,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>成果品一覧（令和8年8月4日現在）</t>
+          <t>成果品一覧（令和8年8月18日現在）</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第11稿で第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映した。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第11稿で第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映した。第12稿で第9期19施策の判定、施策の空白5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（667段落114表34図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>第11稿（7次）</t>
+          <t>第12稿（8次）</t>
         </is>
       </c>
     </row>
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第11稿→第12稿_修正指示書.xlsx</t>
+          <t>第10期計画_レビュー指摘への対応と決定事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第11稿から第12稿への修正の記録。修正の一覧、第9期評価の精緻化、アンケート集計分析の反映、人口推計の補正の反映、解消した確認事項、残る確認事項と次の作業。</t>
+          <t>令和8年8月18日のレビュー（Red Teamレビュー・進捗更新・次工程提案）の指摘13件への対応と、委員会決定事項一覧。指摘への対応、事実確認の結果、決定事項一覧、優先順位と期限、受入ゲートの充足状況、残る課題と当方の見解。</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>修正9件（差替2・是正1・追加6）。第9期19施策に調査の裏づけと代表KPIの対応で判定を付し（強5・中5・弱4・なし5）、施策の空白5領域を明らかにした。算定不可としていた代表KPI4項目（H07・H08・H12・H16）はいずれも代理指標により算定できることを確認し、削除する項目はない。訪問介護13事業所を全数把握（181人）し、高齢者世帯の記述を是正した。解消した確認事項5件、前提が変わった確認事項3件。</t>
+          <t>指摘13件（P0 3・P1 5・P2 4・P3 1）はすべて事実であり、うち3件は当方の誤りであった（健康とくらしの調査の個票の記載、成果品一覧の基準日・版、エビデンス索引のZIP番号）。計画本文に残る［要協議］等90箇所を12件の決定事項に集約し、選択肢・推奨案・影響・決定者・期限を付した。最高優先は決定1（人口推計の基礎）・決定2（認定率のシナリオ）・決定7（調査の集計方法）の3件で、いずれも追加の資料を要さない。受入ゲート5件のうち充足1・一部充足2・未充足2。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1259,34 +1259,34 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>概要版の頁数・体裁・掲載内容を定めるための構成案。位置付けと制約、3案の比較、推奨案の頁割、掲載する図表の候補、本編との対応と用語の言い換え、パブリックコメントとの関係と2版構成、決定を要する事項、レッドチームレビュー。</t>
+          <t>第9期19施策の評価表（受け皿）と、実績が揃わない場合の暫定評価ルール。施策別評価表、実績の入力様式、暫定評価ルール、現時点で判定できる成果評価、委員会用スコアカード。</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>概要版はパブリックコメント（令和9年1月・2週間・WEB）に用いるため、「計画の要約」ではなく「何を決めようとしているのかが分かる文書」として設計する。A4判8頁（表紙＋本文6頁＋裏表紙）を推奨し、本編6章を1章1頁で割り付ける。パブリックコメントの時点では保険料が確定しないため、パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版構成とする。決定を要する事項6件を07シートに整理した。08シートのレッドチームレビュー8件には、本案の前提そのものへの指摘3件を含む。</t>
+          <t>評価を成果評価（アウトカム）とプロセス評価（実施状況）の2層に分け、成果評価は事業実績を要さず現時点で判定できることを示した。19施策のうち成果評価が可能10・調査による代理評価4・プロセス評価のみ5である。未受領年度は「未把握」と記載し、「実施されなかった」と書き分ける。委員会には成果指標12・補足指標4のスコアカードを示す。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>26 KB</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -1299,34 +1299,34 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールとレッドチームレビュー。</t>
+          <t>実施済み3調査の点検事項のうち重大6件・要確認21件の照会票と、確定値の管理表。照会事項の一覧、事業者別の照会票、未回答時の扱い、確定値表、確定後に更新する箇所、発出と回答の管理。</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率のみである。住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）により、社人研 令和5年推計の基準年から最初の推計年までの5年で突合した。3町計では65〜74歳を3年で3.8％上方に、75歳以上を0.7％下方に補正する。社人研は前期高齢者の減少を実績より速く見込んでいる。町別では75歳以上の向きが逆で、東川町が上方（＋3.2％）・東神楽町が下方（▲4.2％）・美瑛町が境界である。町別の適用は、町別の第1号被保険者数の受領まで保留する。</t>
+          <t>27件を照会先別に整理し、事業者への照会は5先に一本化した。未回答時の扱いを5類型（重複計上・回答の偏り・地区が不明・施設の未回答・見える化との不一致）で事前に定めている。確定値表10件のうち確定は2件（訪問介護員等181人、H12の20.4％）で、この2件は照会の結果によらず変わらない。確定後に更新する箇所11件を一覧化した。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -1339,24 +1339,24 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画素案_第11稿→第12稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
+          <t>計画素案 第11稿から第12稿への修正の記録。修正の一覧、第9期評価の精緻化、アンケート集計分析の反映、人口推計の補正の反映、解消した確認事項、残る確認事項と次の作業。</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
+          <t>修正9件（差替2・是正1・追加6）。第9期19施策に調査の裏づけと代表KPIの対応で判定を付し（強5・中5・弱4・なし5）、施策の空白5領域を明らかにした。算定不可としていた代表KPI4項目（H07・H08・H12・H16）はいずれも代理指標により算定できることを確認し、削除する項目はない。訪問介護13事業所を全数把握（181人）し、高齢者世帯の記述を是正した。解消した確認事項5件、前提が変わった確認事項3件。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>第1稿</t>
         </is>
       </c>
     </row>
@@ -1379,39 +1379,39 @@
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
+          <t>概要版の頁数・体裁・掲載内容を定めるための構成案。位置付けと制約、3案の比較、推奨案の頁割、掲載する図表の候補、本編との対応と用語の言い換え、パブリックコメントとの関係と2版構成、決定を要する事項、レッドチームレビュー。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
+          <t>概要版はパブリックコメント（令和9年1月・2週間・WEB）に用いるため、「計画の要約」ではなく「何を決めようとしているのかが分かる文書」として設計する。A4判8頁（表紙＋本文6頁＋裏表紙）を推奨し、本編6章を1章1頁で割り付ける。パブリックコメントの時点では保険料が確定しないため、パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版構成とする。決定を要する事項6件を07シートに整理した。08シートのレッドチームレビュー8件には、本案の前提そのものへの指摘3件を含む。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第1稿</t>
         </is>
       </c>
     </row>
@@ -1419,39 +1419,39 @@
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>第1回委員会に向けた確認事項の依頼文書。</t>
+          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールとレッドチームレビュー。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
+          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率のみである。住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）により、社人研 令和5年推計の基準年から最初の推計年までの5年で突合した。3町計では65〜74歳を3年で3.8％上方に、75歳以上を0.7％下方に補正する。社人研は前期高齢者の減少を実績より速く見込んでいる。町別では75歳以上の向きが逆で、東川町が上方（＋3.2％）・東神楽町が下方（▲4.2％）・美瑛町が境界である。町別の適用は、町別の第1号被保険者数の受領まで保留する。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>第9版</t>
+          <t>第1稿</t>
         </is>
       </c>
     </row>
@@ -1459,24 +1459,24 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>7シート</t>
         </is>
       </c>
     </row>
@@ -1499,29 +1499,29 @@
       <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -1539,39 +1539,39 @@
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>第1回委員会に向けた確認事項の依頼文書。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第9版</t>
         </is>
       </c>
     </row>
@@ -1579,34 +1579,34 @@
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1619,29 +1619,29 @@
       <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
@@ -1659,24 +1659,24 @@
       <c r="A29" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1699,34 +1699,34 @@
       <c r="A30" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -1739,34 +1739,34 @@
       <c r="A31" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1786,27 +1786,27 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1826,27 +1826,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -1906,27 +1906,27 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -1946,27 +1946,27 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -1986,27 +1986,27 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2026,27 +2026,27 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2066,27 +2066,27 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2106,27 +2106,27 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2146,27 +2146,27 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2186,27 +2186,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2226,27 +2226,27 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2266,27 +2266,27 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2299,39 +2299,39 @@
       <c r="A45" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2339,34 +2339,34 @@
       <c r="A46" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2379,34 +2379,34 @@
       <c r="A47" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2419,39 +2419,39 @@
       <c r="A48" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -2459,34 +2459,34 @@
       <c r="A49" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2499,39 +2499,39 @@
       <c r="A50" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H50" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>52 KB</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2539,39 +2539,39 @@
       <c r="A51" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
-        </is>
-      </c>
-      <c r="H51" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>18 KB</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2579,39 +2579,39 @@
       <c r="A52" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
-        </is>
-      </c>
-      <c r="H52" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2626,27 +2626,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H53" s="16" t="inlineStr">
@@ -2666,136 +2666,196 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
+          <t>01_共通_基本コラム部品.xlsx</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>3計画に共通する基本コラム部品。</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>15 KB</t>
+        </is>
+      </c>
+      <c r="H54" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="52" customHeight="1">
+      <c r="A55" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H55" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="52" customHeight="1">
+      <c r="A56" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H56" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="52" customHeight="1">
+      <c r="A57" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G54" s="7" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H54" s="16" t="inlineStr">
+      <c r="H57" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="17" t="inlineStr">
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr"/>
-      <c r="G57" s="3" t="inlineStr"/>
-      <c r="H57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr"/>
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="3" t="inlineStr"/>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
         </is>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B61" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第12稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D58" s="18" t="n"/>
-      <c r="E58" s="18" t="n"/>
-      <c r="F58" s="18" t="n"/>
-      <c r="G58" s="18" t="n"/>
-      <c r="H58" s="19" t="n"/>
-    </row>
-    <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
-        </is>
-      </c>
-      <c r="D59" s="18" t="n"/>
-      <c r="E59" s="18" t="n"/>
-      <c r="F59" s="18" t="n"/>
-      <c r="G59" s="18" t="n"/>
-      <c r="H59" s="19" t="n"/>
-    </row>
-    <row r="60" ht="32" customHeight="1">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画素案_第11稿→第12稿_修正指示書、業務工程管理表、計画素案の別管理表</t>
-        </is>
-      </c>
-      <c r="D60" s="18" t="n"/>
-      <c r="E60" s="18" t="n"/>
-      <c r="F60" s="18" t="n"/>
-      <c r="G60" s="18" t="n"/>
-      <c r="H60" s="19" t="n"/>
-    </row>
-    <row r="61" ht="32" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D61" s="18" t="n"/>
@@ -2805,17 +2865,17 @@
       <c r="H61" s="19" t="n"/>
     </row>
     <row r="62" ht="32" customHeight="1">
-      <c r="A62" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B62" s="6" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、人口推計の補正_65歳以上75歳以上の突合、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D62" s="18" t="n"/>
@@ -2825,17 +2885,17 @@
       <c r="H62" s="19" t="n"/>
     </row>
     <row r="63" ht="32" customHeight="1">
-      <c r="A63" s="13" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>レビュー指摘への対応と決定事項一覧、第10期計画素案_第11稿→第12稿_修正指示書、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D63" s="18" t="n"/>
@@ -2845,17 +2905,17 @@
       <c r="H63" s="19" t="n"/>
     </row>
     <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B64" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D64" s="18" t="n"/>
@@ -2865,17 +2925,17 @@
       <c r="H64" s="19" t="n"/>
     </row>
     <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>将来推計_需要3シナリオの感度表、人口推計の補正_65歳以上75歳以上の突合、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D65" s="18" t="n"/>
@@ -2884,18 +2944,18 @@
       <c r="G65" s="18" t="n"/>
       <c r="H65" s="19" t="n"/>
     </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B66" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="C66" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの45件、別スコープ5件</t>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>設計</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D66" s="18" t="n"/>
@@ -2904,8 +2964,68 @@
       <c r="G66" s="18" t="n"/>
       <c r="H66" s="19" t="n"/>
     </row>
-    <row r="68" ht="100" customHeight="1">
-      <c r="A68" s="21" t="inlineStr">
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="n"/>
+      <c r="E67" s="18" t="n"/>
+      <c r="F67" s="18" t="n"/>
+      <c r="G67" s="18" t="n"/>
+      <c r="H67" s="19" t="n"/>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="n"/>
+      <c r="E68" s="18" t="n"/>
+      <c r="F68" s="18" t="n"/>
+      <c r="G68" s="18" t="n"/>
+      <c r="H68" s="19" t="n"/>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B69" s="20" t="n">
+        <v>53</v>
+      </c>
+      <c r="C69" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの48件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D69" s="18" t="n"/>
+      <c r="E69" s="18" t="n"/>
+      <c r="F69" s="18" t="n"/>
+      <c r="G69" s="18" t="n"/>
+      <c r="H69" s="19" t="n"/>
+    </row>
+    <row r="71" ht="100" customHeight="1">
+      <c r="A71" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -2913,18 +3033,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A56:H56"/>
     <mergeCell ref="C63:H63"/>
     <mergeCell ref="C65:H65"/>
     <mergeCell ref="C62:H62"/>
-    <mergeCell ref="C60:H60"/>
-    <mergeCell ref="C58:H58"/>
+    <mergeCell ref="A59:H59"/>
     <mergeCell ref="C66:H66"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A71:H71"/>
     <mergeCell ref="C61:H61"/>
-    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="C69:H69"/>
     <mergeCell ref="C64:H64"/>
-    <mergeCell ref="C59:H59"/>
+    <mergeCell ref="C68:H68"/>
+    <mergeCell ref="C67:H67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3294,7 +3414,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_素案_第12稿.docx（620段落108表34図）</t>
+          <t>第10期介護保険事業計画_素案_第12稿.docx（667段落114表34図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -3497,7 +3617,7 @@
     <row r="13" ht="100" customHeight="1">
       <c r="A13" s="21" t="inlineStr">
         <is>
-          <t>注1）成果品は編集可能な電子データ及びPDF形式により提出いたします。図表、グラフ及び統計資料についても発注者が加工可能な形式で納品いたします。現時点の分析資料はすべてExcelであり、計算式と元数値を保持しております。注2）健康とくらしの調査の個票データは個人情報を含むため、納品物には集計値のみを収録する扱いとしております。この扱いでよいかご確認をお願いいたします（計画素案の別管理表 成果品No.7）。注3）PDFは最終組版時に一括して作成いたします。現時点ではWord・Excelのみをお渡ししております。注4）納品データは、成果物（本一覧の50件）とエビデンス（成果物の数値の根拠となるデータ）に分けてお渡しいたします。エビデンス集は納品物そのものではなく、上記No.3の「分析資料等の電子データ」の一部として、数値の検証と第11期への引継ぎのために添えるものです。成果物ZIP3本・エビデンスZIP2本の構成です。</t>
+          <t>注1）成果品は編集可能な電子データ及びPDF形式により提出いたします。図表、グラフ及び統計資料についても発注者が加工可能な形式で納品いたします。ただし現時点の分析資料のExcelは、生成スクリプトが算定した結果を書き出した「確定値の転記表」であり、セル内に計算式は入っておりません（第9版までの本欄には「計算式と元数値を保持」と記載しておりましたが、実態と異なるため改めました）。元数値はエビデンス集に、算定の手順は各成果品の「推計の方法」「算定方法」の欄に記載しております。入力値を変えて再計算する必要がある推計については、計算式を入れた「計算過程確認シート」を将来推計の成果品に付しております。注2）健康とくらしの調査の個票データ（4,729票）は令和8年8月に受領し、クロス集計・分析に用いております。個人情報を含むため、成果品及びエビデンス集には集計値のみを収録し、個票そのものは収録しておりません。この扱いでよいかご確認をお願いいたします（計画素案の別管理表 成果品No.7）。注3）PDFは最終組版時に一括して作成いたします。現時点ではWord・Excelのみをお渡ししております。注4）納品データは、成果物（本一覧の50件）とエビデンス（成果物の数値の根拠となるデータ）に分けてお渡しいたします。エビデンス集は納品物そのものではなく、上記No.3の「分析資料等の電子データ」の一部として、数値の検証と第11期への引継ぎのために添えるものです。成果物ZIP3本・エビデンスZIP2本の構成です。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1226,27 +1226,27 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー指摘への対応と決定事項一覧.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月18日のレビュー（Red Teamレビュー・進捗更新・次工程提案）の指摘13件への対応と、委員会決定事項一覧。指摘への対応、事実確認の結果、決定事項一覧、優先順位と期限、受入ゲートの充足状況、残る課題と当方の見解。</t>
+          <t>業務仕様書「４．業務内容」（1）〜（12）の区分ごとの月次進捗報告。今月の総括、業務内容別の実施状況、資料の受領と依頼の状況、ご決定をお願いする事項、進捗が進んでいない事項、翌月の予定。</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>指摘13件（P0 3・P1 5・P2 4・P3 1）はすべて事実であり、うち3件は当方の誤りであった（健康とくらしの調査の個票の記載、成果品一覧の基準日・版、エビデンス索引のZIP番号）。計画本文に残る［要協議］等90箇所を12件の決定事項に集約し、選択肢・推奨案・影響・決定者・期限を付した。最高優先は決定1（人口推計の基礎）・決定2（認定率のシナリオ）・決定7（調査の集計方法）の3件で、いずれも追加の資料を要さない。受入ゲート5件のうち充足1・一部充足2・未充足2。</t>
+          <t>全体進捗60％（前月比＋33pt）。進捗が進んでいない事項は7件で、うち受託者の作業として残るのは3件（再計算可能化・図表の脚注・社会資源一覧の反映）である。残る4件は資料の受領又は発注者のご決定を待つ状態で、受託者側の受け皿は作成済みである。最高優先の決定3件（決定1・決定2・決定7）は追加の資料を要さない。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>185段落 8表</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>48 KB</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1259,24 +1259,24 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>第9期19施策の評価表（受け皿）と、実績が揃わない場合の暫定評価ルール。施策別評価表、実績の入力様式、暫定評価ルール、現時点で判定できる成果評価、委員会用スコアカード。</t>
+          <t>令和8年8月20日に受領した3町の社会資源一覧（74事業所）と、既存の把握との突合。受領した一覧、訪問介護13事業所の突合、サービス別の従業員数、指定事業所一覧との網羅性、反映する箇所。</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>評価を成果評価（アウトカム）とプロセス評価（実施状況）の2層に分け、成果評価は事業実績を要さず現時点で判定できることを示した。19施策のうち成果評価が可能10・調査による代理評価4・プロセス評価のみ5である。未受領年度は「未把握」と記載し、「実施されなかった」と書き分ける。委員会には成果指標12・補足指標4のスコアカードを示す。</t>
+          <t>3町74事業所の従業員総数・常勤・非常勤が得られ、これまで訪問介護でしか把握できなかった従業員数が全サービスについてそろった。訪問介護13事業所は公表画面による把握と13件とも対応し、3事業所は完全に一致した（社会資源203.5人／公表総従業者184.5人）。差は数える範囲（管理者・事務職員を含むか）によるものであり、計画本文の訪問介護員等181人は変わらない。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>26 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -1299,24 +1299,24 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
+          <t>第10期計画_レビュー指摘への対応と決定事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>実施済み3調査の点検事項のうち重大6件・要確認21件の照会票と、確定値の管理表。照会事項の一覧、事業者別の照会票、未回答時の扱い、確定値表、確定後に更新する箇所、発出と回答の管理。</t>
+          <t>令和8年8月18日のレビュー（Red Teamレビュー・進捗更新・次工程提案）の指摘13件への対応と、委員会決定事項一覧。指摘への対応、事実確認の結果、決定事項一覧、優先順位と期限、受入ゲートの充足状況、残る課題と当方の見解。</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>27件を照会先別に整理し、事業者への照会は5先に一本化した。未回答時の扱いを5類型（重複計上・回答の偏り・地区が不明・施設の未回答・見える化との不一致）で事前に定めている。確定値表10件のうち確定は2件（訪問介護員等181人、H12の20.4％）で、この2件は照会の結果によらず変わらない。確定後に更新する箇所11件を一覧化した。</t>
+          <t>指摘13件（P0 3・P1 5・P2 4・P3 1）はすべて事実であり、うち3件は当方の誤りであった（健康とくらしの調査の個票の記載、成果品一覧の基準日・版、エビデンス索引のZIP番号）。計画本文に残る［要協議］等90箇所を12件の決定事項に集約し、選択肢・推奨案・影響・決定者・期限を付した。最高優先は決定1（人口推計の基礎）・決定2（認定率のシナリオ）・決定7（調査の集計方法）の3件で、いずれも追加の資料を要さない。受入ゲート5件のうち充足1・一部充足2・未充足2。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -1339,34 +1339,34 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第11稿→第12稿_修正指示書.xlsx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第11稿から第12稿への修正の記録。修正の一覧、第9期評価の精緻化、アンケート集計分析の反映、人口推計の補正の反映、解消した確認事項、残る確認事項と次の作業。</t>
+          <t>第9期19施策の評価表（受け皿）と、実績が揃わない場合の暫定評価ルール。施策別評価表、実績の入力様式、暫定評価ルール、現時点で判定できる成果評価、委員会用スコアカード。</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>修正9件（差替2・是正1・追加6）。第9期19施策に調査の裏づけと代表KPIの対応で判定を付し（強5・中5・弱4・なし5）、施策の空白5領域を明らかにした。算定不可としていた代表KPI4項目（H07・H08・H12・H16）はいずれも代理指標により算定できることを確認し、削除する項目はない。訪問介護13事業所を全数把握（181人）し、高齢者世帯の記述を是正した。解消した確認事項5件、前提が変わった確認事項3件。</t>
+          <t>評価を成果評価（アウトカム）とプロセス評価（実施状況）の2層に分け、成果評価は事業実績を要さず現時点で判定できることを示した。19施策のうち成果評価が可能10・調査による代理評価4・プロセス評価のみ5である。未受領年度は「未把握」と記載し、「実施されなかった」と書き分ける。委員会には成果指標12・補足指標4のスコアカードを示す。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>26 KB</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1379,34 +1379,34 @@
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>概要版の頁数・体裁・掲載内容を定めるための構成案。位置付けと制約、3案の比較、推奨案の頁割、掲載する図表の候補、本編との対応と用語の言い換え、パブリックコメントとの関係と2版構成、決定を要する事項、レッドチームレビュー。</t>
+          <t>実施済み3調査の点検事項のうち重大6件・要確認21件の照会票と、確定値の管理表。照会事項の一覧、事業者別の照会票、未回答時の扱い、確定値表、確定後に更新する箇所、発出と回答の管理。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>概要版はパブリックコメント（令和9年1月・2週間・WEB）に用いるため、「計画の要約」ではなく「何を決めようとしているのかが分かる文書」として設計する。A4判8頁（表紙＋本文6頁＋裏表紙）を推奨し、本編6章を1章1頁で割り付ける。パブリックコメントの時点では保険料が確定しないため、パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版構成とする。決定を要する事項6件を07シートに整理した。08シートのレッドチームレビュー8件には、本案の前提そのものへの指摘3件を含む。</t>
+          <t>27件を照会先別に整理し、事業者への照会は5先に一本化した。未回答時の扱いを5類型（重複計上・回答の偏り・地区が不明・施設の未回答・見える化との不一致）で事前に定めている。確定値表10件のうち確定は2件（訪問介護員等181人、H12の20.4％）で、この2件は照会の結果によらず変わらない。確定後に更新する箇所11件を一覧化した。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1419,34 +1419,34 @@
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画素案_第11稿→第12稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールとレッドチームレビュー。</t>
+          <t>計画素案 第11稿から第12稿への修正の記録。修正の一覧、第9期評価の精緻化、アンケート集計分析の反映、人口推計の補正の反映、解消した確認事項、残る確認事項と次の作業。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率のみである。住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）により、社人研 令和5年推計の基準年から最初の推計年までの5年で突合した。3町計では65〜74歳を3年で3.8％上方に、75歳以上を0.7％下方に補正する。社人研は前期高齢者の減少を実績より速く見込んでいる。町別では75歳以上の向きが逆で、東川町が上方（＋3.2％）・東神楽町が下方（▲4.2％）・美瑛町が境界である。町別の適用は、町別の第1号被保険者数の受領まで保留する。</t>
+          <t>修正9件（差替2・是正1・追加6）。第9期19施策に調査の裏づけと代表KPIの対応で判定を付し（強5・中5・弱4・なし5）、施策の空白5領域を明らかにした。算定不可としていた代表KPI4項目（H07・H08・H12・H16）はいずれも代理指標により算定できることを確認し、削除する項目はない。訪問介護13事業所を全数把握（181人）し、高齢者世帯の記述を是正した。解消した確認事項5件、前提が変わった確認事項3件。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1459,39 +1459,39 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
+          <t>概要版の頁数・体裁・掲載内容を定めるための構成案。位置付けと制約、3案の比較、推奨案の頁割、掲載する図表の候補、本編との対応と用語の言い換え、パブリックコメントとの関係と2版構成、決定を要する事項、レッドチームレビュー。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
+          <t>概要版はパブリックコメント（令和9年1月・2週間・WEB）に用いるため、「計画の要約」ではなく「何を決めようとしているのかが分かる文書」として設計する。A4判8頁（表紙＋本文6頁＋裏表紙）を推奨し、本編6章を1章1頁で割り付ける。パブリックコメントの時点では保険料が確定しないため、パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版構成とする。決定を要する事項6件を07シートに整理した。08シートのレッドチームレビュー8件には、本案の前提そのものへの指摘3件を含む。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>第1稿</t>
         </is>
       </c>
     </row>
@@ -1499,24 +1499,24 @@
       <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
+          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールとレッドチームレビュー。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
+          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率のみである。住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）により、社人研 令和5年推計の基準年から最初の推計年までの5年で突合した。3町計では65〜74歳を3年で3.8％上方に、75歳以上を0.7％下方に補正する。社人研は前期高齢者の減少を実績より速く見込んでいる。町別では75歳以上の向きが逆で、東川町が上方（＋3.2％）・東神楽町が下方（▲4.2％）・美瑛町が境界である。町別の適用は、町別の第1号被保険者数の受領まで保留する。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第1稿</t>
         </is>
       </c>
     </row>
@@ -1546,32 +1546,32 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>第1回委員会に向けた確認事項の依頼文書。</t>
+          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
+          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>第9版</t>
+          <t>7シート</t>
         </is>
       </c>
     </row>
@@ -1579,34 +1579,34 @@
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1619,39 +1619,39 @@
       <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>第1回委員会に向けた確認事項の依頼文書。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第9版</t>
         </is>
       </c>
     </row>
@@ -1659,34 +1659,34 @@
       <c r="A29" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1699,34 +1699,34 @@
       <c r="A30" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -1746,27 +1746,27 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1779,34 +1779,34 @@
       <c r="A32" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1819,34 +1819,34 @@
       <c r="A33" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -1906,27 +1906,27 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -1946,27 +1946,27 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -1986,17 +1986,17 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2026,27 +2026,27 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2066,27 +2066,27 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2106,27 +2106,27 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2146,27 +2146,27 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2186,27 +2186,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2226,27 +2226,27 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2266,27 +2266,27 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2306,27 +2306,27 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2346,27 +2346,27 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2386,27 +2386,27 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2419,39 +2419,39 @@
       <c r="A48" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2459,34 +2459,34 @@
       <c r="A49" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2506,32 +2506,32 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -2539,34 +2539,34 @@
       <c r="A51" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2579,34 +2579,34 @@
       <c r="A52" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="13" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2619,39 +2619,39 @@
       <c r="A53" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H53" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>18 KB</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2659,39 +2659,39 @@
       <c r="A54" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
-        </is>
-      </c>
-      <c r="H54" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2706,27 +2706,27 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H55" s="16" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H56" s="16" t="inlineStr">
@@ -2786,116 +2786,156 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H57" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="52" customHeight="1">
+      <c r="A58" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H58" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="52" customHeight="1">
+      <c r="A59" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G57" s="7" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H57" s="16" t="inlineStr">
+      <c r="H59" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="17" t="inlineStr">
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr"/>
-      <c r="E60" s="3" t="inlineStr"/>
-      <c r="F60" s="3" t="inlineStr"/>
-      <c r="G60" s="3" t="inlineStr"/>
-      <c r="H60" s="3" t="inlineStr"/>
-    </row>
-    <row r="61" ht="32" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr"/>
+      <c r="E62" s="3" t="inlineStr"/>
+      <c r="F62" s="3" t="inlineStr"/>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
         </is>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B63" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第12稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D61" s="18" t="n"/>
-      <c r="E61" s="18" t="n"/>
-      <c r="F61" s="18" t="n"/>
-      <c r="G61" s="18" t="n"/>
-      <c r="H61" s="19" t="n"/>
-    </row>
-    <row r="62" ht="32" customHeight="1">
-      <c r="A62" s="14" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
-        </is>
-      </c>
-      <c r="D62" s="18" t="n"/>
-      <c r="E62" s="18" t="n"/>
-      <c r="F62" s="18" t="n"/>
-      <c r="G62" s="18" t="n"/>
-      <c r="H62" s="19" t="n"/>
-    </row>
-    <row r="63" ht="32" customHeight="1">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>レビュー指摘への対応と決定事項一覧、第10期計画素案_第11稿→第12稿_修正指示書、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D63" s="18" t="n"/>
@@ -2905,17 +2945,17 @@
       <c r="H63" s="19" t="n"/>
     </row>
     <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B64" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D64" s="18" t="n"/>
@@ -2925,17 +2965,17 @@
       <c r="H64" s="19" t="n"/>
     </row>
     <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、人口推計の補正_65歳以上75歳以上の突合、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>業務進捗報告書_令和8年8月分、レビュー指摘への対応と決定事項一覧、第10期計画素案_第11稿→第12稿_修正指示書、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D65" s="18" t="n"/>
@@ -2945,17 +2985,17 @@
       <c r="H65" s="19" t="n"/>
     </row>
     <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="13" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B66" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D66" s="18" t="n"/>
@@ -2965,17 +3005,17 @@
       <c r="H66" s="19" t="n"/>
     </row>
     <row r="67" ht="32" customHeight="1">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D67" s="18" t="n"/>
@@ -2985,17 +3025,17 @@
       <c r="H67" s="19" t="n"/>
     </row>
     <row r="68" ht="32" customHeight="1">
-      <c r="A68" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B68" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D68" s="18" t="n"/>
@@ -3004,18 +3044,18 @@
       <c r="G68" s="18" t="n"/>
       <c r="H68" s="19" t="n"/>
     </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B69" s="20" t="n">
-        <v>53</v>
-      </c>
-      <c r="C69" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの48件、別スコープ5件</t>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D69" s="18" t="n"/>
@@ -3024,8 +3064,48 @@
       <c r="G69" s="18" t="n"/>
       <c r="H69" s="19" t="n"/>
     </row>
-    <row r="71" ht="100" customHeight="1">
-      <c r="A71" s="21" t="inlineStr">
+    <row r="70" ht="32" customHeight="1">
+      <c r="A70" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+        </is>
+      </c>
+      <c r="D70" s="18" t="n"/>
+      <c r="E70" s="18" t="n"/>
+      <c r="F70" s="18" t="n"/>
+      <c r="G70" s="18" t="n"/>
+      <c r="H70" s="19" t="n"/>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B71" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="C71" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの50件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="n"/>
+      <c r="E71" s="18" t="n"/>
+      <c r="F71" s="18" t="n"/>
+      <c r="G71" s="18" t="n"/>
+      <c r="H71" s="19" t="n"/>
+    </row>
+    <row r="73" ht="100" customHeight="1">
+      <c r="A73" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -3035,15 +3115,15 @@
   <mergeCells count="12">
     <mergeCell ref="C63:H63"/>
     <mergeCell ref="C65:H65"/>
-    <mergeCell ref="C62:H62"/>
-    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="C71:H71"/>
+    <mergeCell ref="C68:H68"/>
     <mergeCell ref="C66:H66"/>
+    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A71:H71"/>
-    <mergeCell ref="C61:H61"/>
+    <mergeCell ref="C70:H70"/>
     <mergeCell ref="C69:H69"/>
     <mergeCell ref="C64:H64"/>
-    <mergeCell ref="C68:H68"/>
+    <mergeCell ref="A61:H61"/>
     <mergeCell ref="C67:H67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>185段落 8表</t>
+          <t>187段落 8表</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
@@ -1346,27 +1346,27 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>第9期19施策の評価表（受け皿）と、実績が揃わない場合の暫定評価ルール。施策別評価表、実績の入力様式、暫定評価ルール、現時点で判定できる成果評価、委員会用スコアカード。</t>
+          <t>仕様書５の令和8年8月の工程末に提出する「第9期計画の評価・検証の中間報告」。本報告の位置づけ、評価の枠組み、成果評価の結果、構造評価の結果、不足している資料と確認事項、評価の確からしさ、9月以降の進め方。</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>評価を成果評価（アウトカム）とプロセス評価（実施状況）の2層に分け、成果評価は事業実績を要さず現時点で判定できることを示した。19施策のうち成果評価が可能10・調査による代理評価4・プロセス評価のみ5である。未受領年度は「未把握」と記載し、「実施されなかった」と書き分ける。委員会には成果指標12・補足指標4のスコアカードを示す。</t>
+          <t>評価を①成果評価②構造評価③プロセス評価の3層に分け、資料を要さない①②を8月に整理した。第9期代表KPI4項目は達成1・未達2・算定可1だが、未達2項目とも実態が悪化したとは言えない。19施策の評価可能性は強5・中5・弱4・なし5で、調査に所見があるのに施策がない5領域を特定した。評価を確定するために不足する資料7件・確認事項5件を洗い出した。③プロセス評価は資料の受領後（令和8年9月以降）である。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>75段落 11表</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>26 KB</t>
+          <t>47 KB</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1386,27 +1386,27 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>実施済み3調査の点検事項のうち重大6件・要確認21件の照会票と、確定値の管理表。照会事項の一覧、事業者別の照会票、未回答時の扱い、確定値表、確定後に更新する箇所、発出と回答の管理。</t>
+          <t>第9期19施策の評価表（受け皿）と、実績が揃わない場合の暫定評価ルール。施策別評価表、実績の入力様式、暫定評価ルール、現時点で判定できる成果評価、委員会用スコアカード。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>27件を照会先別に整理し、事業者への照会は5先に一本化した。未回答時の扱いを5類型（重複計上・回答の偏り・地区が不明・施設の未回答・見える化との不一致）で事前に定めている。確定値表10件のうち確定は2件（訪問介護員等181人、H12の20.4％）で、この2件は照会の結果によらず変わらない。確定後に更新する箇所11件を一覧化した。</t>
+          <t>評価を成果評価（アウトカム）とプロセス評価（実施状況）の2層に分け、成果評価は事業実績を要さず現時点で判定できることを示した。19施策のうち成果評価が可能10・調査による代理評価4・プロセス評価のみ5である。未受領年度は「未把握」と記載し、「実施されなかった」と書き分ける。委員会には成果指標12・補足指標4のスコアカードを示す。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>26 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1419,24 +1419,24 @@
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第11稿→第12稿_修正指示書.xlsx</t>
+          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第11稿から第12稿への修正の記録。修正の一覧、第9期評価の精緻化、アンケート集計分析の反映、人口推計の補正の反映、解消した確認事項、残る確認事項と次の作業。</t>
+          <t>実施済み3調査の点検事項のうち重大6件・要確認21件の照会票と、確定値の管理表。照会事項の一覧、事業者別の照会票、未回答時の扱い、確定値表、確定後に更新する箇所、発出と回答の管理。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>修正9件（差替2・是正1・追加6）。第9期19施策に調査の裏づけと代表KPIの対応で判定を付し（強5・中5・弱4・なし5）、施策の空白5領域を明らかにした。算定不可としていた代表KPI4項目（H07・H08・H12・H16）はいずれも代理指標により算定できることを確認し、削除する項目はない。訪問介護13事業所を全数把握（181人）し、高齢者世帯の記述を是正した。解消した確認事項5件、前提が変わった確認事項3件。</t>
+          <t>27件を照会先別に整理し、事業者への照会は5先に一本化した。未回答時の扱いを5類型（重複計上・回答の偏り・地区が不明・施設の未回答・見える化との不一致）で事前に定めている。確定値表10件のうち確定は2件（訪問介護員等181人、H12の20.4％）で、この2件は照会の結果によらず変わらない。確定後に更新する箇所11件を一覧化した。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1459,34 +1459,34 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画素案_第11稿→第12稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>概要版の頁数・体裁・掲載内容を定めるための構成案。位置付けと制約、3案の比較、推奨案の頁割、掲載する図表の候補、本編との対応と用語の言い換え、パブリックコメントとの関係と2版構成、決定を要する事項、レッドチームレビュー。</t>
+          <t>計画素案 第11稿から第12稿への修正の記録。修正の一覧、第9期評価の精緻化、アンケート集計分析の反映、人口推計の補正の反映、解消した確認事項、残る確認事項と次の作業。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>概要版はパブリックコメント（令和9年1月・2週間・WEB）に用いるため、「計画の要約」ではなく「何を決めようとしているのかが分かる文書」として設計する。A4判8頁（表紙＋本文6頁＋裏表紙）を推奨し、本編6章を1章1頁で割り付ける。パブリックコメントの時点では保険料が確定しないため、パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版構成とする。決定を要する事項6件を07シートに整理した。08シートのレッドチームレビュー8件には、本案の前提そのものへの指摘3件を含む。</t>
+          <t>修正9件（差替2・是正1・追加6）。第9期19施策に調査の裏づけと代表KPIの対応で判定を付し（強5・中5・弱4・なし5）、施策の空白5領域を明らかにした。算定不可としていた代表KPI4項目（H07・H08・H12・H16）はいずれも代理指標により算定できることを確認し、削除する項目はない。訪問介護13事業所を全数把握（181人）し、高齢者世帯の記述を是正した。解消した確認事項5件、前提が変わった確認事項3件。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -1499,34 +1499,34 @@
       <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールとレッドチームレビュー。</t>
+          <t>概要版の頁数・体裁・掲載内容を定めるための構成案。位置付けと制約、3案の比較、推奨案の頁割、掲載する図表の候補、本編との対応と用語の言い換え、パブリックコメントとの関係と2版構成、決定を要する事項、レッドチームレビュー。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率のみである。住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）により、社人研 令和5年推計の基準年から最初の推計年までの5年で突合した。3町計では65〜74歳を3年で3.8％上方に、75歳以上を0.7％下方に補正する。社人研は前期高齢者の減少を実績より速く見込んでいる。町別では75歳以上の向きが逆で、東川町が上方（＋3.2％）・東神楽町が下方（▲4.2％）・美瑛町が境界である。町別の適用は、町別の第1号被保険者数の受領まで保留する。</t>
+          <t>概要版はパブリックコメント（令和9年1月・2週間・WEB）に用いるため、「計画の要約」ではなく「何を決めようとしているのかが分かる文書」として設計する。A4判8頁（表紙＋本文6頁＋裏表紙）を推奨し、本編6章を1章1頁で割り付ける。パブリックコメントの時点では保険料が確定しないため、パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版構成とする。決定を要する事項6件を07シートに整理した。08シートのレッドチームレビュー8件には、本案の前提そのものへの指摘3件を含む。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1539,39 +1539,39 @@
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
+          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールとレッドチームレビュー。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
+          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率のみである。住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）により、社人研 令和5年推計の基準年から最初の推計年までの5年で突合した。3町計では65〜74歳を3年で3.8％上方に、75歳以上を0.7％下方に補正する。社人研は前期高齢者の減少を実績より速く見込んでいる。町別では75歳以上の向きが逆で、東川町が上方（＋3.2％）・東神楽町が下方（▲4.2％）・美瑛町が境界である。町別の適用は、町別の第1号被保険者数の受領まで保留する。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>第1稿</t>
         </is>
       </c>
     </row>
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
+          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
+          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>7シート</t>
         </is>
       </c>
     </row>
@@ -1626,32 +1626,32 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>第1回委員会に向けた確認事項の依頼文書。</t>
+          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
+          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>第9版</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1659,39 +1659,39 @@
       <c r="A29" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>第1回委員会に向けた確認事項の依頼文書。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第9版</t>
         </is>
       </c>
     </row>
@@ -1706,27 +1706,27 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -1739,34 +1739,34 @@
       <c r="A31" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1786,27 +1786,27 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1826,27 +1826,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -1859,34 +1859,34 @@
       <c r="A34" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -1906,27 +1906,27 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -1946,27 +1946,27 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -1986,27 +1986,27 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2106,27 +2106,27 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2146,27 +2146,27 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2186,27 +2186,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2226,27 +2226,27 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2266,17 +2266,17 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2306,27 +2306,27 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2346,27 +2346,27 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2386,27 +2386,27 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2466,27 +2466,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2499,39 +2499,39 @@
       <c r="A50" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2546,32 +2546,32 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -2586,27 +2586,27 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2619,34 +2619,34 @@
       <c r="A53" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="13" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2699,39 +2699,39 @@
       <c r="A55" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H55" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2746,27 +2746,27 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H56" s="16" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H57" s="16" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2866,88 +2866,108 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H59" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="52" customHeight="1">
+      <c r="A60" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E60" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr">
+      <c r="G60" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H59" s="16" t="inlineStr">
+      <c r="H60" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="17" t="inlineStr">
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="28" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr"/>
-      <c r="E62" s="3" t="inlineStr"/>
-      <c r="F62" s="3" t="inlineStr"/>
-      <c r="G62" s="3" t="inlineStr"/>
-      <c r="H62" s="3" t="inlineStr"/>
-    </row>
-    <row r="63" ht="32" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr"/>
+      <c r="E63" s="3" t="inlineStr"/>
+      <c r="F63" s="3" t="inlineStr"/>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第12稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D63" s="18" t="n"/>
-      <c r="E63" s="18" t="n"/>
-      <c r="F63" s="18" t="n"/>
-      <c r="G63" s="18" t="n"/>
-      <c r="H63" s="19" t="n"/>
-    </row>
-    <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="14" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B64" s="6" t="n">
@@ -2955,7 +2975,7 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第12稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D64" s="18" t="n"/>
@@ -2965,17 +2985,17 @@
       <c r="H64" s="19" t="n"/>
     </row>
     <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、レビュー指摘への対応と決定事項一覧、第10期計画素案_第11稿→第12稿_修正指示書、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D65" s="18" t="n"/>
@@ -2985,17 +3005,17 @@
       <c r="H65" s="19" t="n"/>
     </row>
     <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B66" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、レビュー指摘への対応と決定事項一覧、第10期計画素案_第11稿→第12稿_修正指示書、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D66" s="18" t="n"/>
@@ -3005,17 +3025,17 @@
       <c r="H66" s="19" t="n"/>
     </row>
     <row r="67" ht="32" customHeight="1">
-      <c r="A67" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D67" s="18" t="n"/>
@@ -3025,17 +3045,17 @@
       <c r="H67" s="19" t="n"/>
     </row>
     <row r="68" ht="32" customHeight="1">
-      <c r="A68" s="13" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B68" s="6" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D68" s="18" t="n"/>
@@ -3045,17 +3065,17 @@
       <c r="H68" s="19" t="n"/>
     </row>
     <row r="69" ht="32" customHeight="1">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D69" s="18" t="n"/>
@@ -3065,17 +3085,17 @@
       <c r="H69" s="19" t="n"/>
     </row>
     <row r="70" ht="32" customHeight="1">
-      <c r="A70" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B70" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D70" s="18" t="n"/>
@@ -3084,18 +3104,18 @@
       <c r="G70" s="18" t="n"/>
       <c r="H70" s="19" t="n"/>
     </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B71" s="20" t="n">
-        <v>55</v>
-      </c>
-      <c r="C71" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの50件、別スコープ5件</t>
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D71" s="18" t="n"/>
@@ -3104,8 +3124,28 @@
       <c r="G71" s="18" t="n"/>
       <c r="H71" s="19" t="n"/>
     </row>
-    <row r="73" ht="100" customHeight="1">
-      <c r="A73" s="21" t="inlineStr">
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B72" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="C72" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの51件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D72" s="18" t="n"/>
+      <c r="E72" s="18" t="n"/>
+      <c r="F72" s="18" t="n"/>
+      <c r="G72" s="18" t="n"/>
+      <c r="H72" s="19" t="n"/>
+    </row>
+    <row r="74" ht="100" customHeight="1">
+      <c r="A74" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -3113,17 +3153,17 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C63:H63"/>
+    <mergeCell ref="A74:H74"/>
     <mergeCell ref="C65:H65"/>
+    <mergeCell ref="A62:H62"/>
     <mergeCell ref="C71:H71"/>
-    <mergeCell ref="C68:H68"/>
     <mergeCell ref="C66:H66"/>
-    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C70:H70"/>
     <mergeCell ref="C69:H69"/>
     <mergeCell ref="C64:H64"/>
-    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="C68:H68"/>
+    <mergeCell ref="C72:H72"/>
     <mergeCell ref="C67:H67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1346,27 +1346,27 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_中間報告の根拠対照表.xlsx</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の工程末に提出する「第9期計画の評価・検証の中間報告」。本報告の位置づけ、評価の枠組み、成果評価の結果、構造評価の結果、不足している資料と確認事項、評価の確からしさ、9月以降の進め方。</t>
+          <t>中間報告に記載した主要な数値・主張について、出典・収録先・検算の方法を対照させた第三者検証用の索引。記述と根拠の対照39件、出典一覧12件、収録ファイルの一覧（ハッシュ付）、検証の手順10項目、検証できないこと。</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>評価を①成果評価②構造評価③プロセス評価の3層に分け、資料を要さない①②を8月に整理した。第9期代表KPI4項目は達成1・未達2・算定可1だが、未達2項目とも実態が悪化したとは言えない。19施策の評価可能性は強5・中5・弱4・なし5で、調査に所見があるのに施策がない5領域を特定した。評価を確定するために不足する資料7件・確認事項5件を洗い出した。③プロセス評価は資料の受領後（令和8年9月以降）である。</t>
+          <t>中間報告の記述を第三者が検証できるようにするためのもの。出典から直接確認できるもの30件と、受託者の判断や出典側の留保を伴うもの9件を分けている。05シートに「本集では検証できないこと」（個票・見える化δ・受託者の判断による抽出・未受領資料）を明示している。収録ファイルにはSHA-256ハッシュを付し、同一性を確認できる。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>75段落 11表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>47 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1386,27 +1386,27 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>第9期19施策の評価表（受け皿）と、実績が揃わない場合の暫定評価ルール。施策別評価表、実績の入力様式、暫定評価ルール、現時点で判定できる成果評価、委員会用スコアカード。</t>
+          <t>仕様書５の令和8年8月の工程末に提出する「第9期計画の評価・検証の中間報告」。本報告の位置づけ、評価の枠組み、成果評価の結果、構造評価の結果、不足している資料と確認事項、評価の確からしさ、9月以降の進め方。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>評価を成果評価（アウトカム）とプロセス評価（実施状況）の2層に分け、成果評価は事業実績を要さず現時点で判定できることを示した。19施策のうち成果評価が可能10・調査による代理評価4・プロセス評価のみ5である。未受領年度は「未把握」と記載し、「実施されなかった」と書き分ける。委員会には成果指標12・補足指標4のスコアカードを示す。</t>
+          <t>評価を①成果評価②構造評価③プロセス評価の3層に分け、資料を要さない①②を8月に整理した。第9期代表KPI4項目は達成1・未達2・算定可1だが、未達2項目とも実態が悪化したとは言えない。19施策の評価可能性は強5・中5・弱4・なし5で、調査に所見があるのに施策がない5領域を特定した。評価を確定するために不足する資料7件・確認事項5件を洗い出した。③プロセス評価は資料の受領後（令和8年9月以降）である。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>75段落 11表</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>26 KB</t>
+          <t>47 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1426,27 +1426,27 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>実施済み3調査の点検事項のうち重大6件・要確認21件の照会票と、確定値の管理表。照会事項の一覧、事業者別の照会票、未回答時の扱い、確定値表、確定後に更新する箇所、発出と回答の管理。</t>
+          <t>第9期19施策の評価表（受け皿）と、実績が揃わない場合の暫定評価ルール。施策別評価表、実績の入力様式、暫定評価ルール、現時点で判定できる成果評価、委員会用スコアカード。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>27件を照会先別に整理し、事業者への照会は5先に一本化した。未回答時の扱いを5類型（重複計上・回答の偏り・地区が不明・施設の未回答・見える化との不一致）で事前に定めている。確定値表10件のうち確定は2件（訪問介護員等181人、H12の20.4％）で、この2件は照会の結果によらず変わらない。確定後に更新する箇所11件を一覧化した。</t>
+          <t>評価を成果評価（アウトカム）とプロセス評価（実施状況）の2層に分け、成果評価は事業実績を要さず現時点で判定できることを示した。19施策のうち成果評価が可能10・調査による代理評価4・プロセス評価のみ5である。未受領年度は「未把握」と記載し、「実施されなかった」と書き分ける。委員会には成果指標12・補足指標4のスコアカードを示す。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>26 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1459,24 +1459,24 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第11稿→第12稿_修正指示書.xlsx</t>
+          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第11稿から第12稿への修正の記録。修正の一覧、第9期評価の精緻化、アンケート集計分析の反映、人口推計の補正の反映、解消した確認事項、残る確認事項と次の作業。</t>
+          <t>実施済み3調査の点検事項のうち重大6件・要確認21件の照会票と、確定値の管理表。照会事項の一覧、事業者別の照会票、未回答時の扱い、確定値表、確定後に更新する箇所、発出と回答の管理。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>修正9件（差替2・是正1・追加6）。第9期19施策に調査の裏づけと代表KPIの対応で判定を付し（強5・中5・弱4・なし5）、施策の空白5領域を明らかにした。算定不可としていた代表KPI4項目（H07・H08・H12・H16）はいずれも代理指標により算定できることを確認し、削除する項目はない。訪問介護13事業所を全数把握（181人）し、高齢者世帯の記述を是正した。解消した確認事項5件、前提が変わった確認事項3件。</t>
+          <t>27件を照会先別に整理し、事業者への照会は5先に一本化した。未回答時の扱いを5類型（重複計上・回答の偏り・地区が不明・施設の未回答・見える化との不一致）で事前に定めている。確定値表10件のうち確定は2件（訪問介護員等181人、H12の20.4％）で、この2件は照会の結果によらず変わらない。確定後に更新する箇所11件を一覧化した。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -1499,34 +1499,34 @@
       <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画素案_第11稿→第12稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>概要版の頁数・体裁・掲載内容を定めるための構成案。位置付けと制約、3案の比較、推奨案の頁割、掲載する図表の候補、本編との対応と用語の言い換え、パブリックコメントとの関係と2版構成、決定を要する事項、レッドチームレビュー。</t>
+          <t>計画素案 第11稿から第12稿への修正の記録。修正の一覧、第9期評価の精緻化、アンケート集計分析の反映、人口推計の補正の反映、解消した確認事項、残る確認事項と次の作業。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>概要版はパブリックコメント（令和9年1月・2週間・WEB）に用いるため、「計画の要約」ではなく「何を決めようとしているのかが分かる文書」として設計する。A4判8頁（表紙＋本文6頁＋裏表紙）を推奨し、本編6章を1章1頁で割り付ける。パブリックコメントの時点では保険料が確定しないため、パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版構成とする。決定を要する事項6件を07シートに整理した。08シートのレッドチームレビュー8件には、本案の前提そのものへの指摘3件を含む。</t>
+          <t>修正9件（差替2・是正1・追加6）。第9期19施策に調査の裏づけと代表KPIの対応で判定を付し（強5・中5・弱4・なし5）、施策の空白5領域を明らかにした。算定不可としていた代表KPI4項目（H07・H08・H12・H16）はいずれも代理指標により算定できることを確認し、削除する項目はない。訪問介護13事業所を全数把握（181人）し、高齢者世帯の記述を是正した。解消した確認事項5件、前提が変わった確認事項3件。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1539,34 +1539,34 @@
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールとレッドチームレビュー。</t>
+          <t>概要版の頁数・体裁・掲載内容を定めるための構成案。位置付けと制約、3案の比較、推奨案の頁割、掲載する図表の候補、本編との対応と用語の言い換え、パブリックコメントとの関係と2版構成、決定を要する事項、レッドチームレビュー。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率のみである。住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）により、社人研 令和5年推計の基準年から最初の推計年までの5年で突合した。3町計では65〜74歳を3年で3.8％上方に、75歳以上を0.7％下方に補正する。社人研は前期高齢者の減少を実績より速く見込んでいる。町別では75歳以上の向きが逆で、東川町が上方（＋3.2％）・東神楽町が下方（▲4.2％）・美瑛町が境界である。町別の適用は、町別の第1号被保険者数の受領まで保留する。</t>
+          <t>概要版はパブリックコメント（令和9年1月・2週間・WEB）に用いるため、「計画の要約」ではなく「何を決めようとしているのかが分かる文書」として設計する。A4判8頁（表紙＋本文6頁＋裏表紙）を推奨し、本編6章を1章1頁で割り付ける。パブリックコメントの時点では保険料が確定しないため、パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版構成とする。決定を要する事項6件を07シートに整理した。08シートのレッドチームレビュー8件には、本案の前提そのものへの指摘3件を含む。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1579,39 +1579,39 @@
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
+          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールとレッドチームレビュー。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
+          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率のみである。住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）により、社人研 令和5年推計の基準年から最初の推計年までの5年で突合した。3町計では65〜74歳を3年で3.8％上方に、75歳以上を0.7％下方に補正する。社人研は前期高齢者の減少を実績より速く見込んでいる。町別では75歳以上の向きが逆で、東川町が上方（＋3.2％）・東神楽町が下方（▲4.2％）・美瑛町が境界である。町別の適用は、町別の第1号被保険者数の受領まで保留する。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>第1稿</t>
         </is>
       </c>
     </row>
@@ -1626,32 +1626,32 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
+          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
+          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>7シート</t>
         </is>
       </c>
     </row>
@@ -1666,32 +1666,32 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>第1回委員会に向けた確認事項の依頼文書。</t>
+          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
+          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>第9版</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -1699,39 +1699,39 @@
       <c r="A30" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>第1回委員会に向けた確認事項の依頼文書。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第9版</t>
         </is>
       </c>
     </row>
@@ -1746,27 +1746,27 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1779,34 +1779,34 @@
       <c r="A32" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1826,27 +1826,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -1899,34 +1899,34 @@
       <c r="A35" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -1946,27 +1946,27 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -1986,27 +1986,27 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2026,27 +2026,27 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2106,17 +2106,17 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2146,27 +2146,27 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2186,27 +2186,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2226,27 +2226,27 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2266,27 +2266,27 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2346,27 +2346,27 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2386,27 +2386,27 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2466,27 +2466,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2506,27 +2506,27 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2539,39 +2539,39 @@
       <c r="A51" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2586,32 +2586,32 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>第6稿</t>
         </is>
       </c>
     </row>
@@ -2626,27 +2626,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2659,34 +2659,34 @@
       <c r="A54" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2706,17 +2706,17 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -2739,39 +2739,39 @@
       <c r="A56" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H56" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
         </is>
       </c>
     </row>
@@ -2786,27 +2786,27 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H57" s="16" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H58" s="16" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2906,88 +2906,108 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H60" s="16" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="52" customHeight="1">
+      <c r="A61" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E61" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G60" s="7" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H60" s="16" t="inlineStr">
+      <c r="H61" s="16" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="17" t="inlineStr">
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="17" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr"/>
-      <c r="E63" s="3" t="inlineStr"/>
-      <c r="F63" s="3" t="inlineStr"/>
-      <c r="G63" s="3" t="inlineStr"/>
-      <c r="H63" s="3" t="inlineStr"/>
-    </row>
-    <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr"/>
+      <c r="F64" s="3" t="inlineStr"/>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第12稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D64" s="18" t="n"/>
-      <c r="E64" s="18" t="n"/>
-      <c r="F64" s="18" t="n"/>
-      <c r="G64" s="18" t="n"/>
-      <c r="H64" s="19" t="n"/>
-    </row>
-    <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="14" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B65" s="6" t="n">
@@ -2995,7 +3015,7 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第12稿、図表集_白黒</t>
         </is>
       </c>
       <c r="D65" s="18" t="n"/>
@@ -3005,17 +3025,17 @@
       <c r="H65" s="19" t="n"/>
     </row>
     <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B66" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、レビュー指摘への対応と決定事項一覧、第10期計画素案_第11稿→第12稿_修正指示書、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D66" s="18" t="n"/>
@@ -3025,17 +3045,17 @@
       <c r="H66" s="19" t="n"/>
     </row>
     <row r="67" ht="32" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、レビュー指摘への対応と決定事項一覧、第10期計画素案_第11稿→第12稿_修正指示書、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D67" s="18" t="n"/>
@@ -3045,17 +3065,17 @@
       <c r="H67" s="19" t="n"/>
     </row>
     <row r="68" ht="32" customHeight="1">
-      <c r="A68" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B68" s="6" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D68" s="18" t="n"/>
@@ -3065,17 +3085,17 @@
       <c r="H68" s="19" t="n"/>
     </row>
     <row r="69" ht="32" customHeight="1">
-      <c r="A69" s="13" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D69" s="18" t="n"/>
@@ -3085,17 +3105,17 @@
       <c r="H69" s="19" t="n"/>
     </row>
     <row r="70" ht="32" customHeight="1">
-      <c r="A70" s="10" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B70" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
         </is>
       </c>
       <c r="D70" s="18" t="n"/>
@@ -3105,17 +3125,17 @@
       <c r="H70" s="19" t="n"/>
     </row>
     <row r="71" ht="32" customHeight="1">
-      <c r="A71" s="15" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D71" s="18" t="n"/>
@@ -3124,18 +3144,18 @@
       <c r="G71" s="18" t="n"/>
       <c r="H71" s="19" t="n"/>
     </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="20" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B72" s="20" t="n">
-        <v>56</v>
-      </c>
-      <c r="C72" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの51件、別スコープ5件</t>
+    <row r="72" ht="32" customHeight="1">
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D72" s="18" t="n"/>
@@ -3144,8 +3164,28 @@
       <c r="G72" s="18" t="n"/>
       <c r="H72" s="19" t="n"/>
     </row>
-    <row r="74" ht="100" customHeight="1">
-      <c r="A74" s="21" t="inlineStr">
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="20" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B73" s="20" t="n">
+        <v>57</v>
+      </c>
+      <c r="C73" s="20" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの52件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D73" s="18" t="n"/>
+      <c r="E73" s="18" t="n"/>
+      <c r="F73" s="18" t="n"/>
+      <c r="G73" s="18" t="n"/>
+      <c r="H73" s="19" t="n"/>
+    </row>
+    <row r="75" ht="100" customHeight="1">
+      <c r="A75" s="21" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -3153,15 +3193,15 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A74:H74"/>
     <mergeCell ref="C65:H65"/>
-    <mergeCell ref="A62:H62"/>
     <mergeCell ref="C71:H71"/>
     <mergeCell ref="C66:H66"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A63:H63"/>
     <mergeCell ref="C70:H70"/>
     <mergeCell ref="C69:H69"/>
-    <mergeCell ref="C64:H64"/>
+    <mergeCell ref="C73:H73"/>
+    <mergeCell ref="A75:H75"/>
     <mergeCell ref="C68:H68"/>
     <mergeCell ref="C72:H72"/>
     <mergeCell ref="C67:H67"/>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -81,6 +81,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E4DFEC"/>
         <bgColor rgb="00E4DFEC"/>
       </patternFill>
@@ -89,6 +95,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00DAEEF3"/>
         <bgColor rgb="00DAEEF3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -111,20 +123,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -198,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,7 +223,7 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -232,7 +232,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -243,22 +243,25 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -626,17 +629,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -694,6 +698,11 @@
           <t>状態</t>
         </is>
       </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>送付区分</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="4" t="n">
@@ -731,7 +740,12 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>第1稿</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -746,7 +760,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_素案_第12稿.docx</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -756,12 +770,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第11稿で第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映した。第12稿で第9期19施策の判定、施策の空白5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（667段落114表34図）。</t>
+          <t>計画そのもの。第6章の見込量・給付費・保険料は資料の受領を待つため［要協議］［要確認］［要内訳］としている。第2章第3節に施設・住まいの供給量・通常の事業実施地域・入退所の状況を、第5節に在宅生活改善調査を、第6節に介護人材実態調査の第10期分を反映している。令和8年8月時点で、第9期19施策の判定、調査に所見があるが対応する施策を確認できない5領域、訪問介護13事業所の全数把握、代表KPI4項目の振替、人口推計の補正を反映した（667段落114表34図）。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>667段落 114表</t>
+          <t>668段落 114表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -771,7 +785,12 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>第12稿（8次）</t>
+          <t>協議用素案（令和8年8月時点）（8次）</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -814,12 +833,17 @@
           <t>33シート133点</t>
         </is>
       </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
@@ -852,6 +876,11 @@
       <c r="H8" s="8" t="inlineStr">
         <is>
           <t>8シート</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -859,7 +888,7 @@
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>会議</t>
         </is>
@@ -892,6 +921,11 @@
       <c r="H9" s="8" t="inlineStr">
         <is>
           <t>校正反映版</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -899,7 +933,7 @@
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>会議</t>
         </is>
@@ -932,6 +966,11 @@
       <c r="H10" s="8" t="inlineStr">
         <is>
           <t>3シート</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -939,7 +978,7 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>会議</t>
         </is>
@@ -972,6 +1011,11 @@
       <c r="H11" s="8" t="inlineStr">
         <is>
           <t>1シート</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -979,7 +1023,7 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>会議</t>
         </is>
@@ -1012,6 +1056,11 @@
       <c r="H12" s="8" t="inlineStr">
         <is>
           <t>ODF形式</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1068,7 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>会議</t>
         </is>
@@ -1051,7 +1100,12 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>第1稿</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1113,7 @@
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>会議</t>
         </is>
@@ -1092,6 +1146,11 @@
       <c r="H14" s="8" t="inlineStr">
         <is>
           <t>8シート</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1158,7 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>会議</t>
         </is>
@@ -1131,7 +1190,12 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>第1稿</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1203,7 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>会議</t>
         </is>
@@ -1171,7 +1235,12 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>第1稿</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1248,7 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>第9期の評価</t>
         </is>
@@ -1191,12 +1260,12 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>第9期計画 第5章の19施策を洗い出し、実施済み4調査の設問及び代表KPI16項目と紐付けたうえで、レッドチーム方式（自らの整理を否定する立場）で点検した。</t>
+          <t>第9期計画 第5章の19施策を洗い出し、実施済み4調査の設問及び代表KPI16項目と紐付けたうえで、自己点検方式（自らの整理を批判的に検証する立場）で点検した。</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>代表KPIが対応しない施策が9施策（47.4％）、調査の裏づけがない施策が6施策（31.6％）、いずれもない施策が5施策（26.3％）である。05シートに、調査で強い所見があるのに施策がない5領域（移動・経済・意思決定支援・身寄りのない高齢者・未利用認定者）と、評価できない5施策の扱いを示している。04シートのレッドチームレビュー12件には、本表の枠組みそのものへの指摘2件を含む。</t>
+          <t>代表KPIが対応しない施策が9施策（47.4％）、調査の裏づけがない施策が6施策（31.6％）、いずれもない施策が5施策（26.3％）である。05シートに、調査で強い所見があるのに施策がない5領域（移動・経済・意思決定支援・身寄りのない高齢者・未利用認定者）と、評価できない5施策の扱いを示している。04シートの自己点検記録12件には、本表の枠組みそのものへの指摘2件を含む。</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1211,7 +1280,12 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>第1稿</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1293,7 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>工程管理</t>
         </is>
@@ -1251,7 +1325,12 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>第1稿</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1338,7 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
@@ -1291,7 +1370,12 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>第1稿</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -1299,39 +1383,44 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>工程管理</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー指摘への対応と決定事項一覧.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月18日のレビュー（Red Teamレビュー・進捗更新・次工程提案）の指摘13件への対応と、委員会決定事項一覧。指摘への対応、事実確認の結果、決定事項一覧、優先順位と期限、受入ゲートの充足状況、残る課題と当方の見解。</t>
+          <t>ご決定・ご確認をお願いする事項12件。選択肢、受託者の推奨案、決定しない場合の影響、決定者、期限、決定の優先順位、残る課題と受託者の見解。</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>指摘13件（P0 3・P1 5・P2 4・P3 1）はすべて事実であり、うち3件は当方の誤りであった（健康とくらしの調査の個票の記載、成果品一覧の基準日・版、エビデンス索引のZIP番号）。計画本文に残る［要協議］等90箇所を12件の決定事項に集約し、選択肢・推奨案・影響・決定者・期限を付した。最高優先は決定1（人口推計の基礎）・決定2（認定率のシナリオ）・決定7（調査の集計方法）の3件で、いずれも追加の資料を要さない。受入ゲート5件のうち充足1・一部充足2・未充足2。</t>
+          <t>計画本文に残る［要協議］63件・［要確認］15件・「未対応」7件・［要内訳］4件・「暫定」1件の計90箇所を、ご決定いただく単位で12件に集約したもの。最高優先は決定1（人口推計の基礎）・決定2（認定率のシナリオ）・決定7（調査の集計方法）の3件で、いずれも追加の資料を要さない。委員会にはこの一覧を用い、本文を直接お読みいただくことは想定していない。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>32 KB</t>
+          <t>19 KB</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>第1稿</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1428,7 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>第9期の評価</t>
         </is>
@@ -1366,12 +1455,17 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>第1稿</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1473,7 @@
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>第9期の評価</t>
         </is>
@@ -1401,17 +1495,22 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>75段落 11表</t>
+          <t>80段落 11表</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>47 KB</t>
+          <t>49 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>第1稿</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1518,7 @@
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>第9期の評価</t>
         </is>
@@ -1451,7 +1550,12 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>第1稿</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1563,7 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>第9期の評価</t>
         </is>
@@ -1491,7 +1595,12 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>第1稿</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -1499,19 +1608,19 @@
       <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>工程管理</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第11稿→第12稿_修正指示書.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第11稿から第12稿への修正の記録。修正の一覧、第9期評価の精緻化、アンケート集計分析の反映、人口推計の補正の反映、解消した確認事項、残る確認事項と次の作業。</t>
+          <t>計画素案から協議用素案（令和8年8月時点）への修正の記録。修正の一覧、第9期評価の精緻化、アンケート集計分析の反映、人口推計の補正の反映、解消した確認事項、残る確認事項と次の作業。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1531,7 +1640,12 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>第1稿</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1653,7 @@
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>設計</t>
         </is>
@@ -1551,12 +1665,12 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>概要版の頁数・体裁・掲載内容を定めるための構成案。位置付けと制約、3案の比較、推奨案の頁割、掲載する図表の候補、本編との対応と用語の言い換え、パブリックコメントとの関係と2版構成、決定を要する事項、レッドチームレビュー。</t>
+          <t>概要版の頁数・体裁・掲載内容を定めるための構成案。位置付けと制約、3案の比較、推奨案の頁割、掲載する図表の候補、本編との対応と用語の言い換え、パブリックコメントとの関係と2版構成、決定を要する事項、自己点検記録。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>概要版はパブリックコメント（令和9年1月・2週間・WEB）に用いるため、「計画の要約」ではなく「何を決めようとしているのかが分かる文書」として設計する。A4判8頁（表紙＋本文6頁＋裏表紙）を推奨し、本編6章を1章1頁で割り付ける。パブリックコメントの時点では保険料が確定しないため、パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版構成とする。決定を要する事項6件を07シートに整理した。08シートのレッドチームレビュー8件には、本案の前提そのものへの指摘3件を含む。</t>
+          <t>概要版はパブリックコメント（令和9年1月・2週間・WEB）に用いるため、「計画の要約」ではなく「何を決めようとしているのかが分かる文書」として設計する。A4判8頁（表紙＋本文6頁＋裏表紙）を推奨し、本編6章を1章1頁で割り付ける。パブリックコメントの時点では保険料が確定しないため、パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版構成とする。決定を要する事項6件を07シートに整理した。08シートの自己点検記録8件には、本案の前提そのものへの指摘3件を含む。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1571,7 +1685,12 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>第1稿</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1698,7 @@
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
@@ -1591,7 +1710,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールとレッドチームレビュー。</t>
+          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールと自己点検記録。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1611,7 +1730,12 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>第1稿</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1743,7 @@
       <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>発注者への依頼</t>
         </is>
@@ -1652,6 +1776,11 @@
       <c r="H28" s="8" t="inlineStr">
         <is>
           <t>7シート</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1788,7 @@
       <c r="A29" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>発注者への依頼</t>
         </is>
@@ -1692,6 +1821,11 @@
       <c r="H29" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1833,7 @@
       <c r="A30" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>発注者への依頼</t>
         </is>
@@ -1732,6 +1866,11 @@
       <c r="H30" s="8" t="inlineStr">
         <is>
           <t>第9版</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -1739,39 +1878,44 @@
       <c r="A31" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>工程管理</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>20 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -1779,39 +1923,44 @@
       <c r="A32" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>工程管理</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -1819,39 +1968,44 @@
       <c r="A33" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -1859,39 +2013,44 @@
       <c r="A34" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価のレッドチームレビュー.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘が的中し記述を訂正した。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -1899,39 +2058,44 @@
       <c r="A35" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>第9期の評価</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -1939,39 +2103,44 @@
       <c r="A36" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -1979,39 +2148,44 @@
       <c r="A37" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2019,39 +2193,44 @@
       <c r="A38" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2059,39 +2238,44 @@
       <c r="A39" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2099,39 +2283,44 @@
       <c r="A40" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2139,24 +2328,24 @@
       <c r="A41" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2166,12 +2355,17 @@
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2179,39 +2373,44 @@
       <c r="A42" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2219,39 +2418,44 @@
       <c r="A43" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2259,39 +2463,44 @@
       <c r="A44" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2299,39 +2508,44 @@
       <c r="A45" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2339,39 +2553,44 @@
       <c r="A46" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2379,39 +2598,44 @@
       <c r="A47" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2419,39 +2643,44 @@
       <c r="A48" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2459,39 +2688,44 @@
       <c r="A49" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2499,39 +2733,44 @@
       <c r="A50" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2539,39 +2778,44 @@
       <c r="A51" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2581,37 +2825,42 @@
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>会議</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_第6稿.docx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。第2稿に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>第6稿</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2621,37 +2870,42 @@
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>会議</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版・第2稿）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2659,39 +2913,44 @@
       <c r="A54" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="10" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>会議</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2699,39 +2958,44 @@
       <c r="A55" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="13" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2739,39 +3003,44 @@
       <c r="A56" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="13" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_第9稿→第10稿_修正指示書.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>第9稿から第10稿への修正指示66件（区分A20・B25・C21）。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
           <t>最新</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2781,37 +3050,42 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>別スコープ</t>
+          <t>設計</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H57" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>18 KB</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2821,37 +3095,42 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>別スコープ</t>
+          <t>設計</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
-        </is>
-      </c>
-      <c r="H58" s="16" t="inlineStr">
-        <is>
-          <t>参考</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I58" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2859,39 +3138,44 @@
       <c r="A59" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="15" t="inlineStr">
+      <c r="B59" s="17" t="inlineStr">
         <is>
           <t>別スコープ</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
-        </is>
-      </c>
-      <c r="H59" s="16" t="inlineStr">
+          <t>23 KB</t>
+        </is>
+      </c>
+      <c r="H59" s="18" t="inlineStr">
         <is>
           <t>参考</t>
+        </is>
+      </c>
+      <c r="I59" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
         </is>
       </c>
     </row>
@@ -2899,19 +3183,19 @@
       <c r="A60" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="15" t="inlineStr">
+      <c r="B60" s="17" t="inlineStr">
         <is>
           <t>別スコープ</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2926,12 +3210,17 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
-        </is>
-      </c>
-      <c r="H60" s="16" t="inlineStr">
+          <t>15 KB</t>
+        </is>
+      </c>
+      <c r="H60" s="18" t="inlineStr">
         <is>
           <t>参考</t>
+        </is>
+      </c>
+      <c r="I60" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
         </is>
       </c>
     </row>
@@ -2939,253 +3228,358 @@
       <c r="A61" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="15" t="inlineStr">
+      <c r="B61" s="17" t="inlineStr">
         <is>
           <t>別スコープ</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H61" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I61" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="52" customHeight="1">
+      <c r="A62" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H62" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I62" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="52" customHeight="1">
+      <c r="A63" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G61" s="7" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H61" s="16" t="inlineStr">
+      <c r="H63" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="17" t="inlineStr">
+      <c r="I63" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr"/>
-      <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" s="3" t="inlineStr"/>
-      <c r="G64" s="3" t="inlineStr"/>
-      <c r="H64" s="3" t="inlineStr"/>
-    </row>
-    <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr"/>
+      <c r="E66" s="3" t="inlineStr"/>
+      <c r="F66" s="3" t="inlineStr"/>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr"/>
+      <c r="I66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
         </is>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B67" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_素案_第12稿、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D65" s="18" t="n"/>
-      <c r="E65" s="18" t="n"/>
-      <c r="F65" s="18" t="n"/>
-      <c r="G65" s="18" t="n"/>
-      <c r="H65" s="19" t="n"/>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="14" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
+        </is>
+      </c>
+      <c r="D67" s="20" t="n"/>
+      <c r="E67" s="20" t="n"/>
+      <c r="F67" s="20" t="n"/>
+      <c r="G67" s="20" t="n"/>
+      <c r="H67" s="20" t="n"/>
+      <c r="I67" s="21" t="n"/>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="16" t="inlineStr">
         <is>
           <t>発注者への依頼</t>
         </is>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B68" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
-      <c r="D66" s="18" t="n"/>
-      <c r="E66" s="18" t="n"/>
-      <c r="F66" s="18" t="n"/>
-      <c r="G66" s="18" t="n"/>
-      <c r="H66" s="19" t="n"/>
-    </row>
-    <row r="67" ht="32" customHeight="1">
-      <c r="A67" s="12" t="inlineStr">
+      <c r="D68" s="20" t="n"/>
+      <c r="E68" s="20" t="n"/>
+      <c r="F68" s="20" t="n"/>
+      <c r="G68" s="20" t="n"/>
+      <c r="H68" s="20" t="n"/>
+      <c r="I68" s="21" t="n"/>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="14" t="inlineStr">
         <is>
           <t>工程管理</t>
         </is>
       </c>
-      <c r="B67" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>業務進捗報告書_令和8年8月分、レビュー指摘への対応と決定事項一覧、第10期計画素案_第11稿→第12稿_修正指示書、業務工程管理表、計画素案の別管理表</t>
-        </is>
-      </c>
-      <c r="D67" s="18" t="n"/>
-      <c r="E67" s="18" t="n"/>
-      <c r="F67" s="18" t="n"/>
-      <c r="G67" s="18" t="n"/>
-      <c r="H67" s="19" t="n"/>
-    </row>
-    <row r="68" ht="32" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価のレッドチームレビュー、主張の根拠水準の棚卸しと再レビュー</t>
-        </is>
-      </c>
-      <c r="D68" s="18" t="n"/>
-      <c r="E68" s="18" t="n"/>
-      <c r="F68" s="18" t="n"/>
-      <c r="G68" s="18" t="n"/>
-      <c r="H68" s="19" t="n"/>
-    </row>
-    <row r="69" ht="32" customHeight="1">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>分析</t>
-        </is>
-      </c>
       <c r="B69" s="6" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
-        </is>
-      </c>
-      <c r="D69" s="18" t="n"/>
-      <c r="E69" s="18" t="n"/>
-      <c r="F69" s="18" t="n"/>
-      <c r="G69" s="18" t="n"/>
-      <c r="H69" s="19" t="n"/>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+        </is>
+      </c>
+      <c r="D69" s="20" t="n"/>
+      <c r="E69" s="20" t="n"/>
+      <c r="F69" s="20" t="n"/>
+      <c r="G69" s="20" t="n"/>
+      <c r="H69" s="20" t="n"/>
+      <c r="I69" s="21" t="n"/>
     </row>
     <row r="70" ht="32" customHeight="1">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>設計</t>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B70" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_第9稿→第10稿_修正指示書</t>
-        </is>
-      </c>
-      <c r="D70" s="18" t="n"/>
-      <c r="E70" s="18" t="n"/>
-      <c r="F70" s="18" t="n"/>
-      <c r="G70" s="18" t="n"/>
-      <c r="H70" s="19" t="n"/>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+        </is>
+      </c>
+      <c r="D70" s="20" t="n"/>
+      <c r="E70" s="20" t="n"/>
+      <c r="F70" s="20" t="n"/>
+      <c r="G70" s="20" t="n"/>
+      <c r="H70" s="20" t="n"/>
+      <c r="I70" s="21" t="n"/>
     </row>
     <row r="71" ht="32" customHeight="1">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>会議</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_第6稿、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
-        </is>
-      </c>
-      <c r="D71" s="18" t="n"/>
-      <c r="E71" s="18" t="n"/>
-      <c r="F71" s="18" t="n"/>
-      <c r="G71" s="18" t="n"/>
-      <c r="H71" s="19" t="n"/>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+        </is>
+      </c>
+      <c r="D71" s="20" t="n"/>
+      <c r="E71" s="20" t="n"/>
+      <c r="F71" s="20" t="n"/>
+      <c r="G71" s="20" t="n"/>
+      <c r="H71" s="20" t="n"/>
+      <c r="I71" s="21" t="n"/>
     </row>
     <row r="72" ht="32" customHeight="1">
       <c r="A72" s="15" t="inlineStr">
         <is>
+          <t>設計</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+        </is>
+      </c>
+      <c r="D72" s="20" t="n"/>
+      <c r="E72" s="20" t="n"/>
+      <c r="F72" s="20" t="n"/>
+      <c r="G72" s="20" t="n"/>
+      <c r="H72" s="20" t="n"/>
+      <c r="I72" s="21" t="n"/>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+        </is>
+      </c>
+      <c r="D73" s="20" t="n"/>
+      <c r="E73" s="20" t="n"/>
+      <c r="F73" s="20" t="n"/>
+      <c r="G73" s="20" t="n"/>
+      <c r="H73" s="20" t="n"/>
+      <c r="I73" s="21" t="n"/>
+    </row>
+    <row r="74" ht="32" customHeight="1">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
           <t>別スコープ</t>
         </is>
       </c>
-      <c r="B72" s="6" t="n">
+      <c r="B74" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
-      <c r="D72" s="18" t="n"/>
-      <c r="E72" s="18" t="n"/>
-      <c r="F72" s="18" t="n"/>
-      <c r="G72" s="18" t="n"/>
-      <c r="H72" s="19" t="n"/>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="20" t="inlineStr">
+      <c r="D74" s="20" t="n"/>
+      <c r="E74" s="20" t="n"/>
+      <c r="F74" s="20" t="n"/>
+      <c r="G74" s="20" t="n"/>
+      <c r="H74" s="20" t="n"/>
+      <c r="I74" s="21" t="n"/>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="22" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B73" s="20" t="n">
-        <v>57</v>
-      </c>
-      <c r="C73" s="20" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの52件、別スコープ5件</t>
-        </is>
-      </c>
-      <c r="D73" s="18" t="n"/>
-      <c r="E73" s="18" t="n"/>
-      <c r="F73" s="18" t="n"/>
-      <c r="G73" s="18" t="n"/>
-      <c r="H73" s="19" t="n"/>
-    </row>
-    <row r="75" ht="100" customHeight="1">
-      <c r="A75" s="21" t="inlineStr">
+      <c r="B75" s="22" t="n">
+        <v>59</v>
+      </c>
+      <c r="C75" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの54件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D75" s="20" t="n"/>
+      <c r="E75" s="20" t="n"/>
+      <c r="F75" s="20" t="n"/>
+      <c r="G75" s="20" t="n"/>
+      <c r="H75" s="20" t="n"/>
+      <c r="I75" s="21" t="n"/>
+    </row>
+    <row r="77" ht="100" customHeight="1">
+      <c r="A77" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -3193,18 +3587,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C65:H65"/>
-    <mergeCell ref="C71:H71"/>
-    <mergeCell ref="C66:H66"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A63:H63"/>
-    <mergeCell ref="C70:H70"/>
-    <mergeCell ref="C69:H69"/>
-    <mergeCell ref="C73:H73"/>
-    <mergeCell ref="A75:H75"/>
-    <mergeCell ref="C68:H68"/>
-    <mergeCell ref="C72:H72"/>
-    <mergeCell ref="C67:H67"/>
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="C75:I75"/>
+    <mergeCell ref="C74:I74"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="C69:I69"/>
+    <mergeCell ref="C70:I70"/>
+    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="C73:I73"/>
+    <mergeCell ref="C68:I68"/>
+    <mergeCell ref="C72:I72"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C71:I71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3307,7 +3701,7 @@
         <is>
           <t>① 妥当性検証報告書 01_主要所見
 ② 第3章第5節（計画素案）
-③ レッドチームレビュー 08_対応の実施結果</t>
+③ 自己点検記録 08_対応の実施結果</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -3440,14 +3834,14 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>① キックオフ会議資料 第6稿
+          <t>① キックオフ会議資料（更新版・校正反映）
 ② キックオフ会議ヒアリングシート
 ③ キックオフ資料の点検結果 00_点検の結果（反映の経緯）</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>第6稿は、点検結果12件と青枠の仕分けに加え、人口推計の基礎の記述の修正、3調査の受領・点検の結果、将来推計の第2段階の試算、及び北海道の施設・住まいの名簿との突合を反映済みです。重大3件（事業所実態調査が業務範囲外、起点差の解消、H01の指標の変更）はいずれも本文に反映しました。ヒアリングシートは会議中にご記入いただく形式です。</t>
+          <t>会議資料は、点検結果12件と青枠の仕分けに加え、人口推計の基礎の記述の修正、3調査の受領・点検の結果、将来推計の第2段階の試算、及び北海道の施設・住まいの名簿との突合を反映済みです。重大3件（事業所実態調査が業務範囲外、起点差の解消、H01の指標の変更）はいずれも本文に反映しました。ヒアリングシートは会議中にご記入いただく形式です。</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -3484,7 +3878,7 @@
       </c>
     </row>
     <row r="14" ht="100" customHeight="1">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>注1）はじめてご覧いただく場合は、目的1（いま何をお願いしているか）からお読みいただくのが早いと思われます。注2）計画素案は、第1章から順にお読みいただく必要はありません。第3章（第9期の評価）と第6章（見込み）が議論の中心となります。注3）分析資料は、計画素案の記述の根拠を示すものです。計画素案の各節に「（第2章第2節）」のように参照を付しています。</t>
         </is>
@@ -3574,7 +3968,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_素案_第12稿.docx（667段落114表34図）</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx（667段落114表34図）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -3582,7 +3976,7 @@
           <t>本文の頁数と章別配分、図表の点数、図表のレイアウト。第6章の見込量・給付費・保険料。</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
@@ -3613,7 +4007,7 @@
           <t>概要版の頁数、体裁、掲載内容。</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -3643,7 +4037,7 @@
           <t>推計資料のうちサービス見込量・給付費・保険料算定表が未作成。</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
@@ -3665,7 +4059,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>確認依頼書（第9版）、必要事項の一覧、業務工程管理表、計画素案の別管理表、修正指示書、主張の棚卸し、レッドチームレビュー</t>
+          <t>確認依頼書（第9版）、必要事項の一覧、業務工程管理表、計画素案の別管理表、修正指示書、主張の棚卸し、自己点検記録</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -3673,7 +4067,7 @@
           <t>キックオフ会議資料及び委員会資料原案は日程確定後に作成。</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
@@ -3703,7 +4097,7 @@
           <t>第10節の決定・確認を要する事項12件。とくにNo.1（第9期の施策・事業実績）とNo.2（調査の点検事項）。</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
@@ -3725,7 +4119,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_素案_第12稿.docx</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -3733,7 +4127,7 @@
           <t>第6章の見込量・保険料。図表レイアウトの確認結果。</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
@@ -3763,7 +4157,7 @@
           <t>パブリックコメントの意見反映後に作成。</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -3775,7 +4169,7 @@
       </c>
     </row>
     <row r="13" ht="100" customHeight="1">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>注1）成果品は編集可能な電子データ及びPDF形式により提出いたします。図表、グラフ及び統計資料についても発注者が加工可能な形式で納品いたします。ただし現時点の分析資料のExcelは、生成スクリプトが算定した結果を書き出した「確定値の転記表」であり、セル内に計算式は入っておりません（第9版までの本欄には「計算式と元数値を保持」と記載しておりましたが、実態と異なるため改めました）。元数値はエビデンス集に、算定の手順は各成果品の「推計の方法」「算定方法」の欄に記載しております。入力値を変えて再計算する必要がある推計については、計算式を入れた「計算過程確認シート」を将来推計の成果品に付しております。注2）健康とくらしの調査の個票データ（4,729票）は令和8年8月に受領し、クロス集計・分析に用いております。個人情報を含むため、成果品及びエビデンス集には集計値のみを収録し、個票そのものは収録しておりません。この扱いでよいかご確認をお願いいたします（計画素案の別管理表 成果品No.7）。注3）PDFは最終組版時に一括して作成いたします。現時点ではWord・Excelのみをお渡ししております。注4）納品データは、成果物（本一覧の50件）とエビデンス（成果物の数値の根拠となるデータ）に分けてお渡しいたします。エビデンス集は納品物そのものではなく、上記No.3の「分析資料等の電子データ」の一部として、数値の検証と第11期への引継ぎのために添えるものです。成果物ZIP3本・エビデンスZIP2本の構成です。</t>
         </is>
@@ -3857,7 +4251,7 @@
           <t>圏域を統計単位と整備単位に分ける案。訪問・通所困難地域の定義。自給率の3町間の差が3町単位を裏付ける。</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>事業所の実施地域の受領待ち</t>
         </is>
@@ -3879,7 +4273,7 @@
           <t>特定地域の指定基準の判定。3町のうち美瑛町が該当の見込み。</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>告示待ち</t>
         </is>
@@ -3989,7 +4383,7 @@
           <t>令和22年度・令和32年度の人口と認定者数。</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>給付費は第3段階待ち</t>
         </is>
@@ -4003,7 +4397,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>妥当性検証報告書、レッドチームレビュー、認定率の年齢調整分析、地域差の分析13シート</t>
+          <t>妥当性検証報告書、自己点検記録、認定率の年齢調整分析、地域差の分析13シート</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -4011,7 +4405,7 @@
           <t>代表KPIの3軸評価。交付金評価。長期でみた到達点。</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>事業実績の受領待ち（プロセス評価）</t>
         </is>
@@ -4033,7 +4427,7 @@
           <t>代表KPI16項目のデータ源と基準値。</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>3調査の第10期分の受領待ち</t>
         </is>
@@ -4055,7 +4449,7 @@
           <t>5基本目標の5層構成。アウトプットとアウトカムの分離。</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>事業実績の受領待ち</t>
         </is>
@@ -4077,7 +4471,7 @@
           <t>階級別人口×階級別認定率。3シナリオ。</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>シナリオの決定待ち</t>
         </is>
@@ -4099,7 +4493,7 @@
           <t>要介護度別の利用率と単価により算定する。</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>要介護度別認定者数と給付実績の受領待ち</t>
         </is>
@@ -4121,7 +4515,7 @@
           <t>24時間対応サービスの確保方策。区域外の施設への依存。</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>定員・稼働の実績の受領待ち</t>
         </is>
@@ -4143,7 +4537,7 @@
           <t>第9期の剰余の確定。管内比較。16段階の妥当性。</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>決算・基金と政令改正待ち</t>
         </is>
@@ -4165,14 +4559,14 @@
           <t>基本指針の新別表11事項への対応表。図表番号一覧。</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>告示待ち</t>
         </is>
       </c>
     </row>
     <row r="21" ht="100" customHeight="1">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>注1）計画素案の第6章第2節から第7節は、いずれも資料の受領又は決定を待っています。第6章が計画の中心であるため、必要事項の一覧01シートの資料No.1・No.2・No.14の受領を最優先でお願いしております。注2）確定している箇所（第2章第1節から第4節）は、いずれも受領済のデータにより裏付けられています。根拠の水準は「主張の根拠水準の棚卸しと再レビュー」01シートに主張ごとに示しております。注3）本表は令和8年7月31日現在です。資料の受領及び決定により随時更新いたします。</t>
         </is>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>668段落 114表</t>
+          <t>669段落 114表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>48 KB</t>
+          <t>49 KB</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1405,12 +1405,12 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>19 KB</t>
+          <t>16 KB</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>修正9件（差替2・是正1・追加6）。第9期19施策に調査の裏づけと代表KPIの対応で判定を付し（強5・中5・弱4・なし5）、施策の空白5領域を明らかにした。算定不可としていた代表KPI4項目（H07・H08・H12・H16）はいずれも代理指標により算定できることを確認し、削除する項目はない。訪問介護13事業所を全数把握（181人）し、高齢者世帯の記述を是正した。解消した確認事項5件、前提が変わった確認事項3件。</t>
+          <t>修正9件（差替2・是正1・追加6）。第9期19施策に調査の裏づけと代表KPIの対応で判定を付し（強5・中5・弱4・なし5）、調査に所見があるが対応する施策を確認できない5領域を明らかにした。算定不可としていた代表KPI4項目（H07・H08・H12・H16）はいずれも代理指標により算定できることを確認し、削除する項目はない。訪問介護13事業所を全数把握（181人）し、高齢者世帯の記述を是正した。解消した確認事項5件、前提が変わった確認事項3件。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>20 KB</t>
+          <t>22 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>19 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1958,9 +1958,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -895,7 +895,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料（更新版）_校正反映.docx</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>反映済みの版は第10期計画_キックオフ会議議事録_校正反映.odt。ご指示への回答6件には、人口推計を総合戦略ベースの補正とすること、乖離の確認を65歳以上・75歳以上で行うこと、「令和8年実績」を年報・月報に改めること、農業収入と基金取崩しの因果を切り離すこと、算定できない代表KPI4項目（H07・H08・H12・H16）の扱い、事業所実態調査が受領済みであることを含む。</t>
+          <t>反映済みの版は第10期計画_キックオフ会議議事録_令和8年8月6日.odt。ご指示への回答6件には、人口推計を総合戦略ベースの補正とすること、乖離の確認を65歳以上・75歳以上で行うこと、「令和8年実績」を年報・月報に改めること、農業収入と基金取崩しの因果を切り離すこと、算定できない代表KPI4項目（H07・H08・H12・H16）の扱い、事業所実態調査が受領済みであることを含む。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_校正反映.odt</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -1885,37 +1885,37 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>22 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I31" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -1930,32 +1930,32 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>19 KB</t>
+          <t>22 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
@@ -1975,27 +1975,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>19 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -2003,9 +2003,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2020,27 +2020,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>53 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -2048,9 +2048,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2058,34 +2058,34 @@
       <c r="A35" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2138,9 +2138,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I36" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2155,27 +2155,27 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2193,34 +2193,34 @@
       <c r="A38" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2228,9 +2228,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2245,27 +2245,27 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2273,9 +2273,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2290,27 +2290,27 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2335,27 +2335,27 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2380,17 +2380,17 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2425,17 +2425,17 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2470,27 +2470,27 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2515,27 +2515,27 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2543,9 +2543,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2560,27 +2560,27 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2605,27 +2605,27 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2695,27 +2695,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2723,9 +2723,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2740,27 +2740,27 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2768,9 +2768,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2785,27 +2785,27 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2830,27 +2830,27 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2875,27 +2875,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2913,44 +2913,44 @@
       <c r="A54" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I54" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2965,32 +2965,32 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I55" s="12" t="inlineStr">
@@ -3010,27 +3010,27 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3038,9 +3038,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I56" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I56" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3048,34 +3048,34 @@
       <c r="A57" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3083,9 +3083,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3100,17 +3100,17 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3128,9 +3128,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I58" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3138,44 +3138,44 @@
       <c r="A59" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H59" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I59" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I59" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3190,27 +3190,27 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H60" s="18" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H61" s="18" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -3325,95 +3325,119 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H63" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I63" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="52" customHeight="1">
+      <c r="A64" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E64" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G63" s="7" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H63" s="18" t="inlineStr">
+      <c r="H64" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I63" s="18" t="inlineStr">
+      <c r="I64" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="19" t="inlineStr">
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr"/>
-      <c r="E66" s="3" t="inlineStr"/>
-      <c r="F66" s="3" t="inlineStr"/>
-      <c r="G66" s="3" t="inlineStr"/>
-      <c r="H66" s="3" t="inlineStr"/>
-      <c r="I66" s="3" t="inlineStr"/>
-    </row>
-    <row r="67" ht="32" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D67" s="20" t="n"/>
-      <c r="E67" s="20" t="n"/>
-      <c r="F67" s="20" t="n"/>
-      <c r="G67" s="20" t="n"/>
-      <c r="H67" s="20" t="n"/>
-      <c r="I67" s="21" t="n"/>
-    </row>
-    <row r="68" ht="32" customHeight="1">
-      <c r="A68" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B68" s="6" t="n">
@@ -3421,7 +3445,7 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D68" s="20" t="n"/>
@@ -3432,17 +3456,17 @@
       <c r="I68" s="21" t="n"/>
     </row>
     <row r="69" ht="32" customHeight="1">
-      <c r="A69" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D69" s="20" t="n"/>
@@ -3453,9 +3477,9 @@
       <c r="I69" s="21" t="n"/>
     </row>
     <row r="70" ht="32" customHeight="1">
-      <c r="A70" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B70" s="6" t="n">
@@ -3463,7 +3487,7 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D70" s="20" t="n"/>
@@ -3474,17 +3498,17 @@
       <c r="I70" s="21" t="n"/>
     </row>
     <row r="71" ht="32" customHeight="1">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D71" s="20" t="n"/>
@@ -3495,17 +3519,17 @@
       <c r="I71" s="21" t="n"/>
     </row>
     <row r="72" ht="32" customHeight="1">
-      <c r="A72" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D72" s="20" t="n"/>
@@ -3516,17 +3540,17 @@
       <c r="I72" s="21" t="n"/>
     </row>
     <row r="73" ht="32" customHeight="1">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B73" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）_校正反映、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_校正反映.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D73" s="20" t="n"/>
@@ -3537,17 +3561,17 @@
       <c r="I73" s="21" t="n"/>
     </row>
     <row r="74" ht="32" customHeight="1">
-      <c r="A74" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B74" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D74" s="20" t="n"/>
@@ -3557,18 +3581,18 @@
       <c r="H74" s="20" t="n"/>
       <c r="I74" s="21" t="n"/>
     </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B75" s="22" t="n">
-        <v>59</v>
-      </c>
-      <c r="C75" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの54件、別スコープ5件</t>
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D75" s="20" t="n"/>
@@ -3578,8 +3602,29 @@
       <c r="H75" s="20" t="n"/>
       <c r="I75" s="21" t="n"/>
     </row>
-    <row r="77" ht="100" customHeight="1">
-      <c r="A77" s="23" t="inlineStr">
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B76" s="22" t="n">
+        <v>60</v>
+      </c>
+      <c r="C76" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの55件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D76" s="20" t="n"/>
+      <c r="E76" s="20" t="n"/>
+      <c r="F76" s="20" t="n"/>
+      <c r="G76" s="20" t="n"/>
+      <c r="H76" s="20" t="n"/>
+      <c r="I76" s="21" t="n"/>
+    </row>
+    <row r="78" ht="100" customHeight="1">
+      <c r="A78" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -3587,17 +3632,17 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A65:I65"/>
     <mergeCell ref="C75:I75"/>
+    <mergeCell ref="A78:H78"/>
     <mergeCell ref="C74:I74"/>
-    <mergeCell ref="A2:I2"/>
     <mergeCell ref="C69:I69"/>
     <mergeCell ref="C70:I70"/>
-    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A66:I66"/>
     <mergeCell ref="C73:I73"/>
     <mergeCell ref="C68:I68"/>
     <mergeCell ref="C72:I72"/>
-    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C76:I76"/>
     <mergeCell ref="C71:I71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1495,12 +1495,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>80段落 11表</t>
+          <t>90段落 12表</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>49 KB</t>
+          <t>50 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>53 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>90段落 12表</t>
+          <t>92段落 13表</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>51 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1878,29 +1878,29 @@
       <c r="A31" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>令和8年8月25日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
@@ -1913,9 +1913,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -1930,37 +1930,37 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>22 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I32" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -1975,32 +1975,32 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>19 KB</t>
+          <t>22 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I33" s="12" t="inlineStr">
@@ -2020,27 +2020,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>19 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -2048,9 +2048,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2065,27 +2065,27 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>56 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -2093,9 +2093,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2103,34 +2103,34 @@
       <c r="A36" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2155,27 +2155,27 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2183,9 +2183,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I37" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2200,27 +2200,27 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2238,34 +2238,34 @@
       <c r="A39" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2273,9 +2273,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2290,27 +2290,27 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2318,9 +2318,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2335,27 +2335,27 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2380,27 +2380,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2425,17 +2425,17 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2515,27 +2515,27 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2560,27 +2560,27 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2588,9 +2588,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2605,27 +2605,27 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2650,27 +2650,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2695,17 +2695,17 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -2740,27 +2740,27 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2768,9 +2768,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2785,27 +2785,27 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2813,9 +2813,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2830,27 +2830,27 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2875,27 +2875,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2920,27 +2920,27 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2958,44 +2958,44 @@
       <c r="A55" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I55" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3010,32 +3010,32 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I56" s="12" t="inlineStr">
@@ -3055,27 +3055,27 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3083,9 +3083,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I57" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3093,34 +3093,34 @@
       <c r="A58" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3128,9 +3128,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3145,17 +3145,17 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3173,9 +3173,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I59" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3183,44 +3183,44 @@
       <c r="A60" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H60" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I60" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I60" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3235,27 +3235,27 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H61" s="18" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H62" s="18" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -3370,95 +3370,119 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H64" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="52" customHeight="1">
+      <c r="A65" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G64" s="7" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H64" s="18" t="inlineStr">
+      <c r="H65" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I64" s="18" t="inlineStr">
+      <c r="I65" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="19" t="inlineStr">
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="28" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr"/>
-      <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" s="3" t="inlineStr"/>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="3" t="inlineStr"/>
-      <c r="I67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68" ht="32" customHeight="1">
-      <c r="A68" s="5" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr"/>
+      <c r="E68" s="3" t="inlineStr"/>
+      <c r="F68" s="3" t="inlineStr"/>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr"/>
+      <c r="I68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D68" s="20" t="n"/>
-      <c r="E68" s="20" t="n"/>
-      <c r="F68" s="20" t="n"/>
-      <c r="G68" s="20" t="n"/>
-      <c r="H68" s="20" t="n"/>
-      <c r="I68" s="21" t="n"/>
-    </row>
-    <row r="69" ht="32" customHeight="1">
-      <c r="A69" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B69" s="6" t="n">
@@ -3466,7 +3490,7 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D69" s="20" t="n"/>
@@ -3477,17 +3501,17 @@
       <c r="I69" s="21" t="n"/>
     </row>
     <row r="70" ht="32" customHeight="1">
-      <c r="A70" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B70" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D70" s="20" t="n"/>
@@ -3498,9 +3522,9 @@
       <c r="I70" s="21" t="n"/>
     </row>
     <row r="71" ht="32" customHeight="1">
-      <c r="A71" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B71" s="6" t="n">
@@ -3508,7 +3532,7 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D71" s="20" t="n"/>
@@ -3519,17 +3543,17 @@
       <c r="I71" s="21" t="n"/>
     </row>
     <row r="72" ht="32" customHeight="1">
-      <c r="A72" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D72" s="20" t="n"/>
@@ -3540,17 +3564,17 @@
       <c r="I72" s="21" t="n"/>
     </row>
     <row r="73" ht="32" customHeight="1">
-      <c r="A73" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B73" s="6" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D73" s="20" t="n"/>
@@ -3561,17 +3585,17 @@
       <c r="I73" s="21" t="n"/>
     </row>
     <row r="74" ht="32" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A74" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B74" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D74" s="20" t="n"/>
@@ -3582,17 +3606,17 @@
       <c r="I74" s="21" t="n"/>
     </row>
     <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B75" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D75" s="20" t="n"/>
@@ -3602,18 +3626,18 @@
       <c r="H75" s="20" t="n"/>
       <c r="I75" s="21" t="n"/>
     </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B76" s="22" t="n">
-        <v>60</v>
-      </c>
-      <c r="C76" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの55件、別スコープ5件</t>
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D76" s="20" t="n"/>
@@ -3623,8 +3647,29 @@
       <c r="H76" s="20" t="n"/>
       <c r="I76" s="21" t="n"/>
     </row>
-    <row r="78" ht="100" customHeight="1">
-      <c r="A78" s="23" t="inlineStr">
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B77" s="22" t="n">
+        <v>61</v>
+      </c>
+      <c r="C77" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの56件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D77" s="20" t="n"/>
+      <c r="E77" s="20" t="n"/>
+      <c r="F77" s="20" t="n"/>
+      <c r="G77" s="20" t="n"/>
+      <c r="H77" s="20" t="n"/>
+      <c r="I77" s="21" t="n"/>
+    </row>
+    <row r="79" ht="100" customHeight="1">
+      <c r="A79" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -3633,15 +3678,15 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C75:I75"/>
-    <mergeCell ref="A78:H78"/>
     <mergeCell ref="C74:I74"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="C70:I70"/>
     <mergeCell ref="C69:I69"/>
-    <mergeCell ref="C70:I70"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A66:I66"/>
     <mergeCell ref="C73:I73"/>
-    <mergeCell ref="C68:I68"/>
+    <mergeCell ref="C77:I77"/>
+    <mergeCell ref="A67:I67"/>
     <mergeCell ref="C72:I72"/>
+    <mergeCell ref="A79:H79"/>
     <mergeCell ref="C76:I76"/>
     <mergeCell ref="C71:I71"/>
   </mergeCells>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1885,17 +1885,17 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月25日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1913,9 +1913,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -1923,29 +1923,29 @@
       <c r="A32" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>令和8年8月25日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -1958,9 +1958,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -1975,37 +1975,37 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>22 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I33" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2020,32 +2020,32 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>19 KB</t>
+          <t>22 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
@@ -2065,27 +2065,27 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>56 KB</t>
+          <t>19 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -2093,9 +2093,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2138,9 +2138,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2148,34 +2148,34 @@
       <c r="A37" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2200,27 +2200,27 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2228,9 +2228,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I38" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2245,27 +2245,27 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2283,34 +2283,34 @@
       <c r="A40" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2318,9 +2318,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2335,27 +2335,27 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2363,9 +2363,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2380,27 +2380,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2425,27 +2425,27 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2560,27 +2560,27 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2605,27 +2605,27 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2633,9 +2633,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I47" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2650,27 +2650,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2695,27 +2695,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -2785,27 +2785,27 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2813,9 +2813,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2830,27 +2830,27 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2858,9 +2858,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I52" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2875,27 +2875,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2920,27 +2920,27 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2965,27 +2965,27 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -3003,44 +3003,44 @@
       <c r="A56" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I56" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3055,32 +3055,32 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I57" s="12" t="inlineStr">
@@ -3100,27 +3100,27 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3128,9 +3128,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I58" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3138,34 +3138,34 @@
       <c r="A59" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3173,9 +3173,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3190,17 +3190,17 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -3218,9 +3218,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I60" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3228,44 +3228,44 @@
       <c r="A61" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H61" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I61" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I61" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3280,27 +3280,27 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H62" s="18" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H63" s="18" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -3415,95 +3415,119 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H65" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I65" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="52" customHeight="1">
+      <c r="A66" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E66" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G65" s="7" t="inlineStr">
+      <c r="G66" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H65" s="18" t="inlineStr">
+      <c r="H66" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I65" s="18" t="inlineStr">
+      <c r="I66" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="19" t="inlineStr">
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr"/>
-      <c r="E68" s="3" t="inlineStr"/>
-      <c r="F68" s="3" t="inlineStr"/>
-      <c r="G68" s="3" t="inlineStr"/>
-      <c r="H68" s="3" t="inlineStr"/>
-      <c r="I68" s="3" t="inlineStr"/>
-    </row>
-    <row r="69" ht="32" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr"/>
+      <c r="E69" s="3" t="inlineStr"/>
+      <c r="F69" s="3" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70" ht="32" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D69" s="20" t="n"/>
-      <c r="E69" s="20" t="n"/>
-      <c r="F69" s="20" t="n"/>
-      <c r="G69" s="20" t="n"/>
-      <c r="H69" s="20" t="n"/>
-      <c r="I69" s="21" t="n"/>
-    </row>
-    <row r="70" ht="32" customHeight="1">
-      <c r="A70" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B70" s="6" t="n">
@@ -3511,7 +3535,7 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D70" s="20" t="n"/>
@@ -3522,17 +3546,17 @@
       <c r="I70" s="21" t="n"/>
     </row>
     <row r="71" ht="32" customHeight="1">
-      <c r="A71" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D71" s="20" t="n"/>
@@ -3543,9 +3567,9 @@
       <c r="I71" s="21" t="n"/>
     </row>
     <row r="72" ht="32" customHeight="1">
-      <c r="A72" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B72" s="6" t="n">
@@ -3553,7 +3577,7 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D72" s="20" t="n"/>
@@ -3564,17 +3588,17 @@
       <c r="I72" s="21" t="n"/>
     </row>
     <row r="73" ht="32" customHeight="1">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B73" s="6" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D73" s="20" t="n"/>
@@ -3585,17 +3609,17 @@
       <c r="I73" s="21" t="n"/>
     </row>
     <row r="74" ht="32" customHeight="1">
-      <c r="A74" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B74" s="6" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D74" s="20" t="n"/>
@@ -3606,17 +3630,17 @@
       <c r="I74" s="21" t="n"/>
     </row>
     <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A75" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B75" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D75" s="20" t="n"/>
@@ -3627,17 +3651,17 @@
       <c r="I75" s="21" t="n"/>
     </row>
     <row r="76" ht="32" customHeight="1">
-      <c r="A76" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B76" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D76" s="20" t="n"/>
@@ -3647,18 +3671,18 @@
       <c r="H76" s="20" t="n"/>
       <c r="I76" s="21" t="n"/>
     </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B77" s="22" t="n">
-        <v>61</v>
-      </c>
-      <c r="C77" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの56件、別スコープ5件</t>
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D77" s="20" t="n"/>
@@ -3668,8 +3692,29 @@
       <c r="H77" s="20" t="n"/>
       <c r="I77" s="21" t="n"/>
     </row>
-    <row r="79" ht="100" customHeight="1">
-      <c r="A79" s="23" t="inlineStr">
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B78" s="22" t="n">
+        <v>62</v>
+      </c>
+      <c r="C78" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの57件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D78" s="20" t="n"/>
+      <c r="E78" s="20" t="n"/>
+      <c r="F78" s="20" t="n"/>
+      <c r="G78" s="20" t="n"/>
+      <c r="H78" s="20" t="n"/>
+      <c r="I78" s="21" t="n"/>
+    </row>
+    <row r="80" ht="100" customHeight="1">
+      <c r="A80" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -3677,16 +3722,16 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A80:H80"/>
     <mergeCell ref="C75:I75"/>
     <mergeCell ref="C74:I74"/>
+    <mergeCell ref="A68:I68"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C70:I70"/>
-    <mergeCell ref="C69:I69"/>
+    <mergeCell ref="C78:I78"/>
     <mergeCell ref="C73:I73"/>
     <mergeCell ref="C77:I77"/>
-    <mergeCell ref="A67:I67"/>
     <mergeCell ref="C72:I72"/>
-    <mergeCell ref="A79:H79"/>
     <mergeCell ref="C76:I76"/>
     <mergeCell ref="C71:I71"/>
   </mergeCells>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1885,17 +1885,17 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
+          <t>給付実績データ（大雪地区広域連合・東川町・東神楽町　令和6〜8年度）の受領点検。34サービス×7要介護度の月平均利用者数・1人1月あたり利用回数・1人1月あたり給付費、給付費の総額と第9期計画との乖離。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
+          <t>個人情報の取扱いについてご確認をお願いする事項を00シートに掲げている。代表KPI H15の乖離率は、分母を標準給付費見込額とすると▲1.37％、総給付費とすると＋5.49％となる。分母の定義のご決定を要する。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>21 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1913,9 +1913,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -1930,17 +1930,17 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月25日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1958,9 +1958,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -1968,29 +1968,29 @@
       <c r="A33" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>令和8年8月25日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -2003,9 +2003,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2020,37 +2020,37 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>22 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I34" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2065,32 +2065,32 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>19 KB</t>
+          <t>22 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>19 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2138,9 +2138,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2155,27 +2155,27 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>58 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2183,9 +2183,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2193,34 +2193,34 @@
       <c r="A38" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2245,27 +2245,27 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2273,9 +2273,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2290,27 +2290,27 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2328,34 +2328,34 @@
       <c r="A41" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2363,9 +2363,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2380,27 +2380,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2408,9 +2408,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2425,27 +2425,27 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2470,27 +2470,27 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2605,27 +2605,27 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2650,27 +2650,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2678,9 +2678,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2695,27 +2695,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2740,27 +2740,27 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2785,17 +2785,17 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -2830,27 +2830,27 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2858,9 +2858,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2875,27 +2875,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2903,9 +2903,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2920,27 +2920,27 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2965,27 +2965,27 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -3010,27 +3010,27 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3048,44 +3048,44 @@
       <c r="A57" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I57" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3100,32 +3100,32 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I58" s="12" t="inlineStr">
@@ -3145,27 +3145,27 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3173,9 +3173,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I59" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I59" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3183,34 +3183,34 @@
       <c r="A60" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -3218,9 +3218,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3235,17 +3235,17 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3263,9 +3263,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I61" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3273,44 +3273,44 @@
       <c r="A62" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H62" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I62" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I62" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3325,27 +3325,27 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H63" s="18" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H64" s="18" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -3460,95 +3460,119 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H66" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I66" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="52" customHeight="1">
+      <c r="A67" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G66" s="7" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H66" s="18" t="inlineStr">
+      <c r="H67" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I66" s="18" t="inlineStr">
+      <c r="I67" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="19" t="inlineStr">
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="28" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr"/>
-      <c r="E69" s="3" t="inlineStr"/>
-      <c r="F69" s="3" t="inlineStr"/>
-      <c r="G69" s="3" t="inlineStr"/>
-      <c r="H69" s="3" t="inlineStr"/>
-      <c r="I69" s="3" t="inlineStr"/>
-    </row>
-    <row r="70" ht="32" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="3" t="inlineStr"/>
+      <c r="F70" s="3" t="inlineStr"/>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr"/>
+      <c r="I70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D70" s="20" t="n"/>
-      <c r="E70" s="20" t="n"/>
-      <c r="F70" s="20" t="n"/>
-      <c r="G70" s="20" t="n"/>
-      <c r="H70" s="20" t="n"/>
-      <c r="I70" s="21" t="n"/>
-    </row>
-    <row r="71" ht="32" customHeight="1">
-      <c r="A71" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B71" s="6" t="n">
@@ -3556,7 +3580,7 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D71" s="20" t="n"/>
@@ -3567,17 +3591,17 @@
       <c r="I71" s="21" t="n"/>
     </row>
     <row r="72" ht="32" customHeight="1">
-      <c r="A72" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A72" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D72" s="20" t="n"/>
@@ -3588,9 +3612,9 @@
       <c r="I72" s="21" t="n"/>
     </row>
     <row r="73" ht="32" customHeight="1">
-      <c r="A73" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B73" s="6" t="n">
@@ -3598,7 +3622,7 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D73" s="20" t="n"/>
@@ -3609,17 +3633,17 @@
       <c r="I73" s="21" t="n"/>
     </row>
     <row r="74" ht="32" customHeight="1">
-      <c r="A74" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B74" s="6" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D74" s="20" t="n"/>
@@ -3630,17 +3654,17 @@
       <c r="I74" s="21" t="n"/>
     </row>
     <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B75" s="6" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D75" s="20" t="n"/>
@@ -3651,17 +3675,17 @@
       <c r="I75" s="21" t="n"/>
     </row>
     <row r="76" ht="32" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A76" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B76" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D76" s="20" t="n"/>
@@ -3672,17 +3696,17 @@
       <c r="I76" s="21" t="n"/>
     </row>
     <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B77" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D77" s="20" t="n"/>
@@ -3692,18 +3716,18 @@
       <c r="H77" s="20" t="n"/>
       <c r="I77" s="21" t="n"/>
     </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B78" s="22" t="n">
-        <v>62</v>
-      </c>
-      <c r="C78" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの57件、別スコープ5件</t>
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D78" s="20" t="n"/>
@@ -3713,8 +3737,29 @@
       <c r="H78" s="20" t="n"/>
       <c r="I78" s="21" t="n"/>
     </row>
-    <row r="80" ht="100" customHeight="1">
-      <c r="A80" s="23" t="inlineStr">
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B79" s="22" t="n">
+        <v>63</v>
+      </c>
+      <c r="C79" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの58件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D79" s="20" t="n"/>
+      <c r="E79" s="20" t="n"/>
+      <c r="F79" s="20" t="n"/>
+      <c r="G79" s="20" t="n"/>
+      <c r="H79" s="20" t="n"/>
+      <c r="I79" s="21" t="n"/>
+    </row>
+    <row r="81" ht="100" customHeight="1">
+      <c r="A81" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -3722,16 +3767,16 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A80:H80"/>
     <mergeCell ref="C75:I75"/>
     <mergeCell ref="C74:I74"/>
-    <mergeCell ref="A68:I68"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="C70:I70"/>
     <mergeCell ref="C78:I78"/>
+    <mergeCell ref="C79:I79"/>
+    <mergeCell ref="A81:H81"/>
     <mergeCell ref="C73:I73"/>
     <mergeCell ref="C77:I77"/>
     <mergeCell ref="C72:I72"/>
+    <mergeCell ref="A69:I69"/>
     <mergeCell ref="C76:I76"/>
     <mergeCell ref="C71:I71"/>
   </mergeCells>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1815,7 +1815,7 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>21 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1765,12 +1765,12 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>29 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -2175,7 +2175,7 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>58 KB</t>
+          <t>59 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月25日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1815,7 +1815,7 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>43 KB</t>
+          <t>44 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>59 KB</t>
+          <t>60 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1815,7 +1815,7 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>44 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1815,7 +1815,7 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>43 KB</t>
+          <t>44 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>19 KB</t>
+          <t>20 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>60 KB</t>
+          <t>61 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -2175,7 +2175,7 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>61 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1930,27 +1930,27 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
+          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
+          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1975,27 +1975,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -2003,9 +2003,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2013,34 +2013,34 @@
       <c r="A34" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -2058,24 +2058,24 @@
       <c r="A35" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2085,17 +2085,17 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>22 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I35" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2103,34 +2103,34 @@
       <c r="A36" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>20 KB</t>
+          <t>14 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2138,9 +2138,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I36" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2148,34 +2148,34 @@
       <c r="A37" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2193,34 +2193,34 @@
       <c r="A38" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2238,34 +2238,34 @@
       <c r="A39" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>16 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2273,9 +2273,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2283,39 +2283,39 @@
       <c r="A40" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>22 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
@@ -2328,34 +2328,34 @@
       <c r="A41" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>20 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2373,34 +2373,34 @@
       <c r="A42" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>64 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2418,34 +2418,34 @@
       <c r="A43" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2463,34 +2463,34 @@
       <c r="A44" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2508,24 +2508,24 @@
       <c r="A45" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2543,9 +2543,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2553,34 +2553,34 @@
       <c r="A46" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2588,9 +2588,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2605,27 +2605,27 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2633,9 +2633,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2650,27 +2650,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2695,22 +2695,22 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -2723,9 +2723,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2740,27 +2740,27 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2768,9 +2768,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2785,27 +2785,27 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2813,9 +2813,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2830,27 +2830,27 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2858,9 +2858,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I52" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2875,27 +2875,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2920,27 +2920,27 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2965,27 +2965,27 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -3010,27 +3010,27 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3055,17 +3055,17 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3093,44 +3093,44 @@
       <c r="A58" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I58" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3138,34 +3138,34 @@
       <c r="A59" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3173,9 +3173,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I59" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3183,34 +3183,34 @@
       <c r="A60" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -3228,34 +3228,34 @@
       <c r="A61" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3263,9 +3263,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3273,34 +3273,34 @@
       <c r="A62" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -3308,9 +3308,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I62" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3318,44 +3318,44 @@
       <c r="A63" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H63" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I63" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>54 KB</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I63" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3363,44 +3363,44 @@
       <c r="A64" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
-        </is>
-      </c>
-      <c r="H64" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I64" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>35 KB</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I64" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3408,44 +3408,44 @@
       <c r="A65" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
-        </is>
-      </c>
-      <c r="H65" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I65" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>52 KB</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3453,44 +3453,44 @@
       <c r="A66" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
-        </is>
-      </c>
-      <c r="H66" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I66" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>18 KB</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3498,186 +3498,306 @@
       <c r="A67" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="17" t="inlineStr">
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>修正の履歴。反映済み57件。</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I67" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="52" customHeight="1">
+      <c r="A68" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
         <is>
           <t>別スコープ</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表.xlsx</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>10シート</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>23 KB</t>
+        </is>
+      </c>
+      <c r="H68" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I68" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="52" customHeight="1">
+      <c r="A69" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>01_共通_基本コラム部品.xlsx</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>3計画に共通する基本コラム部品。</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>15 KB</t>
+        </is>
+      </c>
+      <c r="H69" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I69" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="52" customHeight="1">
+      <c r="A70" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H70" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I70" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="52" customHeight="1">
+      <c r="A71" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H71" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I71" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="52" customHeight="1">
+      <c r="A72" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D72" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E72" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G67" s="7" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H67" s="18" t="inlineStr">
+      <c r="H72" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I67" s="18" t="inlineStr">
+      <c r="I72" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="19" t="inlineStr">
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+    <row r="75" ht="28" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr"/>
-      <c r="E70" s="3" t="inlineStr"/>
-      <c r="F70" s="3" t="inlineStr"/>
-      <c r="G70" s="3" t="inlineStr"/>
-      <c r="H70" s="3" t="inlineStr"/>
-      <c r="I70" s="3" t="inlineStr"/>
-    </row>
-    <row r="71" ht="32" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr"/>
+      <c r="E75" s="3" t="inlineStr"/>
+      <c r="F75" s="3" t="inlineStr"/>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D71" s="20" t="n"/>
-      <c r="E71" s="20" t="n"/>
-      <c r="F71" s="20" t="n"/>
-      <c r="G71" s="20" t="n"/>
-      <c r="H71" s="20" t="n"/>
-      <c r="I71" s="21" t="n"/>
-    </row>
-    <row r="72" ht="32" customHeight="1">
-      <c r="A72" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
-        </is>
-      </c>
-      <c r="D72" s="20" t="n"/>
-      <c r="E72" s="20" t="n"/>
-      <c r="F72" s="20" t="n"/>
-      <c r="G72" s="20" t="n"/>
-      <c r="H72" s="20" t="n"/>
-      <c r="I72" s="21" t="n"/>
-    </row>
-    <row r="73" ht="32" customHeight="1">
-      <c r="A73" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
-        </is>
-      </c>
-      <c r="D73" s="20" t="n"/>
-      <c r="E73" s="20" t="n"/>
-      <c r="F73" s="20" t="n"/>
-      <c r="G73" s="20" t="n"/>
-      <c r="H73" s="20" t="n"/>
-      <c r="I73" s="21" t="n"/>
-    </row>
-    <row r="74" ht="32" customHeight="1">
-      <c r="A74" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
-        </is>
-      </c>
-      <c r="D74" s="20" t="n"/>
-      <c r="E74" s="20" t="n"/>
-      <c r="F74" s="20" t="n"/>
-      <c r="G74" s="20" t="n"/>
-      <c r="H74" s="20" t="n"/>
-      <c r="I74" s="21" t="n"/>
-    </row>
-    <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
-        </is>
-      </c>
-      <c r="D75" s="20" t="n"/>
-      <c r="E75" s="20" t="n"/>
-      <c r="F75" s="20" t="n"/>
-      <c r="G75" s="20" t="n"/>
-      <c r="H75" s="20" t="n"/>
-      <c r="I75" s="21" t="n"/>
-    </row>
-    <row r="76" ht="32" customHeight="1">
-      <c r="A76" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
         </is>
       </c>
       <c r="B76" s="6" t="n">
@@ -3685,7 +3805,7 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D76" s="20" t="n"/>
@@ -3696,17 +3816,17 @@
       <c r="I76" s="21" t="n"/>
     </row>
     <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A77" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B77" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D77" s="20" t="n"/>
@@ -3717,17 +3837,17 @@
       <c r="I77" s="21" t="n"/>
     </row>
     <row r="78" ht="32" customHeight="1">
-      <c r="A78" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B78" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D78" s="20" t="n"/>
@@ -3737,18 +3857,18 @@
       <c r="H78" s="20" t="n"/>
       <c r="I78" s="21" t="n"/>
     </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B79" s="22" t="n">
-        <v>63</v>
-      </c>
-      <c r="C79" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの58件、別スコープ5件</t>
+    <row r="79" ht="32" customHeight="1">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D79" s="20" t="n"/>
@@ -3758,8 +3878,113 @@
       <c r="H79" s="20" t="n"/>
       <c r="I79" s="21" t="n"/>
     </row>
-    <row r="81" ht="100" customHeight="1">
-      <c r="A81" s="23" t="inlineStr">
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+        </is>
+      </c>
+      <c r="D80" s="20" t="n"/>
+      <c r="E80" s="20" t="n"/>
+      <c r="F80" s="20" t="n"/>
+      <c r="G80" s="20" t="n"/>
+      <c r="H80" s="20" t="n"/>
+      <c r="I80" s="21" t="n"/>
+    </row>
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>概要版の構成案、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+        </is>
+      </c>
+      <c r="D81" s="20" t="n"/>
+      <c r="E81" s="20" t="n"/>
+      <c r="F81" s="20" t="n"/>
+      <c r="G81" s="20" t="n"/>
+      <c r="H81" s="20" t="n"/>
+      <c r="I81" s="21" t="n"/>
+    </row>
+    <row r="82" ht="32" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+        </is>
+      </c>
+      <c r="D82" s="20" t="n"/>
+      <c r="E82" s="20" t="n"/>
+      <c r="F82" s="20" t="n"/>
+      <c r="G82" s="20" t="n"/>
+      <c r="H82" s="20" t="n"/>
+      <c r="I82" s="21" t="n"/>
+    </row>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+        </is>
+      </c>
+      <c r="D83" s="20" t="n"/>
+      <c r="E83" s="20" t="n"/>
+      <c r="F83" s="20" t="n"/>
+      <c r="G83" s="20" t="n"/>
+      <c r="H83" s="20" t="n"/>
+      <c r="I83" s="21" t="n"/>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B84" s="22" t="n">
+        <v>68</v>
+      </c>
+      <c r="C84" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの63件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D84" s="20" t="n"/>
+      <c r="E84" s="20" t="n"/>
+      <c r="F84" s="20" t="n"/>
+      <c r="G84" s="20" t="n"/>
+      <c r="H84" s="20" t="n"/>
+      <c r="I84" s="21" t="n"/>
+    </row>
+    <row r="86" ht="100" customHeight="1">
+      <c r="A86" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -3767,18 +3992,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C75:I75"/>
-    <mergeCell ref="C74:I74"/>
+    <mergeCell ref="C84:I84"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A86:H86"/>
+    <mergeCell ref="C80:I80"/>
     <mergeCell ref="C78:I78"/>
     <mergeCell ref="C79:I79"/>
-    <mergeCell ref="A81:H81"/>
-    <mergeCell ref="C73:I73"/>
+    <mergeCell ref="C82:I82"/>
     <mergeCell ref="C77:I77"/>
-    <mergeCell ref="C72:I72"/>
-    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="C83:I83"/>
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="C81:I81"/>
     <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C71:I71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>669段落 114表</t>
+          <t>717段落 122表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>92段落 13表</t>
+          <t>103段落 15表</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>51 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>26 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -775,7 +775,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>717段落 122表</t>
+          <t>728段落 124表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1930,27 +1930,27 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
+          <t>将来推計 第3段階。標準給付費見込額・地域支援事業費・第1号被保険者負担分・調整交付金・基金取崩額から保険料基準額までを組み立てたもの（11シート）。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
+          <t>第9期の算定を再現すると公表値6,428円と一致する。基本ケースの暫定値は月額6,684円で、第9期の条例基準額6,400円を284円上回る。感度分析8件のうち最も大きいレバーは給付費の水準で幅は455円。確定を要する事項9件を10シートに掲げている。確定値ではない。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>11シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1958,9 +1958,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -1975,27 +1975,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
+          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
+          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -2020,17 +2020,17 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
+          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
+          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -2065,17 +2065,17 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
+          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -2103,34 +2103,34 @@
       <c r="A36" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
+          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
+          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>14 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2138,9 +2138,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2148,34 +2148,34 @@
       <c r="A37" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
+          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
+          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>14 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2183,9 +2183,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2200,17 +2200,17 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2228,9 +2228,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2238,34 +2238,34 @@
       <c r="A39" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2273,9 +2273,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2290,37 +2290,37 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>22 KB</t>
+          <t>16 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I40" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2335,32 +2335,32 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>20 KB</t>
+          <t>22 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr">
@@ -2380,27 +2380,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>64 KB</t>
+          <t>20 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2408,9 +2408,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2425,27 +2425,27 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>43 KB</t>
+          <t>65 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2453,9 +2453,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2463,34 +2463,34 @@
       <c r="A44" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2515,27 +2515,27 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2543,9 +2543,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2560,27 +2560,27 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2598,34 +2598,34 @@
       <c r="A47" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2633,9 +2633,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I47" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2650,27 +2650,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2678,9 +2678,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2695,27 +2695,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2740,27 +2740,27 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2785,17 +2785,17 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2830,17 +2830,17 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2875,27 +2875,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2920,27 +2920,27 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2948,9 +2948,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I54" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2965,27 +2965,27 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -3010,27 +3010,27 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3055,17 +3055,17 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3100,27 +3100,27 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3128,9 +3128,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3145,27 +3145,27 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3173,9 +3173,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I59" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3190,27 +3190,27 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -3235,27 +3235,27 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3280,27 +3280,27 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -3318,44 +3318,44 @@
       <c r="A63" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I63" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3370,32 +3370,32 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I64" s="12" t="inlineStr">
@@ -3415,27 +3415,27 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -3443,9 +3443,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I65" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3453,34 +3453,34 @@
       <c r="A66" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -3488,9 +3488,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3505,17 +3505,17 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -3533,9 +3533,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I67" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3543,44 +3543,44 @@
       <c r="A68" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H68" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I68" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I68" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3595,27 +3595,27 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H69" s="18" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H70" s="18" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -3730,95 +3730,119 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H72" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I72" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="52" customHeight="1">
+      <c r="A73" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E73" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="F73" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G72" s="7" t="inlineStr">
+      <c r="G73" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H72" s="18" t="inlineStr">
+      <c r="H73" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I72" s="18" t="inlineStr">
+      <c r="I73" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="19" t="inlineStr">
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="28" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr"/>
-      <c r="E75" s="3" t="inlineStr"/>
-      <c r="F75" s="3" t="inlineStr"/>
-      <c r="G75" s="3" t="inlineStr"/>
-      <c r="H75" s="3" t="inlineStr"/>
-      <c r="I75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76" ht="32" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr"/>
+      <c r="E76" s="3" t="inlineStr"/>
+      <c r="F76" s="3" t="inlineStr"/>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D76" s="20" t="n"/>
-      <c r="E76" s="20" t="n"/>
-      <c r="F76" s="20" t="n"/>
-      <c r="G76" s="20" t="n"/>
-      <c r="H76" s="20" t="n"/>
-      <c r="I76" s="21" t="n"/>
-    </row>
-    <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B77" s="6" t="n">
@@ -3826,7 +3850,7 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D77" s="20" t="n"/>
@@ -3837,17 +3861,17 @@
       <c r="I77" s="21" t="n"/>
     </row>
     <row r="78" ht="32" customHeight="1">
-      <c r="A78" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B78" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D78" s="20" t="n"/>
@@ -3858,9 +3882,9 @@
       <c r="I78" s="21" t="n"/>
     </row>
     <row r="79" ht="32" customHeight="1">
-      <c r="A79" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B79" s="6" t="n">
@@ -3868,7 +3892,7 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D79" s="20" t="n"/>
@@ -3879,17 +3903,17 @@
       <c r="I79" s="21" t="n"/>
     </row>
     <row r="80" ht="32" customHeight="1">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B80" s="6" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D80" s="20" t="n"/>
@@ -3900,17 +3924,17 @@
       <c r="I80" s="21" t="n"/>
     </row>
     <row r="81" ht="32" customHeight="1">
-      <c r="A81" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B81" s="6" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、将来推計_第3段階_給付費と保険料、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D81" s="20" t="n"/>
@@ -3921,17 +3945,17 @@
       <c r="I81" s="21" t="n"/>
     </row>
     <row r="82" ht="32" customHeight="1">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A82" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B82" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D82" s="20" t="n"/>
@@ -3942,17 +3966,17 @@
       <c r="I82" s="21" t="n"/>
     </row>
     <row r="83" ht="32" customHeight="1">
-      <c r="A83" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B83" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D83" s="20" t="n"/>
@@ -3962,18 +3986,18 @@
       <c r="H83" s="20" t="n"/>
       <c r="I83" s="21" t="n"/>
     </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B84" s="22" t="n">
-        <v>68</v>
-      </c>
-      <c r="C84" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの63件、別スコープ5件</t>
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D84" s="20" t="n"/>
@@ -3983,8 +4007,29 @@
       <c r="H84" s="20" t="n"/>
       <c r="I84" s="21" t="n"/>
     </row>
-    <row r="86" ht="100" customHeight="1">
-      <c r="A86" s="23" t="inlineStr">
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B85" s="22" t="n">
+        <v>69</v>
+      </c>
+      <c r="C85" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの64件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D85" s="20" t="n"/>
+      <c r="E85" s="20" t="n"/>
+      <c r="F85" s="20" t="n"/>
+      <c r="G85" s="20" t="n"/>
+      <c r="H85" s="20" t="n"/>
+      <c r="I85" s="21" t="n"/>
+    </row>
+    <row r="87" ht="100" customHeight="1">
+      <c r="A87" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -3994,16 +4039,16 @@
   <mergeCells count="12">
     <mergeCell ref="C84:I84"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A86:H86"/>
+    <mergeCell ref="A87:H87"/>
     <mergeCell ref="C80:I80"/>
     <mergeCell ref="C78:I78"/>
+    <mergeCell ref="A75:I75"/>
     <mergeCell ref="C79:I79"/>
     <mergeCell ref="C82:I82"/>
     <mergeCell ref="C77:I77"/>
     <mergeCell ref="C83:I83"/>
-    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="C85:I85"/>
     <mergeCell ref="C81:I81"/>
-    <mergeCell ref="C76:I76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -1495,12 +1495,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>103段落 15表</t>
+          <t>112段落 16表</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>第9期19施策の評価表（受け皿）と、実績が揃わない場合の暫定評価ルール。施策別評価表、実績の入力様式、暫定評価ルール、現時点で判定できる成果評価、委員会用スコアカード。</t>
+          <t>第9期19施策の評価表（受け皿）と、実績が揃わない場合の暫定評価ルール。施策別評価表、実績の入力様式、暫定評価ルール、現時点で判定できる成果評価、委員会用スコアカード、交付金の得点による19施策の暫定評価。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>評価を成果評価（アウトカム）とプロセス評価（実施状況）の2層に分け、成果評価は事業実績を要さず現時点で判定できることを示した。19施策のうち成果評価が可能10・調査による代理評価4・プロセス評価のみ5である。未受領年度は「未把握」と記載し、「実施されなかった」と書き分ける。委員会には成果指標12・補足指標4のスコアカードを示す。</t>
+          <t>評価を成果評価（アウトカム）とプロセス評価（実施状況）の2層に分け、成果評価は事業実績を要さず現時点で判定できることを示した。19施策のうち成果評価が可能10・調査による代理評価4・プロセス評価のみ5である。未受領年度は「未把握」と記載し、「実施されなかった」と書き分ける。委員会には成果指標12・補足指標4のスコアカードを示す。06シートでは交付金の大項目別得点53項目を19施策に割り当て、取組あり・改善4／横ばい7／低下4／交付金では判定できない4に分けた。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>32 KB</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -775,12 +775,12 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>728段落 124表</t>
+          <t>738段落 124表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>2.3 MB</t>
+          <t>2.7 MB</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -820,17 +820,17 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>33シート</t>
+          <t>36シート</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>277 KB</t>
+          <t>298 KB</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>33シート133点</t>
+          <t>36シート142点</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -1923,34 +1923,34 @@
       <c r="A32" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_3町別の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階。標準給付費見込額・地域支援事業費・第1号被保険者負担分・調整交付金・基金取崩額から保険料基準額までを組み立てたもの（11シート）。</t>
+          <t>令和8年10月・11月の3町協議に向けた論点整理（7シート）。町別の現在地、総合事業の町別実施状況、交付金評価の町別得点、町ごとの論点、3町共通の論点、協議の進め方。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>第9期の算定を再現すると公表値6,428円と一致する。基本ケースの暫定値は月額6,684円で、第9期の条例基準額6,400円を284円上回る。感度分析8件のうち最も大きいレバーは給付費の水準で幅は455円。確定を要する事項9件を10シートに掲げている。確定値ではない。</t>
+          <t>町別の差が最も大きいのは総合事業である。週1回以上の通いの場11箇所はすべて東神楽町にあり、地域リハビリテーション活動支援事業は美瑛町のみ、国保データベースの活用は東川町のみ未実施である。交付金の合計得点は東神楽町が3か年とも最も高く、令和6→8年度で東神楽町＋11点に対し東川町▲1点・美瑛町▲4点である。町ごとの論点12件と3町共通の論点8件を掲げている。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>11シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1975,27 +1975,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
+          <t>将来推計 第3段階。標準給付費見込額・地域支援事業費・第1号被保険者負担分・調整交付金・基金取崩額から保険料基準額までを組み立てたもの（11シート）。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
+          <t>第9期の算定を再現すると公表値6,428円と一致する。基本ケースの暫定値は月額6,684円で、第9期の条例基準額6,400円を284円上回る。感度分析8件のうち最も大きいレバーは給付費の水準で幅は455円。確定を要する事項9件を10シートに掲げている。確定値ではない。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>11シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -2003,9 +2003,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2020,27 +2020,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
+          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
+          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -2065,17 +2065,17 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
+          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
+          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -2110,17 +2110,17 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
+          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2148,34 +2148,34 @@
       <c r="A37" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
+          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
+          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>14 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2183,9 +2183,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2193,34 +2193,34 @@
       <c r="A38" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
+          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
+          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>14 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2228,9 +2228,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2245,17 +2245,17 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2273,9 +2273,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2283,34 +2283,34 @@
       <c r="A40" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2318,9 +2318,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2335,37 +2335,37 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>22 KB</t>
+          <t>16 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I41" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2380,32 +2380,32 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>20 KB</t>
+          <t>22 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
@@ -2425,27 +2425,27 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>65 KB</t>
+          <t>20 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2453,9 +2453,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2470,27 +2470,27 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>43 KB</t>
+          <t>66 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2498,9 +2498,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2508,34 +2508,34 @@
       <c r="A45" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2560,27 +2560,27 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2588,9 +2588,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I46" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2605,27 +2605,27 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2643,34 +2643,34 @@
       <c r="A48" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2678,9 +2678,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2695,27 +2695,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2723,9 +2723,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2740,27 +2740,27 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2785,27 +2785,27 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2830,17 +2830,17 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2875,17 +2875,17 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2920,27 +2920,27 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2965,27 +2965,27 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -2993,9 +2993,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I55" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3010,27 +3010,27 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3055,27 +3055,27 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3100,17 +3100,17 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -3145,27 +3145,27 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3173,9 +3173,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3190,27 +3190,27 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -3218,9 +3218,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I60" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3235,27 +3235,27 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3280,27 +3280,27 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -3325,27 +3325,27 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -3363,44 +3363,44 @@
       <c r="A64" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I64" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3415,32 +3415,32 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I65" s="12" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -3488,9 +3488,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I66" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I66" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3498,34 +3498,34 @@
       <c r="A67" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -3533,9 +3533,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I67" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3550,17 +3550,17 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -3578,9 +3578,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I68" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3588,44 +3588,44 @@
       <c r="A69" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H69" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I69" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I69" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3640,27 +3640,27 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H70" s="18" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H71" s="18" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -3775,95 +3775,119 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H73" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I73" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="52" customHeight="1">
+      <c r="A74" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E74" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr">
+      <c r="G74" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H73" s="18" t="inlineStr">
+      <c r="H74" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I73" s="18" t="inlineStr">
+      <c r="I74" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="19" t="inlineStr">
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="28" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
+    <row r="77" ht="28" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr"/>
-      <c r="E76" s="3" t="inlineStr"/>
-      <c r="F76" s="3" t="inlineStr"/>
-      <c r="G76" s="3" t="inlineStr"/>
-      <c r="H76" s="3" t="inlineStr"/>
-      <c r="I76" s="3" t="inlineStr"/>
-    </row>
-    <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr"/>
+      <c r="E77" s="3" t="inlineStr"/>
+      <c r="F77" s="3" t="inlineStr"/>
+      <c r="G77" s="3" t="inlineStr"/>
+      <c r="H77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D77" s="20" t="n"/>
-      <c r="E77" s="20" t="n"/>
-      <c r="F77" s="20" t="n"/>
-      <c r="G77" s="20" t="n"/>
-      <c r="H77" s="20" t="n"/>
-      <c r="I77" s="21" t="n"/>
-    </row>
-    <row r="78" ht="32" customHeight="1">
-      <c r="A78" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B78" s="6" t="n">
@@ -3871,7 +3895,7 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D78" s="20" t="n"/>
@@ -3882,17 +3906,17 @@
       <c r="I78" s="21" t="n"/>
     </row>
     <row r="79" ht="32" customHeight="1">
-      <c r="A79" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B79" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D79" s="20" t="n"/>
@@ -3903,9 +3927,9 @@
       <c r="I79" s="21" t="n"/>
     </row>
     <row r="80" ht="32" customHeight="1">
-      <c r="A80" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B80" s="6" t="n">
@@ -3913,7 +3937,7 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D80" s="20" t="n"/>
@@ -3924,17 +3948,17 @@
       <c r="I80" s="21" t="n"/>
     </row>
     <row r="81" ht="32" customHeight="1">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B81" s="6" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、将来推計_第3段階_給付費と保険料、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D81" s="20" t="n"/>
@@ -3945,17 +3969,17 @@
       <c r="I81" s="21" t="n"/>
     </row>
     <row r="82" ht="32" customHeight="1">
-      <c r="A82" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B82" s="6" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、将来推計_第3段階_給付費と保険料、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D82" s="20" t="n"/>
@@ -3966,17 +3990,17 @@
       <c r="I82" s="21" t="n"/>
     </row>
     <row r="83" ht="32" customHeight="1">
-      <c r="A83" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A83" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B83" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D83" s="20" t="n"/>
@@ -3987,17 +4011,17 @@
       <c r="I83" s="21" t="n"/>
     </row>
     <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B84" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、3町別の論点整理、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D84" s="20" t="n"/>
@@ -4007,18 +4031,18 @@
       <c r="H84" s="20" t="n"/>
       <c r="I84" s="21" t="n"/>
     </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B85" s="22" t="n">
-        <v>69</v>
-      </c>
-      <c r="C85" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの64件、別スコープ5件</t>
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D85" s="20" t="n"/>
@@ -4028,8 +4052,29 @@
       <c r="H85" s="20" t="n"/>
       <c r="I85" s="21" t="n"/>
     </row>
-    <row r="87" ht="100" customHeight="1">
-      <c r="A87" s="23" t="inlineStr">
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="n">
+        <v>70</v>
+      </c>
+      <c r="C86" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの65件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D86" s="20" t="n"/>
+      <c r="E86" s="20" t="n"/>
+      <c r="F86" s="20" t="n"/>
+      <c r="G86" s="20" t="n"/>
+      <c r="H86" s="20" t="n"/>
+      <c r="I86" s="21" t="n"/>
+    </row>
+    <row r="88" ht="100" customHeight="1">
+      <c r="A88" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -4039,16 +4084,16 @@
   <mergeCells count="12">
     <mergeCell ref="C84:I84"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A87:H87"/>
     <mergeCell ref="C80:I80"/>
     <mergeCell ref="C78:I78"/>
-    <mergeCell ref="A75:I75"/>
     <mergeCell ref="C79:I79"/>
+    <mergeCell ref="A76:I76"/>
     <mergeCell ref="C82:I82"/>
-    <mergeCell ref="C77:I77"/>
     <mergeCell ref="C83:I83"/>
+    <mergeCell ref="C86:I86"/>
     <mergeCell ref="C85:I85"/>
     <mergeCell ref="C81:I81"/>
+    <mergeCell ref="A88:H88"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4479,7 +4524,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>分析9件（妥当性検証・調査クロス集計・認定率の年齢調整・地域差・人口推計の基礎・将来推計・保険料2件・追加調査）、図表集33シート133点。あわせてエビデンス集（統計データ・事業所と公表情報・調査の集計値のExcel3冊と索引、図表の画像79点）を添える。</t>
+          <t>分析9件（妥当性検証・調査クロス集計・認定率の年齢調整・地域差・人口推計の基礎・将来推計・保険料2件・追加調査）、図表集36シート142点。あわせてエビデンス集（統計データ・事業所と公表情報・調査の集計値のExcel3冊と索引、図表の画像79点）を添える。</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2020,27 +2020,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
+          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>21 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -2065,27 +2065,27 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
+          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
+          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -2110,17 +2110,17 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
+          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
+          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2155,17 +2155,17 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
+          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2193,34 +2193,34 @@
       <c r="A38" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
+          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
+          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>14 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2228,9 +2228,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2238,34 +2238,34 @@
       <c r="A39" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
+          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
+          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>14 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2273,9 +2273,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2290,17 +2290,17 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2318,9 +2318,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2328,34 +2328,34 @@
       <c r="A41" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2363,9 +2363,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2380,37 +2380,37 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>22 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I42" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2425,32 +2425,32 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>20 KB</t>
+          <t>22 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I43" s="12" t="inlineStr">
@@ -2470,27 +2470,27 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>66 KB</t>
+          <t>20 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2498,9 +2498,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2515,27 +2515,27 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>43 KB</t>
+          <t>66 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2543,9 +2543,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2553,34 +2553,34 @@
       <c r="A46" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2605,27 +2605,27 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2633,9 +2633,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2650,27 +2650,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2688,34 +2688,34 @@
       <c r="A49" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2723,9 +2723,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2740,27 +2740,27 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2768,9 +2768,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2785,27 +2785,27 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2830,27 +2830,27 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2875,17 +2875,17 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2965,27 +2965,27 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -3010,27 +3010,27 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3038,9 +3038,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I56" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3055,27 +3055,27 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3100,27 +3100,27 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3145,17 +3145,17 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -3190,27 +3190,27 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -3218,9 +3218,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3235,27 +3235,27 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3263,9 +3263,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I61" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3280,27 +3280,27 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -3325,27 +3325,27 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -3370,27 +3370,27 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -3408,44 +3408,44 @@
       <c r="A65" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I65" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3460,32 +3460,32 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I66" s="12" t="inlineStr">
@@ -3505,27 +3505,27 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -3533,9 +3533,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I67" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I67" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3543,34 +3543,34 @@
       <c r="A68" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -3578,9 +3578,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I68" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3595,17 +3595,17 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -3623,9 +3623,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I69" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3633,44 +3633,44 @@
       <c r="A70" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H70" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I70" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I70" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3685,27 +3685,27 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H71" s="18" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H72" s="18" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -3820,95 +3820,119 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H74" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I74" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="52" customHeight="1">
+      <c r="A75" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="E75" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H74" s="18" t="inlineStr">
+      <c r="H75" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I74" s="18" t="inlineStr">
+      <c r="I75" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="19" t="inlineStr">
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="28" customHeight="1">
-      <c r="A77" s="3" t="inlineStr">
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr"/>
-      <c r="E77" s="3" t="inlineStr"/>
-      <c r="F77" s="3" t="inlineStr"/>
-      <c r="G77" s="3" t="inlineStr"/>
-      <c r="H77" s="3" t="inlineStr"/>
-      <c r="I77" s="3" t="inlineStr"/>
-    </row>
-    <row r="78" ht="32" customHeight="1">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr"/>
+      <c r="E78" s="3" t="inlineStr"/>
+      <c r="F78" s="3" t="inlineStr"/>
+      <c r="G78" s="3" t="inlineStr"/>
+      <c r="H78" s="3" t="inlineStr"/>
+      <c r="I78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79" ht="32" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D78" s="20" t="n"/>
-      <c r="E78" s="20" t="n"/>
-      <c r="F78" s="20" t="n"/>
-      <c r="G78" s="20" t="n"/>
-      <c r="H78" s="20" t="n"/>
-      <c r="I78" s="21" t="n"/>
-    </row>
-    <row r="79" ht="32" customHeight="1">
-      <c r="A79" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B79" s="6" t="n">
@@ -3916,7 +3940,7 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D79" s="20" t="n"/>
@@ -3927,17 +3951,17 @@
       <c r="I79" s="21" t="n"/>
     </row>
     <row r="80" ht="32" customHeight="1">
-      <c r="A80" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A80" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B80" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D80" s="20" t="n"/>
@@ -3948,9 +3972,9 @@
       <c r="I80" s="21" t="n"/>
     </row>
     <row r="81" ht="32" customHeight="1">
-      <c r="A81" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B81" s="6" t="n">
@@ -3958,7 +3982,7 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D81" s="20" t="n"/>
@@ -3969,17 +3993,17 @@
       <c r="I81" s="21" t="n"/>
     </row>
     <row r="82" ht="32" customHeight="1">
-      <c r="A82" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B82" s="6" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、将来推計_第3段階_給付費と保険料、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D82" s="20" t="n"/>
@@ -3990,17 +4014,17 @@
       <c r="I82" s="21" t="n"/>
     </row>
     <row r="83" ht="32" customHeight="1">
-      <c r="A83" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B83" s="6" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、将来推計_第3段階_給付費と保険料、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D83" s="20" t="n"/>
@@ -4011,17 +4035,17 @@
       <c r="I83" s="21" t="n"/>
     </row>
     <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A84" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B84" s="6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、3町別の論点整理、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D84" s="20" t="n"/>
@@ -4032,17 +4056,17 @@
       <c r="I84" s="21" t="n"/>
     </row>
     <row r="85" ht="32" customHeight="1">
-      <c r="A85" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B85" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、3町別の論点整理、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D85" s="20" t="n"/>
@@ -4052,18 +4076,18 @@
       <c r="H85" s="20" t="n"/>
       <c r="I85" s="21" t="n"/>
     </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B86" s="22" t="n">
-        <v>70</v>
-      </c>
-      <c r="C86" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの65件、別スコープ5件</t>
+    <row r="86" ht="32" customHeight="1">
+      <c r="A86" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D86" s="20" t="n"/>
@@ -4073,8 +4097,29 @@
       <c r="H86" s="20" t="n"/>
       <c r="I86" s="21" t="n"/>
     </row>
-    <row r="88" ht="100" customHeight="1">
-      <c r="A88" s="23" t="inlineStr">
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B87" s="22" t="n">
+        <v>71</v>
+      </c>
+      <c r="C87" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの66件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D87" s="20" t="n"/>
+      <c r="E87" s="20" t="n"/>
+      <c r="F87" s="20" t="n"/>
+      <c r="G87" s="20" t="n"/>
+      <c r="H87" s="20" t="n"/>
+      <c r="I87" s="21" t="n"/>
+    </row>
+    <row r="89" ht="100" customHeight="1">
+      <c r="A89" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -4085,15 +4130,15 @@
     <mergeCell ref="C84:I84"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C80:I80"/>
-    <mergeCell ref="C78:I78"/>
     <mergeCell ref="C79:I79"/>
-    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="C87:I87"/>
     <mergeCell ref="C82:I82"/>
     <mergeCell ref="C83:I83"/>
     <mergeCell ref="C86:I86"/>
     <mergeCell ref="C85:I85"/>
+    <mergeCell ref="A89:H89"/>
+    <mergeCell ref="A77:I77"/>
     <mergeCell ref="C81:I81"/>
-    <mergeCell ref="A88:H88"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -775,7 +775,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>738段落 124表</t>
+          <t>739段落 124表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>135段落 11表</t>
+          <t>138段落 11表</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>第9期の算定を再現すると公表値6,428円と一致する。基本ケースの暫定値は月額6,684円で、第9期の条例基準額6,400円を284円上回る。感度分析8件のうち最も大きいレバーは給付費の水準で幅は455円。確定を要する事項9件を10シートに掲げている。確定値ではない。</t>
+          <t>第9期の算定を再現すると公表値6,428円と一致する。基本ケースの暫定値は月額6,755円で、第9期の条例基準額6,400円を355円上回る。感度分析8件のうち最も大きいレバーは給付費の水準で幅は596円。確定を要する事項9件を10シートに掲げている。確定値ではない。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -2020,27 +2020,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
+          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,684円・案B（社人研＋補正）6,593円・案C 6,789円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円である。採用案のご確認（確認事項No.63）を要する。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>21 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -2048,9 +2048,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2065,27 +2065,27 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
+          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>21 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
+          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
+          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2155,17 +2155,17 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
+          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
+          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2200,17 +2200,17 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
+          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2238,34 +2238,34 @@
       <c r="A39" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
+          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
+          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>14 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2273,9 +2273,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2283,34 +2283,34 @@
       <c r="A40" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
+          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
+          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>14 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2318,9 +2318,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2335,17 +2335,17 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2363,9 +2363,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2373,34 +2373,34 @@
       <c r="A42" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2408,9 +2408,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2425,37 +2425,37 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>22 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2470,32 +2470,32 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>20 KB</t>
+          <t>22 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
@@ -2515,27 +2515,27 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>66 KB</t>
+          <t>21 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2543,9 +2543,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2560,27 +2560,27 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>43 KB</t>
+          <t>67 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2588,9 +2588,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2598,34 +2598,34 @@
       <c r="A47" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2650,27 +2650,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2678,9 +2678,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I48" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2695,27 +2695,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2733,34 +2733,34 @@
       <c r="A50" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2768,9 +2768,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2785,27 +2785,27 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2813,9 +2813,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2830,27 +2830,27 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2875,27 +2875,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2965,17 +2965,17 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -3010,27 +3010,27 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3055,27 +3055,27 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3083,9 +3083,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3100,27 +3100,27 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3145,27 +3145,27 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3190,17 +3190,17 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -3235,27 +3235,27 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3263,9 +3263,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3280,27 +3280,27 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -3308,9 +3308,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I62" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3325,27 +3325,27 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -3370,27 +3370,27 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -3415,27 +3415,27 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -3453,44 +3453,44 @@
       <c r="A66" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I66" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3505,32 +3505,32 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I67" s="12" t="inlineStr">
@@ -3550,27 +3550,27 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -3578,9 +3578,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I68" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I68" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3588,34 +3588,34 @@
       <c r="A69" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -3623,9 +3623,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3640,17 +3640,17 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -3668,9 +3668,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I70" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3678,44 +3678,44 @@
       <c r="A71" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H71" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I71" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I71" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3730,27 +3730,27 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H72" s="18" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H73" s="18" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -3865,95 +3865,119 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H75" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I75" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="52" customHeight="1">
+      <c r="A76" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D76" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E76" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G75" s="7" t="inlineStr">
+      <c r="G76" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H75" s="18" t="inlineStr">
+      <c r="H76" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I75" s="18" t="inlineStr">
+      <c r="I76" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="19" t="inlineStr">
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="28" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr"/>
-      <c r="E78" s="3" t="inlineStr"/>
-      <c r="F78" s="3" t="inlineStr"/>
-      <c r="G78" s="3" t="inlineStr"/>
-      <c r="H78" s="3" t="inlineStr"/>
-      <c r="I78" s="3" t="inlineStr"/>
-    </row>
-    <row r="79" ht="32" customHeight="1">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr"/>
+      <c r="E79" s="3" t="inlineStr"/>
+      <c r="F79" s="3" t="inlineStr"/>
+      <c r="G79" s="3" t="inlineStr"/>
+      <c r="H79" s="3" t="inlineStr"/>
+      <c r="I79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D79" s="20" t="n"/>
-      <c r="E79" s="20" t="n"/>
-      <c r="F79" s="20" t="n"/>
-      <c r="G79" s="20" t="n"/>
-      <c r="H79" s="20" t="n"/>
-      <c r="I79" s="21" t="n"/>
-    </row>
-    <row r="80" ht="32" customHeight="1">
-      <c r="A80" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B80" s="6" t="n">
@@ -3961,7 +3985,7 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D80" s="20" t="n"/>
@@ -3972,17 +3996,17 @@
       <c r="I80" s="21" t="n"/>
     </row>
     <row r="81" ht="32" customHeight="1">
-      <c r="A81" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A81" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B81" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D81" s="20" t="n"/>
@@ -3993,9 +4017,9 @@
       <c r="I81" s="21" t="n"/>
     </row>
     <row r="82" ht="32" customHeight="1">
-      <c r="A82" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B82" s="6" t="n">
@@ -4003,7 +4027,7 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D82" s="20" t="n"/>
@@ -4014,17 +4038,17 @@
       <c r="I82" s="21" t="n"/>
     </row>
     <row r="83" ht="32" customHeight="1">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B83" s="6" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、将来推計_第3段階_給付費と保険料、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D83" s="20" t="n"/>
@@ -4035,17 +4059,17 @@
       <c r="I83" s="21" t="n"/>
     </row>
     <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B84" s="6" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、将来推計_第3段階_給付費と保険料、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D84" s="20" t="n"/>
@@ -4056,17 +4080,17 @@
       <c r="I84" s="21" t="n"/>
     </row>
     <row r="85" ht="32" customHeight="1">
-      <c r="A85" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B85" s="6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、3町別の論点整理、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D85" s="20" t="n"/>
@@ -4077,17 +4101,17 @@
       <c r="I85" s="21" t="n"/>
     </row>
     <row r="86" ht="32" customHeight="1">
-      <c r="A86" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B86" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、3町別の論点整理、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D86" s="20" t="n"/>
@@ -4097,18 +4121,18 @@
       <c r="H86" s="20" t="n"/>
       <c r="I86" s="21" t="n"/>
     </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B87" s="22" t="n">
-        <v>71</v>
-      </c>
-      <c r="C87" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの66件、別スコープ5件</t>
+    <row r="87" ht="32" customHeight="1">
+      <c r="A87" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D87" s="20" t="n"/>
@@ -4118,8 +4142,29 @@
       <c r="H87" s="20" t="n"/>
       <c r="I87" s="21" t="n"/>
     </row>
-    <row r="89" ht="100" customHeight="1">
-      <c r="A89" s="23" t="inlineStr">
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B88" s="22" t="n">
+        <v>72</v>
+      </c>
+      <c r="C88" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの67件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D88" s="20" t="n"/>
+      <c r="E88" s="20" t="n"/>
+      <c r="F88" s="20" t="n"/>
+      <c r="G88" s="20" t="n"/>
+      <c r="H88" s="20" t="n"/>
+      <c r="I88" s="21" t="n"/>
+    </row>
+    <row r="90" ht="100" customHeight="1">
+      <c r="A90" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -4129,16 +4174,16 @@
   <mergeCells count="12">
     <mergeCell ref="C84:I84"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="C88:I88"/>
     <mergeCell ref="C80:I80"/>
-    <mergeCell ref="C79:I79"/>
     <mergeCell ref="C87:I87"/>
     <mergeCell ref="C82:I82"/>
     <mergeCell ref="C83:I83"/>
+    <mergeCell ref="A90:H90"/>
     <mergeCell ref="C86:I86"/>
     <mergeCell ref="C85:I85"/>
-    <mergeCell ref="A89:H89"/>
-    <mergeCell ref="A77:I77"/>
     <mergeCell ref="C81:I81"/>
+    <mergeCell ref="A78:I78"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1923,34 +1923,34 @@
       <c r="A32" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町別の論点整理.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>令和8年10月・11月の3町協議に向けた論点整理（7シート）。町別の現在地、総合事業の町別実施状況、交付金評価の町別得点、町ごとの論点、3町共通の論点、協議の進め方。</t>
+          <t>広域連合において行うべき事業を優先順位をもとに整理したもの（8シート）。富良野市のサービスガイドと鹿児島県の生活支援体制整備事業取組事例集を参照し、当区域の実績データと突き合わせて20件を掲げている。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>町別の差が最も大きいのは総合事業である。週1回以上の通いの場11箇所はすべて東神楽町にあり、地域リハビリテーション活動支援事業は美瑛町のみ、国保データベースの活用は東川町のみ未実施である。交付金の合計得点は東神楽町が3か年とも最も高く、令和6→8年度で東神楽町＋11点に対し東川町▲1点・美瑛町▲4点である。町ごとの論点12件と3町共通の論点8件を掲げている。</t>
+          <t>義務・欠落・実行・効果・主体の5項目を各3点で採点し、優先度A4件・B7件・C9件に分けた。優先度Aは、総合事業の事業評価（3町とも未実施）、生活支援体制整備の区域共通運営、24時間対応サービスの確保方策、包括的支援事業・任意事業の実績管理である。優先順位は受託者の案であり、発注者の決定を要する。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>44 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1968,34 +1968,34 @@
       <c r="A33" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階。標準給付費見込額・地域支援事業費・第1号被保険者負担分・調整交付金・基金取崩額から保険料基準額までを組み立てたもの（11シート）。</t>
+          <t>富良野市「介護・高齢者福祉サービスガイド」と同じ構成による当区域のサービスガイドの構成案（15章）。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>第9期の算定を再現すると公表値6,428円と一致する。基本ケースの暫定値は月額6,755円で、第9期の条例基準額6,400円を355円上回る。感度分析8件のうち最も大きいレバーは給付費の水準で幅は596円。確定を要する事項9件を10シートに掲げている。確定値ではない。</t>
+          <t>介護保険のしくみ・手続・費用と、区域内74事業所の一覧は原案を作成した。3町の高齢者福祉サービス（介護保険外）、社会福祉協議会のサービス、事業所の所在地・電話番号は記入枠としている。3町への照会（事業の優先順位 事業No.14）により確定する。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>11シート</t>
+          <t>79段落 27表</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>56 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -2013,24 +2013,24 @@
       <c r="A34" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_3町別の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
+          <t>令和8年10月・11月の3町協議に向けた論点整理（7シート）。町別の現在地、総合事業の町別実施状況、交付金評価の町別得点、町ごとの論点、3町共通の論点、協議の進め方。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,684円・案B（社人研＋補正）6,593円・案C 6,789円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円である。採用案のご確認（確認事項No.63）を要する。</t>
+          <t>町別の差が最も大きいのは総合事業である。週1回以上の通いの場11箇所はすべて東神楽町にあり、地域リハビリテーション活動支援事業は美瑛町のみ、国保データベースの活用は東川町のみ未実施である。交付金の合計得点は東神楽町が3か年とも最も高く、令和6→8年度で東神楽町＋11点に対し東川町▲1点・美瑛町▲4点である。町ごとの論点12件と3町共通の論点8件を掲げている。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -2065,27 +2065,27 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
+          <t>将来推計 第3段階。標準給付費見込額・地域支援事業費・第1号被保険者負担分・調整交付金・基金取崩額から保険料基準額までを組み立てたもの（11シート）。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
+          <t>第9期の算定を再現すると公表値6,428円と一致する。基本ケースの暫定値は月額6,755円で、第9期の条例基準額6,400円を355円上回る。感度分析8件のうち最も大きいレバーは給付費の水準で幅は596円。確定を要する事項9件を10シートに掲げている。確定値ではない。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>11シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>21 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -2093,9 +2093,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2110,17 +2110,17 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
+          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,684円・案B（社人研＋補正）6,593円・案C 6,789円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円である。採用案のご確認（確認事項No.63）を要する。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2138,9 +2138,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2155,27 +2155,27 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
+          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>21 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2200,27 +2200,27 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
+          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
+          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2245,17 +2245,17 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
+          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
+          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2283,34 +2283,34 @@
       <c r="A40" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
+          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>14 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2318,9 +2318,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2335,27 +2335,27 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
+          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
+          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2373,34 +2373,34 @@
       <c r="A42" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>14 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2418,29 +2418,29 @@
       <c r="A43" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -2463,44 +2463,44 @@
       <c r="A44" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>22 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2515,27 +2515,27 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>21 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2543,9 +2543,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2560,37 +2560,37 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>67 KB</t>
+          <t>22 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
-        </is>
-      </c>
-      <c r="I46" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2605,27 +2605,27 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>43 KB</t>
+          <t>21 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2633,9 +2633,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2643,34 +2643,34 @@
       <c r="A48" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>68 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2678,9 +2678,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2688,34 +2688,34 @@
       <c r="A49" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2723,9 +2723,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I49" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2740,27 +2740,27 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2768,9 +2768,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2778,34 +2778,34 @@
       <c r="A51" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2813,9 +2813,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2823,34 +2823,34 @@
       <c r="A52" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2858,9 +2858,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2875,27 +2875,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2903,9 +2903,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I53" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2920,27 +2920,27 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2965,27 +2965,27 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -3010,17 +3010,17 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3055,27 +3055,27 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3100,27 +3100,27 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3128,9 +3128,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3145,27 +3145,27 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3173,9 +3173,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I59" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3190,27 +3190,27 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -3235,27 +3235,27 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3280,27 +3280,27 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -3308,9 +3308,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3325,27 +3325,27 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -3370,27 +3370,27 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>30 KB</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -3398,9 +3398,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I64" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3415,27 +3415,27 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -3498,44 +3498,44 @@
       <c r="A67" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I67" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3543,34 +3543,34 @@
       <c r="A68" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -3578,9 +3578,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I68" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3595,37 +3595,37 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
-        </is>
-      </c>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I69" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3633,34 +3633,34 @@
       <c r="A70" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -3668,9 +3668,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I70" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I70" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3678,34 +3678,34 @@
       <c r="A71" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -3713,9 +3713,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I71" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3723,44 +3723,44 @@
       <c r="A72" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H72" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I72" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>18 KB</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3768,44 +3768,44 @@
       <c r="A73" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
-        </is>
-      </c>
-      <c r="H73" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I73" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I73" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3820,27 +3820,27 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H74" s="18" t="inlineStr">
@@ -3865,12 +3865,12 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H75" s="18" t="inlineStr">
@@ -3910,124 +3910,172 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H76" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I76" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="52" customHeight="1">
+      <c r="A77" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H77" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I77" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="52" customHeight="1">
+      <c r="A78" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E78" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr">
+      <c r="G78" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H76" s="18" t="inlineStr">
+      <c r="H78" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I76" s="18" t="inlineStr">
+      <c r="I78" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="19" t="inlineStr">
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="28" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr"/>
-      <c r="E79" s="3" t="inlineStr"/>
-      <c r="F79" s="3" t="inlineStr"/>
-      <c r="G79" s="3" t="inlineStr"/>
-      <c r="H79" s="3" t="inlineStr"/>
-      <c r="I79" s="3" t="inlineStr"/>
-    </row>
-    <row r="80" ht="32" customHeight="1">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr"/>
+      <c r="E81" s="3" t="inlineStr"/>
+      <c r="F81" s="3" t="inlineStr"/>
+      <c r="G81" s="3" t="inlineStr"/>
+      <c r="H81" s="3" t="inlineStr"/>
+      <c r="I81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82" ht="32" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
         </is>
       </c>
-      <c r="B80" s="6" t="n">
+      <c r="B82" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D80" s="20" t="n"/>
-      <c r="E80" s="20" t="n"/>
-      <c r="F80" s="20" t="n"/>
-      <c r="G80" s="20" t="n"/>
-      <c r="H80" s="20" t="n"/>
-      <c r="I80" s="21" t="n"/>
-    </row>
-    <row r="81" ht="32" customHeight="1">
-      <c r="A81" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
-        </is>
-      </c>
-      <c r="D81" s="20" t="n"/>
-      <c r="E81" s="20" t="n"/>
-      <c r="F81" s="20" t="n"/>
-      <c r="G81" s="20" t="n"/>
-      <c r="H81" s="20" t="n"/>
-      <c r="I81" s="21" t="n"/>
-    </row>
-    <row r="82" ht="32" customHeight="1">
-      <c r="A82" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D82" s="20" t="n"/>
@@ -4038,17 +4086,17 @@
       <c r="I82" s="21" t="n"/>
     </row>
     <row r="83" ht="32" customHeight="1">
-      <c r="A83" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A83" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B83" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D83" s="20" t="n"/>
@@ -4059,17 +4107,17 @@
       <c r="I83" s="21" t="n"/>
     </row>
     <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B84" s="6" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、将来推計_第3段階_給付費と保険料、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D84" s="20" t="n"/>
@@ -4080,17 +4128,17 @@
       <c r="I84" s="21" t="n"/>
     </row>
     <row r="85" ht="32" customHeight="1">
-      <c r="A85" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A85" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B85" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D85" s="20" t="n"/>
@@ -4101,17 +4149,17 @@
       <c r="I85" s="21" t="n"/>
     </row>
     <row r="86" ht="32" customHeight="1">
-      <c r="A86" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B86" s="6" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、3町別の論点整理、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D86" s="20" t="n"/>
@@ -4122,9 +4170,9 @@
       <c r="I86" s="21" t="n"/>
     </row>
     <row r="87" ht="32" customHeight="1">
-      <c r="A87" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A87" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B87" s="6" t="n">
@@ -4132,7 +4180,7 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D87" s="20" t="n"/>
@@ -4142,18 +4190,18 @@
       <c r="H87" s="20" t="n"/>
       <c r="I87" s="21" t="n"/>
     </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B88" s="22" t="n">
-        <v>72</v>
-      </c>
-      <c r="C88" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの67件、別スコープ5件</t>
+    <row r="88" ht="32" customHeight="1">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、3町別の論点整理、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D88" s="20" t="n"/>
@@ -4163,8 +4211,50 @@
       <c r="H88" s="20" t="n"/>
       <c r="I88" s="21" t="n"/>
     </row>
-    <row r="90" ht="100" customHeight="1">
-      <c r="A90" s="23" t="inlineStr">
+    <row r="89" ht="32" customHeight="1">
+      <c r="A89" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+        </is>
+      </c>
+      <c r="D89" s="20" t="n"/>
+      <c r="E89" s="20" t="n"/>
+      <c r="F89" s="20" t="n"/>
+      <c r="G89" s="20" t="n"/>
+      <c r="H89" s="20" t="n"/>
+      <c r="I89" s="21" t="n"/>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B90" s="22" t="n">
+        <v>74</v>
+      </c>
+      <c r="C90" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの69件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D90" s="20" t="n"/>
+      <c r="E90" s="20" t="n"/>
+      <c r="F90" s="20" t="n"/>
+      <c r="G90" s="20" t="n"/>
+      <c r="H90" s="20" t="n"/>
+      <c r="I90" s="21" t="n"/>
+    </row>
+    <row r="92" ht="100" customHeight="1">
+      <c r="A92" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -4172,18 +4262,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C89:I89"/>
     <mergeCell ref="C84:I84"/>
+    <mergeCell ref="A92:H92"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C88:I88"/>
-    <mergeCell ref="C80:I80"/>
     <mergeCell ref="C87:I87"/>
     <mergeCell ref="C82:I82"/>
     <mergeCell ref="C83:I83"/>
-    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A80:I80"/>
+    <mergeCell ref="C90:I90"/>
     <mergeCell ref="C86:I86"/>
     <mergeCell ref="C85:I85"/>
-    <mergeCell ref="C81:I81"/>
-    <mergeCell ref="A78:I78"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>739段落 124表</t>
+          <t>740段落 124表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1350,27 +1350,27 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月20日に受領した3町の社会資源一覧（74事業所）と、既存の把握との突合。受領した一覧、訪問介護13事業所の突合、サービス別の従業員数、指定事業所一覧との網羅性、反映する箇所。</t>
+          <t>令和8年8月20日に受領した3町の社会資源一覧（74事業所）と、既存の把握との突合。受領した一覧、訪問介護13事業所の突合、サービス別の従業員数、指定事業所一覧との網羅性、反映する箇所、計画素案とサービスガイド構成案の事業所の整合（6シート）。</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>3町74事業所の従業員総数・常勤・非常勤が得られ、これまで訪問介護でしか把握できなかった従業員数が全サービスについてそろった。訪問介護13事業所は公表画面による把握と13件とも対応し、3事業所は完全に一致した（社会資源203.5人／公表総従業者184.5人）。差は数える範囲（管理者・事務職員を含むか）によるものであり、計画本文の訪問介護員等181人は変わらない。</t>
+          <t>3町74事業所の従業員総数・常勤・非常勤が得られ、これまで訪問介護でしか把握できなかった従業員数が全サービスについてそろった。訪問介護13事業所は公表画面による把握と13件とも対応し、3事業所は完全に一致した（社会資源203.5人／公表総従業者184.5人）。差は数える範囲（管理者・事務職員を含むか）によるものであり、計画本文の訪問介護員等181人は変わらない。06シートで、見える化・北海道の介護保険事業所一覧・介護サービス情報公表システム・社会資源一覧の4出所をサービス種別ごとに並べ、22種別のうち17種別が一致することを確認した。一致しない5種別の理由（時点・みなし指定・掲載の有無）を示している。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>29 KB</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
+          <t>最新</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
@@ -1990,12 +1990,12 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>79段落 27表</t>
+          <t>80段落 27表</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>56 KB</t>
+          <t>59 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>68 KB</t>
+          <t>69 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -775,7 +775,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>740段落 124表</t>
+          <t>741段落 124表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>第9期の算定を再現すると公表値6,428円と一致する。基本ケースの暫定値は月額6,755円で、第9期の条例基準額6,400円を355円上回る。感度分析8件のうち最も大きいレバーは給付費の水準で幅は596円。確定を要する事項9件を10シートに掲げている。確定値ではない。</t>
+          <t>第9期の算定を再現すると公表値6,428円と一致する。基本ケースの暫定値は月額6,740円で、第9期の条例基準額6,400円を340円上回る。感度分析8件のうち最も大きいレバーは給付費の水準で幅は596円。確定を要する事項9件を10シートに掲げている。確定値ではない。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>36 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
+          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,684円・案B（社人研＋補正）6,593円・案C 6,789円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円である。採用案のご確認（確認事項No.63）を要する。</t>
+          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>33 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2155,27 +2155,27 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
+          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>21 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2183,9 +2183,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2200,27 +2200,27 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
+          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>21 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2245,27 +2245,27 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
+          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
+          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
+          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
+          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2335,17 +2335,17 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
+          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2373,34 +2373,34 @@
       <c r="A42" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
+          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
+          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>14 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2408,9 +2408,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2418,34 +2418,34 @@
       <c r="A43" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
+          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
+          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>14 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2453,9 +2453,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2470,17 +2470,17 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2498,9 +2498,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2508,34 +2508,34 @@
       <c r="A45" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2543,9 +2543,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2560,37 +2560,37 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>22 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I46" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2605,32 +2605,32 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>21 KB</t>
+          <t>22 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I47" s="12" t="inlineStr">
@@ -2650,27 +2650,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>69 KB</t>
+          <t>21 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2678,9 +2678,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2695,27 +2695,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>43 KB</t>
+          <t>70 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2723,9 +2723,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2733,34 +2733,34 @@
       <c r="A50" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2785,27 +2785,27 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2813,9 +2813,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I51" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2830,27 +2830,27 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2868,34 +2868,34 @@
       <c r="A53" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2903,9 +2903,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I53" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2920,27 +2920,27 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2948,9 +2948,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2965,27 +2965,27 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -3010,27 +3010,27 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3055,17 +3055,17 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3100,17 +3100,17 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3145,27 +3145,27 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3190,27 +3190,27 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -3218,9 +3218,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I60" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3235,27 +3235,27 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3280,27 +3280,27 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -3325,17 +3325,17 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -3370,27 +3370,27 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>30 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -3398,9 +3398,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3415,27 +3415,27 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>31 KB</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -3443,9 +3443,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -3505,27 +3505,27 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -3550,27 +3550,27 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -3588,44 +3588,44 @@
       <c r="A69" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I69" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3640,32 +3640,32 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I70" s="12" t="inlineStr">
@@ -3685,27 +3685,27 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -3713,9 +3713,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I71" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I71" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3723,34 +3723,34 @@
       <c r="A72" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -3758,9 +3758,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I72" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3775,17 +3775,17 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -3803,9 +3803,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I73" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3813,44 +3813,44 @@
       <c r="A74" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H74" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I74" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I74" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3865,27 +3865,27 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H75" s="18" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H76" s="18" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -4000,95 +4000,119 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H78" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I78" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="52" customHeight="1">
+      <c r="A79" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E79" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H78" s="18" t="inlineStr">
+      <c r="H79" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I78" s="18" t="inlineStr">
+      <c r="I79" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="19" t="inlineStr">
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="28" customHeight="1">
-      <c r="A81" s="3" t="inlineStr">
+    <row r="82" ht="28" customHeight="1">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr"/>
-      <c r="E81" s="3" t="inlineStr"/>
-      <c r="F81" s="3" t="inlineStr"/>
-      <c r="G81" s="3" t="inlineStr"/>
-      <c r="H81" s="3" t="inlineStr"/>
-      <c r="I81" s="3" t="inlineStr"/>
-    </row>
-    <row r="82" ht="32" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr"/>
+      <c r="E82" s="3" t="inlineStr"/>
+      <c r="F82" s="3" t="inlineStr"/>
+      <c r="G82" s="3" t="inlineStr"/>
+      <c r="H82" s="3" t="inlineStr"/>
+      <c r="I82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D82" s="20" t="n"/>
-      <c r="E82" s="20" t="n"/>
-      <c r="F82" s="20" t="n"/>
-      <c r="G82" s="20" t="n"/>
-      <c r="H82" s="20" t="n"/>
-      <c r="I82" s="21" t="n"/>
-    </row>
-    <row r="83" ht="32" customHeight="1">
-      <c r="A83" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B83" s="6" t="n">
@@ -4096,7 +4120,7 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D83" s="20" t="n"/>
@@ -4107,17 +4131,17 @@
       <c r="I83" s="21" t="n"/>
     </row>
     <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A84" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B84" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D84" s="20" t="n"/>
@@ -4128,9 +4152,9 @@
       <c r="I84" s="21" t="n"/>
     </row>
     <row r="85" ht="32" customHeight="1">
-      <c r="A85" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B85" s="6" t="n">
@@ -4138,7 +4162,7 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D85" s="20" t="n"/>
@@ -4149,17 +4173,17 @@
       <c r="I85" s="21" t="n"/>
     </row>
     <row r="86" ht="32" customHeight="1">
-      <c r="A86" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A86" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B86" s="6" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D86" s="20" t="n"/>
@@ -4170,17 +4194,17 @@
       <c r="I86" s="21" t="n"/>
     </row>
     <row r="87" ht="32" customHeight="1">
-      <c r="A87" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B87" s="6" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D87" s="20" t="n"/>
@@ -4191,17 +4215,17 @@
       <c r="I87" s="21" t="n"/>
     </row>
     <row r="88" ht="32" customHeight="1">
-      <c r="A88" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A88" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B88" s="6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、3町別の論点整理、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D88" s="20" t="n"/>
@@ -4212,17 +4236,17 @@
       <c r="I88" s="21" t="n"/>
     </row>
     <row r="89" ht="32" customHeight="1">
-      <c r="A89" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B89" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、3町別の論点整理、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D89" s="20" t="n"/>
@@ -4232,18 +4256,18 @@
       <c r="H89" s="20" t="n"/>
       <c r="I89" s="21" t="n"/>
     </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B90" s="22" t="n">
-        <v>74</v>
-      </c>
-      <c r="C90" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの69件、別スコープ5件</t>
+    <row r="90" ht="32" customHeight="1">
+      <c r="A90" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D90" s="20" t="n"/>
@@ -4253,8 +4277,29 @@
       <c r="H90" s="20" t="n"/>
       <c r="I90" s="21" t="n"/>
     </row>
-    <row r="92" ht="100" customHeight="1">
-      <c r="A92" s="23" t="inlineStr">
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B91" s="22" t="n">
+        <v>75</v>
+      </c>
+      <c r="C91" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの70件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D91" s="20" t="n"/>
+      <c r="E91" s="20" t="n"/>
+      <c r="F91" s="20" t="n"/>
+      <c r="G91" s="20" t="n"/>
+      <c r="H91" s="20" t="n"/>
+      <c r="I91" s="21" t="n"/>
+    </row>
+    <row r="93" ht="100" customHeight="1">
+      <c r="A93" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -4264,16 +4309,16 @@
   <mergeCells count="12">
     <mergeCell ref="C89:I89"/>
     <mergeCell ref="C84:I84"/>
-    <mergeCell ref="A92:H92"/>
+    <mergeCell ref="A81:I81"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C88:I88"/>
     <mergeCell ref="C87:I87"/>
-    <mergeCell ref="C82:I82"/>
+    <mergeCell ref="C90:I90"/>
     <mergeCell ref="C83:I83"/>
-    <mergeCell ref="A80:I80"/>
-    <mergeCell ref="C90:I90"/>
+    <mergeCell ref="C91:I91"/>
     <mergeCell ref="C86:I86"/>
     <mergeCell ref="C85:I85"/>
+    <mergeCell ref="A93:H93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -775,7 +775,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>741段落 124表</t>
+          <t>750段落 124表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -2110,17 +2110,17 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
+          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
+          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,745〜1,746市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>33 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2138,9 +2138,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2155,27 +2155,27 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
+          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
+          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>33 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2200,27 +2200,27 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
+          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>21 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2228,9 +2228,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2245,27 +2245,27 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
+          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>21 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2290,27 +2290,27 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
+          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
+          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2335,17 +2335,17 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
+          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
+          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2380,17 +2380,17 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
+          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2418,34 +2418,34 @@
       <c r="A43" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
+          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
+          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>14 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2453,9 +2453,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2463,34 +2463,34 @@
       <c r="A44" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
+          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
+          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>14 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2498,9 +2498,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2515,17 +2515,17 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2543,9 +2543,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2553,34 +2553,34 @@
       <c r="A46" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2588,9 +2588,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2605,37 +2605,37 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>22 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2650,32 +2650,32 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>21 KB</t>
+          <t>22 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I48" s="12" t="inlineStr">
@@ -2695,27 +2695,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>70 KB</t>
+          <t>22 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2723,9 +2723,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2740,27 +2740,27 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>43 KB</t>
+          <t>72 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2768,9 +2768,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2778,34 +2778,34 @@
       <c r="A51" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2830,27 +2830,27 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2858,9 +2858,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I52" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2875,27 +2875,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2913,34 +2913,34 @@
       <c r="A54" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2948,9 +2948,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I54" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I54" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2965,27 +2965,27 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -2993,9 +2993,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3010,27 +3010,27 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3055,27 +3055,27 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3100,17 +3100,17 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3145,17 +3145,17 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3190,27 +3190,27 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -3235,27 +3235,27 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3263,9 +3263,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I61" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3280,27 +3280,27 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -3325,27 +3325,27 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -3370,17 +3370,17 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -3415,27 +3415,27 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>31 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -3443,9 +3443,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>31 KB</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -3488,9 +3488,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I66" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3505,27 +3505,27 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -3550,27 +3550,27 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -3595,27 +3595,27 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -3633,44 +3633,44 @@
       <c r="A70" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I70" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3685,32 +3685,32 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I71" s="12" t="inlineStr">
@@ -3730,27 +3730,27 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -3758,9 +3758,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I72" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I72" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3768,34 +3768,34 @@
       <c r="A73" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -3803,9 +3803,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3820,17 +3820,17 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -3848,9 +3848,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I74" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3858,44 +3858,44 @@
       <c r="A75" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H75" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I75" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I75" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3910,27 +3910,27 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H76" s="18" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H77" s="18" t="inlineStr">
@@ -4000,12 +4000,12 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -4045,95 +4045,119 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H79" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I79" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="52" customHeight="1">
+      <c r="A80" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D80" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E80" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G79" s="7" t="inlineStr">
+      <c r="G80" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H79" s="18" t="inlineStr">
+      <c r="H80" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I79" s="18" t="inlineStr">
+      <c r="I80" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="19" t="inlineStr">
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="28" customHeight="1">
-      <c r="A82" s="3" t="inlineStr">
+    <row r="83" ht="28" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr"/>
-      <c r="E82" s="3" t="inlineStr"/>
-      <c r="F82" s="3" t="inlineStr"/>
-      <c r="G82" s="3" t="inlineStr"/>
-      <c r="H82" s="3" t="inlineStr"/>
-      <c r="I82" s="3" t="inlineStr"/>
-    </row>
-    <row r="83" ht="32" customHeight="1">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr"/>
+      <c r="E83" s="3" t="inlineStr"/>
+      <c r="F83" s="3" t="inlineStr"/>
+      <c r="G83" s="3" t="inlineStr"/>
+      <c r="H83" s="3" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D83" s="20" t="n"/>
-      <c r="E83" s="20" t="n"/>
-      <c r="F83" s="20" t="n"/>
-      <c r="G83" s="20" t="n"/>
-      <c r="H83" s="20" t="n"/>
-      <c r="I83" s="21" t="n"/>
-    </row>
-    <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B84" s="6" t="n">
@@ -4141,7 +4165,7 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D84" s="20" t="n"/>
@@ -4152,17 +4176,17 @@
       <c r="I84" s="21" t="n"/>
     </row>
     <row r="85" ht="32" customHeight="1">
-      <c r="A85" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B85" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D85" s="20" t="n"/>
@@ -4173,9 +4197,9 @@
       <c r="I85" s="21" t="n"/>
     </row>
     <row r="86" ht="32" customHeight="1">
-      <c r="A86" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B86" s="6" t="n">
@@ -4183,7 +4207,7 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D86" s="20" t="n"/>
@@ -4194,17 +4218,17 @@
       <c r="I86" s="21" t="n"/>
     </row>
     <row r="87" ht="32" customHeight="1">
-      <c r="A87" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A87" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B87" s="6" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D87" s="20" t="n"/>
@@ -4215,17 +4239,17 @@
       <c r="I87" s="21" t="n"/>
     </row>
     <row r="88" ht="32" customHeight="1">
-      <c r="A88" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B88" s="6" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D88" s="20" t="n"/>
@@ -4236,17 +4260,17 @@
       <c r="I88" s="21" t="n"/>
     </row>
     <row r="89" ht="32" customHeight="1">
-      <c r="A89" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A89" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B89" s="6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、3町別の論点整理、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D89" s="20" t="n"/>
@@ -4257,17 +4281,17 @@
       <c r="I89" s="21" t="n"/>
     </row>
     <row r="90" ht="32" customHeight="1">
-      <c r="A90" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B90" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、3町別の論点整理、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D90" s="20" t="n"/>
@@ -4277,18 +4301,18 @@
       <c r="H90" s="20" t="n"/>
       <c r="I90" s="21" t="n"/>
     </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B91" s="22" t="n">
-        <v>75</v>
-      </c>
-      <c r="C91" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの70件、別スコープ5件</t>
+    <row r="91" ht="32" customHeight="1">
+      <c r="A91" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D91" s="20" t="n"/>
@@ -4298,8 +4322,29 @@
       <c r="H91" s="20" t="n"/>
       <c r="I91" s="21" t="n"/>
     </row>
-    <row r="93" ht="100" customHeight="1">
-      <c r="A93" s="23" t="inlineStr">
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B92" s="22" t="n">
+        <v>76</v>
+      </c>
+      <c r="C92" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの71件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D92" s="20" t="n"/>
+      <c r="E92" s="20" t="n"/>
+      <c r="F92" s="20" t="n"/>
+      <c r="G92" s="20" t="n"/>
+      <c r="H92" s="20" t="n"/>
+      <c r="I92" s="21" t="n"/>
+    </row>
+    <row r="94" ht="100" customHeight="1">
+      <c r="A94" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -4307,18 +4352,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A82:I82"/>
+    <mergeCell ref="C84:I84"/>
     <mergeCell ref="C89:I89"/>
-    <mergeCell ref="C84:I84"/>
-    <mergeCell ref="A81:I81"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C88:I88"/>
     <mergeCell ref="C87:I87"/>
     <mergeCell ref="C90:I90"/>
-    <mergeCell ref="C83:I83"/>
     <mergeCell ref="C91:I91"/>
     <mergeCell ref="C86:I86"/>
+    <mergeCell ref="C92:I92"/>
     <mergeCell ref="C85:I85"/>
-    <mergeCell ref="A93:H93"/>
+    <mergeCell ref="A94:H94"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -775,12 +775,12 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>750段落 124表</t>
+          <t>737段落 121表</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>2.7 MB</t>
+          <t>2.5 MB</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -2103,34 +2103,34 @@
       <c r="A36" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料（7章・12表）。この資料の位置づけ、3か年の得点の推移、指標群別・目標別の位置、全国の多くが取得し当区域が取得できていない項目、介護給付費の適正化、成果指向型配分枠、委員会にお諮りする事項。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,745〜1,746市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
+          <t>評価指標が「モニタリングの結果を外部の関係者を含む議論の場で検証を行っている」ことを求めているため、委員会にお諮りすること自体が交付金の要件に当たる。このため評価結果は計画本文に載せず本資料に整理し、計画本文には毎年度委員会へ報告し検証する手順のみを第1章第6節に定めた。明細列の全国該当率を算定し、3町とも0点で全国の半数以上が得点している項目38件・147点を特定した。最も全国該当率が高いのは介護給付費適正化事業の「3事業の全てを実施している」（96.9％）である。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>73段落 12表</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>257 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2138,9 +2138,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2155,17 +2155,17 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
+          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
+          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,745〜1,746市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>33 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2183,9 +2183,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2200,27 +2200,27 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
+          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
+          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>33 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2245,27 +2245,27 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
+          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>21 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2273,9 +2273,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2290,27 +2290,27 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
+          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>21 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2335,27 +2335,27 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
+          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
+          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2380,17 +2380,17 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
+          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
+          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2425,17 +2425,17 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
+          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2463,34 +2463,34 @@
       <c r="A44" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
+          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
+          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>14 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2498,9 +2498,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2508,34 +2508,34 @@
       <c r="A45" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
+          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
+          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>14 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2543,9 +2543,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2560,17 +2560,17 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2588,9 +2588,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2598,34 +2598,34 @@
       <c r="A47" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2633,9 +2633,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I47" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2650,37 +2650,37 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>22 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I48" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2695,22 +2695,22 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I49" s="12" t="inlineStr">
@@ -2740,27 +2740,27 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>72 KB</t>
+          <t>22 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -2768,9 +2768,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2785,27 +2785,27 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>43 KB</t>
+          <t>73 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2813,9 +2813,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2823,34 +2823,34 @@
       <c r="A52" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2875,27 +2875,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2903,9 +2903,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I53" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2920,27 +2920,27 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2958,34 +2958,34 @@
       <c r="A55" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -2993,9 +2993,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I55" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I55" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3010,27 +3010,27 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3038,9 +3038,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3055,27 +3055,27 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3100,27 +3100,27 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3145,17 +3145,17 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3190,17 +3190,17 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -3235,27 +3235,27 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3280,27 +3280,27 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -3308,9 +3308,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I62" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3325,27 +3325,27 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -3370,27 +3370,27 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -3415,17 +3415,17 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>31 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -3488,9 +3488,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3505,27 +3505,27 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>31 KB</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -3533,9 +3533,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I67" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3550,27 +3550,27 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -3595,27 +3595,27 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -3640,27 +3640,27 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -3678,44 +3678,44 @@
       <c r="A71" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I71" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3730,32 +3730,32 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I72" s="12" t="inlineStr">
@@ -3775,27 +3775,27 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -3803,9 +3803,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I73" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I73" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3813,34 +3813,34 @@
       <c r="A74" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -3848,9 +3848,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I74" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3865,17 +3865,17 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -3893,9 +3893,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I75" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3903,44 +3903,44 @@
       <c r="A76" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H76" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I76" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I76" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3955,27 +3955,27 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H77" s="18" t="inlineStr">
@@ -4000,12 +4000,12 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H78" s="18" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -4090,95 +4090,119 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H80" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I80" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="52" customHeight="1">
+      <c r="A81" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E81" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="F81" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G80" s="7" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H80" s="18" t="inlineStr">
+      <c r="H81" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I80" s="18" t="inlineStr">
+      <c r="I81" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="19" t="inlineStr">
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="28" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
+    <row r="84" ht="28" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr"/>
-      <c r="E83" s="3" t="inlineStr"/>
-      <c r="F83" s="3" t="inlineStr"/>
-      <c r="G83" s="3" t="inlineStr"/>
-      <c r="H83" s="3" t="inlineStr"/>
-      <c r="I83" s="3" t="inlineStr"/>
-    </row>
-    <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr"/>
+      <c r="E84" s="3" t="inlineStr"/>
+      <c r="F84" s="3" t="inlineStr"/>
+      <c r="G84" s="3" t="inlineStr"/>
+      <c r="H84" s="3" t="inlineStr"/>
+      <c r="I84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D84" s="20" t="n"/>
-      <c r="E84" s="20" t="n"/>
-      <c r="F84" s="20" t="n"/>
-      <c r="G84" s="20" t="n"/>
-      <c r="H84" s="20" t="n"/>
-      <c r="I84" s="21" t="n"/>
-    </row>
-    <row r="85" ht="32" customHeight="1">
-      <c r="A85" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B85" s="6" t="n">
@@ -4186,7 +4210,7 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D85" s="20" t="n"/>
@@ -4197,17 +4221,17 @@
       <c r="I85" s="21" t="n"/>
     </row>
     <row r="86" ht="32" customHeight="1">
-      <c r="A86" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B86" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D86" s="20" t="n"/>
@@ -4218,9 +4242,9 @@
       <c r="I86" s="21" t="n"/>
     </row>
     <row r="87" ht="32" customHeight="1">
-      <c r="A87" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A87" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B87" s="6" t="n">
@@ -4228,7 +4252,7 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D87" s="20" t="n"/>
@@ -4239,17 +4263,17 @@
       <c r="I87" s="21" t="n"/>
     </row>
     <row r="88" ht="32" customHeight="1">
-      <c r="A88" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A88" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B88" s="6" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D88" s="20" t="n"/>
@@ -4260,17 +4284,17 @@
       <c r="I88" s="21" t="n"/>
     </row>
     <row r="89" ht="32" customHeight="1">
-      <c r="A89" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B89" s="6" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D89" s="20" t="n"/>
@@ -4281,17 +4305,17 @@
       <c r="I89" s="21" t="n"/>
     </row>
     <row r="90" ht="32" customHeight="1">
-      <c r="A90" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A90" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B90" s="6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、3町別の論点整理、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D90" s="20" t="n"/>
@@ -4302,17 +4326,17 @@
       <c r="I90" s="21" t="n"/>
     </row>
     <row r="91" ht="32" customHeight="1">
-      <c r="A91" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B91" s="6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D91" s="20" t="n"/>
@@ -4322,18 +4346,18 @@
       <c r="H91" s="20" t="n"/>
       <c r="I91" s="21" t="n"/>
     </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B92" s="22" t="n">
-        <v>76</v>
-      </c>
-      <c r="C92" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの71件、別スコープ5件</t>
+    <row r="92" ht="32" customHeight="1">
+      <c r="A92" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D92" s="20" t="n"/>
@@ -4343,8 +4367,29 @@
       <c r="H92" s="20" t="n"/>
       <c r="I92" s="21" t="n"/>
     </row>
-    <row r="94" ht="100" customHeight="1">
-      <c r="A94" s="23" t="inlineStr">
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B93" s="22" t="n">
+        <v>77</v>
+      </c>
+      <c r="C93" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの72件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D93" s="20" t="n"/>
+      <c r="E93" s="20" t="n"/>
+      <c r="F93" s="20" t="n"/>
+      <c r="G93" s="20" t="n"/>
+      <c r="H93" s="20" t="n"/>
+      <c r="I93" s="21" t="n"/>
+    </row>
+    <row r="95" ht="100" customHeight="1">
+      <c r="A95" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -4352,18 +4397,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A82:I82"/>
-    <mergeCell ref="C84:I84"/>
     <mergeCell ref="C89:I89"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C88:I88"/>
+    <mergeCell ref="A95:H95"/>
     <mergeCell ref="C87:I87"/>
     <mergeCell ref="C90:I90"/>
     <mergeCell ref="C91:I91"/>
     <mergeCell ref="C86:I86"/>
     <mergeCell ref="C92:I92"/>
     <mergeCell ref="C85:I85"/>
-    <mergeCell ref="A94:H94"/>
+    <mergeCell ref="A83:I83"/>
+    <mergeCell ref="C93:I93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2148,34 +2148,34 @@
       <c r="A37" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
+          <t>介護保険法第115条の45第5項の介護給付等費用適正化事業として行うケアプランの点検の実施要領の案（14章・15表）。目的と根拠、点検の範囲、対象、抽出方法、点検の視点、方法と年間の工程、件数と計上の方法、点検後の指導と改善の確認、有料老人ホーム等の入居者、リハビリテーション専門職等の関与、実施体制、評価指標と公表、交付金の評価指標との対応、確定を要する事項。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,745〜1,746市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
+          <t>介護給付適正化の主要3事業のうちケアプランの点検のみが令和6〜8年度とも3町いずれも0点であり、このため「3事業の全てを実施している」（全国該当率96.9％）が3町とも0点となっている。国が必須とする2帳票（認定調査状況と利用サービス不一致一覧表、支給限度額一定割合超一覧表）を第1順位の抽出源とし、件数は国の計上方法（対象者数×点検対象とした月数）による。受託者案は令和9年度264件（11事業所×4人×6か月分）、令和10年度396件、令和11年度528件。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>105段落 15表</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>50 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2183,9 +2183,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2200,17 +2200,17 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
+          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
+          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,745〜1,746市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>33 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2228,9 +2228,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2245,27 +2245,27 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
+          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
+          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>33 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2290,27 +2290,27 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
+          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>21 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2318,9 +2318,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2335,27 +2335,27 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
+          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>21 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2380,27 +2380,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
+          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
+          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2425,17 +2425,17 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
+          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
+          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
+          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2508,34 +2508,34 @@
       <c r="A45" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
+          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
+          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>14 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2543,9 +2543,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2553,34 +2553,34 @@
       <c r="A46" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
+          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
+          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>14 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2588,9 +2588,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2605,17 +2605,17 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2633,9 +2633,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2643,34 +2643,34 @@
       <c r="A48" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2678,9 +2678,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2695,37 +2695,37 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>22 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I49" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2740,22 +2740,22 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I50" s="12" t="inlineStr">
@@ -2785,27 +2785,27 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>73 KB</t>
+          <t>22 KB</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2813,9 +2813,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2830,27 +2830,27 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>43 KB</t>
+          <t>74 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2858,9 +2858,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2868,34 +2868,34 @@
       <c r="A53" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2920,27 +2920,27 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2948,9 +2948,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I54" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2965,27 +2965,27 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -3003,34 +3003,34 @@
       <c r="A56" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3038,9 +3038,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I56" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I56" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3055,27 +3055,27 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3083,9 +3083,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3100,27 +3100,27 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3145,27 +3145,27 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3190,17 +3190,17 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -3235,17 +3235,17 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3280,27 +3280,27 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -3325,27 +3325,27 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -3353,9 +3353,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I63" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3370,27 +3370,27 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -3415,27 +3415,27 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -3460,17 +3460,17 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3505,27 +3505,27 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>31 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -3533,9 +3533,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I67" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3550,27 +3550,27 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>31 KB</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -3578,9 +3578,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I68" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3595,27 +3595,27 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -3640,27 +3640,27 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -3685,27 +3685,27 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -3723,44 +3723,44 @@
       <c r="A72" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I72" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3775,32 +3775,32 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I73" s="12" t="inlineStr">
@@ -3820,27 +3820,27 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -3848,9 +3848,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I74" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3858,34 +3858,34 @@
       <c r="A75" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -3893,9 +3893,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3910,17 +3910,17 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -3938,9 +3938,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I76" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3948,44 +3948,44 @@
       <c r="A77" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H77" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I77" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I77" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4000,27 +4000,27 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H78" s="18" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H79" s="18" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -4135,95 +4135,119 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H81" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I81" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="52" customHeight="1">
+      <c r="A82" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D82" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E82" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G81" s="7" t="inlineStr">
+      <c r="G82" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H81" s="18" t="inlineStr">
+      <c r="H82" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I81" s="18" t="inlineStr">
+      <c r="I82" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="19" t="inlineStr">
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="28" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr"/>
-      <c r="E84" s="3" t="inlineStr"/>
-      <c r="F84" s="3" t="inlineStr"/>
-      <c r="G84" s="3" t="inlineStr"/>
-      <c r="H84" s="3" t="inlineStr"/>
-      <c r="I84" s="3" t="inlineStr"/>
-    </row>
-    <row r="85" ht="32" customHeight="1">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr"/>
+      <c r="E85" s="3" t="inlineStr"/>
+      <c r="F85" s="3" t="inlineStr"/>
+      <c r="G85" s="3" t="inlineStr"/>
+      <c r="H85" s="3" t="inlineStr"/>
+      <c r="I85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86" ht="32" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D85" s="20" t="n"/>
-      <c r="E85" s="20" t="n"/>
-      <c r="F85" s="20" t="n"/>
-      <c r="G85" s="20" t="n"/>
-      <c r="H85" s="20" t="n"/>
-      <c r="I85" s="21" t="n"/>
-    </row>
-    <row r="86" ht="32" customHeight="1">
-      <c r="A86" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B86" s="6" t="n">
@@ -4231,7 +4255,7 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D86" s="20" t="n"/>
@@ -4242,17 +4266,17 @@
       <c r="I86" s="21" t="n"/>
     </row>
     <row r="87" ht="32" customHeight="1">
-      <c r="A87" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B87" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D87" s="20" t="n"/>
@@ -4263,9 +4287,9 @@
       <c r="I87" s="21" t="n"/>
     </row>
     <row r="88" ht="32" customHeight="1">
-      <c r="A88" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B88" s="6" t="n">
@@ -4273,7 +4297,7 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D88" s="20" t="n"/>
@@ -4284,17 +4308,17 @@
       <c r="I88" s="21" t="n"/>
     </row>
     <row r="89" ht="32" customHeight="1">
-      <c r="A89" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B89" s="6" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D89" s="20" t="n"/>
@@ -4305,17 +4329,17 @@
       <c r="I89" s="21" t="n"/>
     </row>
     <row r="90" ht="32" customHeight="1">
-      <c r="A90" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B90" s="6" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D90" s="20" t="n"/>
@@ -4326,17 +4350,17 @@
       <c r="I90" s="21" t="n"/>
     </row>
     <row r="91" ht="32" customHeight="1">
-      <c r="A91" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A91" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B91" s="6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、ケアプラン点検実施要領（案）、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D91" s="20" t="n"/>
@@ -4347,17 +4371,17 @@
       <c r="I91" s="21" t="n"/>
     </row>
     <row r="92" ht="32" customHeight="1">
-      <c r="A92" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D92" s="20" t="n"/>
@@ -4367,18 +4391,18 @@
       <c r="H92" s="20" t="n"/>
       <c r="I92" s="21" t="n"/>
     </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B93" s="22" t="n">
-        <v>77</v>
-      </c>
-      <c r="C93" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの72件、別スコープ5件</t>
+    <row r="93" ht="32" customHeight="1">
+      <c r="A93" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D93" s="20" t="n"/>
@@ -4388,8 +4412,29 @@
       <c r="H93" s="20" t="n"/>
       <c r="I93" s="21" t="n"/>
     </row>
-    <row r="95" ht="100" customHeight="1">
-      <c r="A95" s="23" t="inlineStr">
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B94" s="22" t="n">
+        <v>78</v>
+      </c>
+      <c r="C94" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの73件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D94" s="20" t="n"/>
+      <c r="E94" s="20" t="n"/>
+      <c r="F94" s="20" t="n"/>
+      <c r="G94" s="20" t="n"/>
+      <c r="H94" s="20" t="n"/>
+      <c r="I94" s="21" t="n"/>
+    </row>
+    <row r="96" ht="100" customHeight="1">
+      <c r="A96" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -4400,14 +4445,14 @@
     <mergeCell ref="C89:I89"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C88:I88"/>
-    <mergeCell ref="A95:H95"/>
+    <mergeCell ref="A84:I84"/>
+    <mergeCell ref="A96:H96"/>
     <mergeCell ref="C87:I87"/>
     <mergeCell ref="C90:I90"/>
     <mergeCell ref="C91:I91"/>
     <mergeCell ref="C86:I86"/>
     <mergeCell ref="C92:I92"/>
-    <mergeCell ref="C85:I85"/>
-    <mergeCell ref="A83:I83"/>
+    <mergeCell ref="C94:I94"/>
     <mergeCell ref="C93:I93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1615,37 +1615,37 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
+          <t>第10期計画_9月作業_アンケート分析の作業状況.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>計画素案から協議用素案（令和8年8月時点）への修正の記録。修正の一覧、第9期評価の精緻化、アンケート集計分析の反映、人口推計の補正の反映、解消した確認事項、残る確認事項と次の作業。</t>
+          <t>業務仕様書５の令和8年9月工程のうち、アンケート調査（4調査）の集計・分析について作業状況を整理したもの（10シート）。4調査の段階別の状況、成果品と収録内容、完了した作業16件、未了の作業8件と着手の条件、点検事項35件の状況、発注者のご判断を待っている事項4件、代表KPIの基準値の確定状況、計画素案への反映の状況13箇所、9月内の作業工程。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>修正9件（差替2・是正1・追加6）。第9期19施策に調査の裏づけと代表KPIの対応で判定を付し（強5・中5・弱4・なし5）、調査に所見があるが対応する施策を確認できない5領域を明らかにした。算定不可としていた代表KPI4項目（H07・H08・H12・H16）はいずれも代理指標により算定できることを確認し、削除する項目はない。訪問介護13事業所を全数把握（181人）し、高齢者世帯の記述を是正した。解消した確認事項5件、前提が変わった確認事項3件。</t>
+          <t>集計・クロス集計・分析は4調査とも完了しており、9月に残っているのは確定値化と計画本文への反映である。未了8件のうち受託者の作業だけで進むのは1件で、5件は発注者のご判断又は資料の提供を待っている。最も多くの作業を止めているのは確認事項No.8（3調査の点検事項の取扱い）であり、この1件の決定により照会の発出から成果品の更新まで一連の作業が動く。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I25" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -1653,34 +1653,34 @@
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>概要版の頁数・体裁・掲載内容を定めるための構成案。位置付けと制約、3案の比較、推奨案の頁割、掲載する図表の候補、本編との対応と用語の言い換え、パブリックコメントとの関係と2版構成、決定を要する事項、自己点検記録。</t>
+          <t>計画素案から協議用素案（令和8年8月時点）への修正の記録。修正の一覧、第9期評価の精緻化、アンケート集計分析の反映、人口推計の補正の反映、解消した確認事項、残る確認事項と次の作業。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>概要版はパブリックコメント（令和9年1月・2週間・WEB）に用いるため、「計画の要約」ではなく「何を決めようとしているのかが分かる文書」として設計する。A4判8頁（表紙＋本文6頁＋裏表紙）を推奨し、本編6章を1章1頁で割り付ける。パブリックコメントの時点では保険料が確定しないため、パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版構成とする。決定を要する事項6件を07シートに整理した。08シートの自己点検記録8件には、本案の前提そのものへの指摘3件を含む。</t>
+          <t>修正9件（差替2・是正1・追加6）。第9期19施策に調査の裏づけと代表KPIの対応で判定を付し（強5・中5・弱4・なし5）、調査に所見があるが対応する施策を確認できない5領域を明らかにした。算定不可としていた代表KPI4項目（H07・H08・H12・H16）はいずれも代理指標により算定できることを確認し、削除する項目はない。訪問介護13事業所を全数把握（181人）し、高齢者世帯の記述を是正した。解消した確認事項5件、前提が変わった確認事項3件。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -1688,9 +1688,9 @@
           <t>作成済</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -1698,34 +1698,34 @@
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールと自己点検記録。</t>
+          <t>概要版の頁数・体裁・掲載内容を定めるための構成案。位置付けと制約、3案の比較、推奨案の頁割、掲載する図表の候補、本編との対応と用語の言い換え、パブリックコメントとの関係と2版構成、決定を要する事項、自己点検記録。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率のみである。住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）により、社人研 令和5年推計の基準年から最初の推計年までの5年で突合した。3町計では65〜74歳を3年で3.8％上方に、75歳以上を0.7％下方に補正する。社人研は前期高齢者の減少を実績より速く見込んでいる。町別では75歳以上の向きが逆で、東川町が上方（＋3.2％）・東神楽町が下方（▲4.2％）・美瑛町が境界である。町別の適用は、町別の第1号被保険者数の受領まで保留する。</t>
+          <t>概要版はパブリックコメント（令和9年1月・2週間・WEB）に用いるため、「計画の要約」ではなく「何を決めようとしているのかが分かる文書」として設計する。A4判8頁（表紙＋本文6頁＋裏表紙）を推奨し、本編6章を1章1頁で割り付ける。パブリックコメントの時点では保険料が確定しないため、パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版構成とする。決定を要する事項6件を07シートに整理した。08シートの自己点検記録8件には、本案の前提そのものへの指摘3件を含む。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1743,44 +1743,44 @@
       <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
+          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールと自己点検記録。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
+          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率のみである。住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）により、社人研 令和5年推計の基準年から最初の推計年までの5年で突合した。3町計では65〜74歳を3年で3.8％上方に、75歳以上を0.7％下方に補正する。社人研は前期高齢者の減少を実績より速く見込んでいる。町別では75歳以上の向きが逆で、東川町が上方（＋3.2％）・東神楽町が下方（▲4.2％）・美瑛町が境界である。町別の適用は、町別の第1号被保険者数の受領まで保留する。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>7シート</t>
-        </is>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -1795,32 +1795,32 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
+          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
+          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>44 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
@@ -1840,32 +1840,32 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>第1回委員会に向けた確認事項の依頼文書。</t>
+          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
+          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>44 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>第9版</t>
+          <t>最新</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
@@ -1878,44 +1878,44 @@
       <c r="A31" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>給付実績データ（大雪地区広域連合・東川町・東神楽町　令和6〜8年度）の受領点検。34サービス×7要介護度の月平均利用者数・1人1月あたり利用回数・1人1月あたり給付費、給付費の総額と第9期計画との乖離。</t>
+          <t>第1回委員会に向けた確認事項の依頼文書。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>個人情報の取扱いについてご確認をお願いする事項を00シートに掲げている。代表KPI H15の乖離率は、分母を標準給付費見込額とすると▲1.37％、総給付費とすると＋5.49％となる。分母の定義のご決定を要する。</t>
+          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
-        </is>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+          <t>第9版</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -1930,27 +1930,27 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業を優先順位をもとに整理したもの（8シート）。富良野市のサービスガイドと鹿児島県の生活支援体制整備事業取組事例集を参照し、当区域の実績データと突き合わせて20件を掲げている。</t>
+          <t>給付実績データ（大雪地区広域連合・東川町・東神楽町　令和6〜8年度）の受領点検。34サービス×7要介護度の月平均利用者数・1人1月あたり利用回数・1人1月あたり給付費、給付費の総額と第9期計画との乖離。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>義務・欠落・実行・効果・主体の5項目を各3点で採点し、優先度A4件・B7件・C9件に分けた。優先度Aは、総合事業の事業評価（3町とも未実施）、生活支援体制整備の区域共通運営、24時間対応サービスの確保方策、包括的支援事業・任意事業の実績管理である。優先順位は受託者の案であり、発注者の決定を要する。</t>
+          <t>個人情報の取扱いについてご確認をお願いする事項を00シートに掲げている。代表KPI H15の乖離率は、分母を標準給付費見込額とすると▲1.37％、総給付費とすると＋5.49％となる。分母の定義のご決定を要する。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>44 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1968,34 +1968,34 @@
       <c r="A33" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>富良野市「介護・高齢者福祉サービスガイド」と同じ構成による当区域のサービスガイドの構成案（15章）。</t>
+          <t>広域連合において行うべき事業を優先順位をもとに整理したもの（8シート）。富良野市のサービスガイドと鹿児島県の生活支援体制整備事業取組事例集を参照し、当区域の実績データと突き合わせて20件を掲げている。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>介護保険のしくみ・手続・費用と、区域内74事業所の一覧は原案を作成した。3町の高齢者福祉サービス（介護保険外）、社会福祉協議会のサービス、事業所の所在地・電話番号は記入枠としている。3町への照会（事業の優先順位 事業No.14）により確定する。</t>
+          <t>義務・欠落・実行・効果・主体の5項目を各3点で採点し、優先度A4件・B7件・C9件に分けた。優先度Aは、総合事業の事業評価（3町とも未実施）、生活支援体制整備の区域共通運営、24時間対応サービスの確保方策、包括的支援事業・任意事業の実績管理である。優先順位は受託者の案であり、発注者の決定を要する。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>80段落 27表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>59 KB</t>
+          <t>44 KB</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -2013,34 +2013,34 @@
       <c r="A34" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町別の論点整理.xlsx</t>
+          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>令和8年10月・11月の3町協議に向けた論点整理（7シート）。町別の現在地、総合事業の町別実施状況、交付金評価の町別得点、町ごとの論点、3町共通の論点、協議の進め方。</t>
+          <t>富良野市「介護・高齢者福祉サービスガイド」と同じ構成による当区域のサービスガイドの構成案（15章）。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>町別の差が最も大きいのは総合事業である。週1回以上の通いの場11箇所はすべて東神楽町にあり、地域リハビリテーション活動支援事業は美瑛町のみ、国保データベースの活用は東川町のみ未実施である。交付金の合計得点は東神楽町が3か年とも最も高く、令和6→8年度で東神楽町＋11点に対し東川町▲1点・美瑛町▲4点である。町ごとの論点12件と3町共通の論点8件を掲げている。</t>
+          <t>介護保険のしくみ・手続・費用と、区域内74事業所の一覧は原案を作成した。3町の高齢者福祉サービス（介護保険外）、社会福祉協議会のサービス、事業所の所在地・電話番号は記入枠としている。3町への照会（事業の優先順位 事業No.14）により確定する。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>80段落 27表</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>59 KB</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -2058,34 +2058,34 @@
       <c r="A35" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_3町別の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階。標準給付費見込額・地域支援事業費・第1号被保険者負担分・調整交付金・基金取崩額から保険料基準額までを組み立てたもの（11シート）。</t>
+          <t>令和8年10月・11月の3町協議に向けた論点整理（7シート）。町別の現在地、総合事業の町別実施状況、交付金評価の町別得点、町ごとの論点、3町共通の論点、協議の進め方。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>第9期の算定を再現すると公表値6,428円と一致する。基本ケースの暫定値は月額6,740円で、第9期の条例基準額6,400円を340円上回る。感度分析8件のうち最も大きいレバーは給付費の水準で幅は596円。確定を要する事項9件を10シートに掲げている。確定値ではない。</t>
+          <t>町別の差が最も大きいのは総合事業である。週1回以上の通いの場11箇所はすべて東神楽町にあり、地域リハビリテーション活動支援事業は美瑛町のみ、国保データベースの活用は東川町のみ未実施である。交付金の合計得点は東神楽町が3か年とも最も高く、令和6→8年度で東神楽町＋11点に対し東川町▲1点・美瑛町▲4点である。町ごとの論点12件と3町共通の論点8件を掲げている。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>11シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>36 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -2103,34 +2103,34 @@
       <c r="A36" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料（7章・12表）。この資料の位置づけ、3か年の得点の推移、指標群別・目標別の位置、全国の多くが取得し当区域が取得できていない項目、介護給付費の適正化、成果指向型配分枠、委員会にお諮りする事項。</t>
+          <t>将来推計 第3段階。標準給付費見込額・地域支援事業費・第1号被保険者負担分・調整交付金・基金取崩額から保険料基準額までを組み立てたもの（11シート）。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>評価指標が「モニタリングの結果を外部の関係者を含む議論の場で検証を行っている」ことを求めているため、委員会にお諮りすること自体が交付金の要件に当たる。このため評価結果は計画本文に載せず本資料に整理し、計画本文には毎年度委員会へ報告し検証する手順のみを第1章第6節に定めた。明細列の全国該当率を算定し、3町とも0点で全国の半数以上が得点している項目38件・147点を特定した。最も全国該当率が高いのは介護給付費適正化事業の「3事業の全てを実施している」（96.9％）である。</t>
+          <t>第9期の算定を再現すると公表値6,428円と一致する。基本ケースの暫定値は月額6,740円で、第9期の条例基準額6,400円を340円上回る。感度分析8件のうち最も大きいレバーは給付費の水準で幅は596円。確定を要する事項9件を10シートに掲げている。確定値ではない。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>73段落 12表</t>
+          <t>11シート</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>257 KB</t>
+          <t>36 KB</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2148,34 +2148,34 @@
       <c r="A37" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第115条の45第5項の介護給付等費用適正化事業として行うケアプランの点検の実施要領の案（14章・15表）。目的と根拠、点検の範囲、対象、抽出方法、点検の視点、方法と年間の工程、件数と計上の方法、点検後の指導と改善の確認、有料老人ホーム等の入居者、リハビリテーション専門職等の関与、実施体制、評価指標と公表、交付金の評価指標との対応、確定を要する事項。</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料（7章・12表）。この資料の位置づけ、3か年の得点の推移、指標群別・目標別の位置、全国の多くが取得し当区域が取得できていない項目、介護給付費の適正化、成果指向型配分枠、委員会にお諮りする事項。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>介護給付適正化の主要3事業のうちケアプランの点検のみが令和6〜8年度とも3町いずれも0点であり、このため「3事業の全てを実施している」（全国該当率96.9％）が3町とも0点となっている。国が必須とする2帳票（認定調査状況と利用サービス不一致一覧表、支給限度額一定割合超一覧表）を第1順位の抽出源とし、件数は国の計上方法（対象者数×点検対象とした月数）による。受託者案は令和9年度264件（11事業所×4人×6か月分）、令和10年度396件、令和11年度528件。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。</t>
+          <t>評価指標が「モニタリングの結果を外部の関係者を含む議論の場で検証を行っている」ことを求めているため、委員会にお諮りすること自体が交付金の要件に当たる。このため評価結果は計画本文に載せず本資料に整理し、計画本文には毎年度委員会へ報告し検証する手順のみを第1章第6節に定めた。明細列の全国該当率を算定し、3町とも0点で全国の半数以上が得点している項目38件・147点を特定した。最も全国該当率が高いのは介護給付費適正化事業の「3事業の全てを実施している」（96.9％）である。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>105段落 15表</t>
+          <t>73段落 12表</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>257 KB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2193,34 +2193,34 @@
       <c r="A38" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
+          <t>介護保険法第115条の45第5項の介護給付等費用適正化事業として行うケアプランの点検の実施要領の案（14章・15表）。目的と根拠、点検の範囲、対象、抽出方法、点検の視点、方法と年間の工程、件数と計上の方法、点検後の指導と改善の確認、有料老人ホーム等の入居者、リハビリテーション専門職等の関与、実施体制、評価指標と公表、交付金の評価指標との対応、確定を要する事項。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,745〜1,746市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
+          <t>介護給付適正化の主要3事業のうちケアプランの点検のみが令和6〜8年度とも3町いずれも0点であり、このため「3事業の全てを実施している」（全国該当率96.9％）が3町とも0点となっている。国が必須とする2帳票（認定調査状況と利用サービス不一致一覧表、支給限度額一定割合超一覧表）を第1順位の抽出源とし、件数は国の計上方法（対象者数×点検対象とした月数）による。受託者案は令和9年度264件（11事業所×4人×6か月分）、令和10年度396件、令和11年度528件。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>105段落 15表</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>34 KB</t>
+          <t>50 KB</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2228,9 +2228,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2245,17 +2245,17 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
+          <t>保険者機能強化推進交付金等の全国集計結果（令和6〜8年度）の原本と、令和8年度評価指標（42頁）の受領点検（8シート）。収録値との突合、配点の検証、全国・北海道との3か年比較、指標群別の位置、成果指向型配分枠。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
+          <t>3町×3か年の198値をすべて突合し不一致はなかった。原本を得たことで全国1,745〜1,746市町村・北海道179市町村との比較を3か年に広げられた。全国平均が3年で32.5点上がる一方3町平均は2.0点の変化にとどまり、対全国比は78.6％から73.4％へ低下している。令和8年度の全国順位（下位からの位置）は東川町6.7％・美瑛町6.0％で全国の下位1割以内である。評価指標により、評価の対象が令和7年度の取組であること、成果指向型配分枠（100点）が新設されたこと、目標Ⅳ成果指標群の満点が100点であることが確定した。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>33 KB</t>
+          <t>34 KB</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -2273,9 +2273,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2290,27 +2290,27 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
+          <t>見込量算定と保険料試算の計算方法を、国の様式（介護保険事業計画作成支援ツール及び自然体推計の計算過程確認シートのガイド）並びに見える化システムの将来推計と対照したもの（8シート）。保険料算定式の対照、割増率の項目別検算、見込量推計の手順の対照、上限1.1・下限0.9への適合、補正の設計。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
+          <t>式の骨格・補正後被保険者数の算定・予定収納率は国の様式と一致した。地域支援事業費の範囲と調整交付金の算定基礎の総合事業費を修正し、基本ケースは月額6,755円から6,740円に改まった。割増率1.05909は計画作成支援ツールの実績値による項目の積上げで再現でき（差0.0005％）、単一の係数ではなく特定入所者介護サービス費・高額介護サービス費等の合計として説明できるようになった。給付費を見える化の自然体推計の総額に認定者数の比を乗じて置き直している点は国の手順と対応せず、見える化システムの再出力を要する（確認事項No.68）。</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>33 KB</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -2335,27 +2335,27 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応（7シート）。社人研を用いている箇所の棚卸し、総合戦略の目標人口の状況、案Cの組立て、3案の比較、保険料への影響、確定を要する事項。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
+          <t>総合戦略の目標は総人口のみで年齢階級別の内訳がなく、美瑛町には目標そのものが設定されていない。総人口は総合戦略の目標、年齢階級別は住民基本台帳の実績趨勢による案Cを組み立て、成果品に反映した。指数による概算では令和11年度の月額基準額は案A（社人研）6,670円・案B（社人研＋補正）6,578円・案C 6,774円で、基礎の選び方により約200円動く。通して再計算した案Cは6,755円であり、その後の算定方法の点検により6,740円に改めた。採用案のご確認（確認事項No.63）を要する。</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>21 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -2363,9 +2363,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2380,27 +2380,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4（年齢別人口割合）の受領点検（6シート）。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
+          <t>町別の75歳以上人口を、按分による推計値から公表値に置き換えた。差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。3町計の補正係数（65〜74歳1.0377・75歳以上0.9927）と保険料の試算には影響しない。自己点検の指摘No.5（重大）と計画素案の［要確認］2件が解消した。</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>27 KB</t>
+          <t>21 KB</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -2425,27 +2425,27 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
+          <t>地域包括ケア「見える化」システムの総括表（6シート）と管理指標グラフ（7指標）の受領点検。第7期から第9期までの計画値・実績値・対計画比。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
+          <t>第9期（令和6・7年度）の対計画比が公表資料で揃い、成果評価が成立する見通しとなった。代表KPI H15の基準値は令和6年度▲3.66％・令和7年度▲2.17％でいずれも目標の±5％以内。「第9期累計」欄を達成率と読まないなど、読み方の注意6点を掲げている。</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>27 KB</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
+          <t>総合事業の実施状況に関する調査（令和6年度・市町村Ⅰ〜Ⅲ）の受領点検。通いの場・一般介護予防事業・サービス活動事業の町別実績。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
+          <t>代表KPI H05の基準値が令和6年度3.53％（参加者330人／65歳以上人口9,346人）と確定した。週1回以上開催の11箇所はすべて東神楽町である。</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>24 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）と月報（令和8年4〜7月）の受領点検。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
+          <t>介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数が確定し、将来推計の第3段階の前提がほぼ揃った。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>24 KB</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -2553,34 +2553,34 @@
       <c r="A46" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
+          <t>令和6年度介護保険特別会計決算書の受領点検。款項別の決算額と介護給付費準備基金の推移。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
+          <t>年報様式4との対照22項目はすべて一致した。実質収支額142,873,961円に対し基金への積立ては運用益232,197円のみである。</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>14 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2588,9 +2588,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2598,34 +2598,34 @@
       <c r="A47" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
+          <t>介護保険事業財政調整基金条例及び処遇改善臨時特例基金条例の確認。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
+          <t>第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）を令和6年度末残高が26,492,172円上回る。上限の読み方と第10期の取崩方針について確認事項No.53としてご協議をお願いしている。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>17 KB</t>
+          <t>14 KB</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2633,9 +2633,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I47" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2650,17 +2650,17 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
+          <t>令和8年8月28日に受領した9件（交付金の全国集計結果3か年、要介護認定の集計帳票3か年、在宅医療機関・薬局リスト、総合事業の指標値）の点検結果。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
+          <t>交付金の評価が構成3町別に行われていることが判明した。3町別・3か年の得点と全国順位、要介護認定の申請・認定・所要日数、成果品への反映箇所9件を整理している。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>17 KB</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -2678,9 +2678,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2688,34 +2688,34 @@
       <c r="A49" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
+          <t>社会資源一覧（74事業所・延べ1,460.5人）における従業員数の重複計上の整理。重複の候補8組（200人＋要確認52人）、数え方の3案、供給制約の推定への影響。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
+          <t>令和8年8月26日の進捗確認の打合せでのご指示に対応するもの。01シートに「ご確認欄」を設け、同じ職員かどうかをご記入いただく様式としている。受託者の案は、供給制約の推定に施設単位の実人数を用い、サービス別の分析には延べを用いる使い分けである。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -2723,9 +2723,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -2740,37 +2740,37 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
+          <t>発注者へ送付する資料だけを掲げた一覧。ご確認・ご決定をお願いする事項、今後更新する箇所。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
+          <t>送付時に用いる一覧。本一覧（成果品一覧）は内部保管資料を含むため、納品時に用いる。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>22 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2785,22 +2785,22 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
+          <t>受託者の点検対応の記録。点検指摘13件への対応、事実確認の結果、受入ゲートの充足状況。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
+          <t>作業過程の記録であり、送付資料としては用いない（内部保管）。ご決定を要する事項は「発注者確認事項一覧」に移してある。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I51" s="12" t="inlineStr">
@@ -2830,27 +2830,27 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
+          <t>成果品ごとの送付区分（送付・条件付き・内部保管・対象外）と理由、送付資料で用いない表現、送付前の点検手順。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
+          <t>本一覧の「送付区分」欄の根拠。02シートに用いない表現13件を、03シートに送付前の点検手順7件を示している。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>74 KB</t>
+          <t>22 KB</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2858,9 +2858,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I52" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -2875,27 +2875,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
+          <t>仕様書４（1）〜（12）の業務別進捗、月別工程、確認事項、成果品、調査別の状況、資料提供依頼。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
+          <t>業務の進捗と工程の管理。状態欄はプルダウンで色が変わる。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>43 KB</t>
+          <t>74 KB</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2903,9 +2903,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I53" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -2913,34 +2913,34 @@
       <c r="A54" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
+          <t>計画本文から外に出した事項（変更履歴、目次の新設、本文の注記）の管理。打合せ確認事項を文言と数値・計算根拠に切り分けている。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>第3章の根拠。24シート。</t>
+          <t>打合せの資料。03シートが文言、04シートが数値・計算根拠。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>162 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -2965,27 +2965,27 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
+          <t>第9期計画の評価・検証。主要所見と代表KPIの3軸評価。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
+          <t>第3章の根拠。24シート。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>55 KB</t>
+          <t>162 KB</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -2993,9 +2993,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I55" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3010,27 +3010,27 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
+          <t>受託者による自己点検。成り立たない可能性のある主張を批判的に洗い出す。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
+          <t>指摘29件（重大11・中14・軽微4）。うち5件は資料の受領により指摘のとおりであることが確認され記述を訂正した。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>55 KB</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3048,34 +3048,34 @@
       <c r="A57" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
+          <t>全成果物の主張を領域9区分×根拠水準5階層でMECEに分類したもの。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
+          <t>どの記述がどこまで確定しているかの一覧。主張59件。07シートに記述ルールと禁止する記述を定めている。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>111 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3083,9 +3083,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I57" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3100,27 +3100,27 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
+          <t>健康とくらしの調査（令和7年度・個票4,729票）のクロス集計と分析。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
+          <t>小学校区12地区別、年齢調整による地域比較、同規模保険者40との比較。24シート。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>111 KB</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3128,9 +3128,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3145,27 +3145,27 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
+          <t>見える化B4・B5・B6系列による認定率の年齢調整分析。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
+          <t>年齢構成を調整すると認定率が低下していること、中重度は低下が続き軽度が上昇に転じたことを示す。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3190,27 +3190,27 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
+          <t>介護サービス自給率（δ）・地域差指数（D49）・保険料（C1）による上川管内での位置の分析。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
+          <t>第2章第2節・第3節、第6章第6節の根拠。15シート。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -3235,17 +3235,17 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
+          <t>見える化A系列（2000〜2050年）による将来推計の基礎の検証。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>07シートに人口推計の基礎の選択の判断材料。社人研推計の採用は受託者の案であり、キックオフ会議で発注者のご意向を確認する。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -3280,17 +3280,17 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
+          <t>将来推計の第1段階。人口と認定者数を3シナリオで推計。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>上川管内21保険者、北海道、全国との対比。</t>
+          <t>第6章第1節の根拠。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -3325,27 +3325,27 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
+          <t>保険料水準と保険者機能強化推進交付金の評価の他団体比較。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
+          <t>上川管内21保険者、北海道、全国との対比。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>37 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -3370,27 +3370,27 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
+          <t>第9期の16段階の所得段階と低所得者軽減の妥当性の検証、及び算定ロジックの整理。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節・第6章の根拠。</t>
+          <t>第6章第6節・第7節の根拠。補正後被保険者数と基準額を再現している。</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>37 KB</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -3398,9 +3398,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I64" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3415,27 +3415,27 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
+          <t>特定地域の指定基準、訪問・通所困難地域、自然体推計の構造等の追加調査。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
+          <t>第1章第9節・第6章の根拠。</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>96 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）の受領点検と集計。</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
+          <t>第2章第3節・第4節、第3章第5節、第6章第2節・第4節・第5節の根拠。02シートに点検事項35件（重大6件）、09シートに計画本文への反映方針、10シートに見える化システムのK系列・M2系列との突合、11〜13シートに各調査の中でのクロス集計、14シートに事業所への照会用の記載内容の一覧、15シートに公表データによる職員数の突合の検討。個票データは収録せず集計値のみ。16シート。</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>96 KB</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -3505,17 +3505,17 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
+          <t>見える化システムB系列（要支援・要介護認定）27ファイルの確認。要介護度別認定者数・認定率・調整済み認定率・新規認定者・認知症及び障害高齢者自立度。</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
+          <t>第2章第2節・第4節、第6章第1節・第2節の根拠。01シートに要介護度別認定者数（資料依頼No.14に相当）。05シートに既存の記述との突合、06シートにデータの限界。7シート。</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -3550,27 +3550,27 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
+          <t>見える化システムD系列（介護サービス受給者数）39ファイルの確認。要介護度別の利用率・サービス種別の受給率・受給者1人当たりの利用日数と回数。</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
+          <t>第2章第2節、第6章第2節の根拠。05シートで第2段階（サービス見込量）の算定チェーンが令和7年度の実績を1％未満の差で再現することを検証している。06シートに不足しているデータ。7シート。</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>31 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -3578,9 +3578,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I68" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3595,27 +3595,27 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
+          <t>将来推計の第2段階。要介護度別の認定者数×利用率×1人当たり利用日数・回数によりサービス見込量を算定する。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
+          <t>第6章第2節の根拠。利用率と1人当たりの値を令和7年度で固定した基本ケースと、直近3年の趨勢を延長した感度分析を併記している（05シート）。06シートで施設・居住系の定員と突合している。8シート。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>1.8 MB</t>
+          <t>31 KB</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -3623,9 +3623,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3640,27 +3640,27 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
+          <t>仕様書４（3）の対象4調査の結果報告書。発注者から提示のあった様式（令和8年度 介護人材実態調査 結果報告書）のスタイル・構成に合わせ、第1章 調査の概要、第2章〜第6章 調査ごとの結果、第7章 供給構造からみた解釈、第8章 総括、（参考）用語集で構成する。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
+          <t>発注者・委員会に示す報告書の本体。本文はBIZ UDPゴシック10.5pt、見出1 16pt・見出2 14pt、注記はＭＳ Ｐゴシック11pt（灰色）で、提示様式に合わせている。単数回答は帯グラフ、複数回答は横棒グラフで、白黒印刷を前提とした濃淡とハッチングにより表す。8章51表39図。</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>1.8 MB</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -3685,27 +3685,27 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
+          <t>仕様書４（3）の対象4調査の集計・分析の結果を1冊にまとめた報告書。調査ごとの結果に加え、公表データによる供給構造の分析（事業所数と定員・通常の事業実施地域・運営法人の集中・従事者数）と、供給と需要の対照を収める。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
+          <t>結果報告書（docx）の集計・分析の裏付けとなる作業資料。4調査横断のクロス集計は発注者のご意向により行わず、供給構造の分析により調査相互を接続した（13シート）。所見20件のうち11件は点検事項の決定を要せず計画本文へ反映できる。14シート。</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>57 KB</t>
+          <t>62 KB</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -3730,27 +3730,27 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
+          <t>北海道が公表する8つの名簿・データ（届出済有料老人ホーム・未届け有料老人ホーム・住所地特例適用のサービス付き高齢者向け住宅・軽費老人ホーム・養護老人ホーム・特別養護老人ホーム・介護保険事業所一覧47区分・位置情報付き事業所データ）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査及び見える化K系列と突合する。</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
+          <t>第1章第7節（訪問・通所困難地域）、第2章第3節（住まいの供給量・サービス提供体制）、第6章第2節・第4節の根拠。特定施設の区域内定員156人、住宅型有料9施設223人、特別養護老人ホーム160人＋地域密着型62人を確定し、通常の事業の実施地域（確認No.15）を解消した。10シートで公表システムの個別画面による従業者数の確認方法を実証した。11シートで区域内の訪問介護13事業所すべての公表画面を突合し、訪問介護員等181人の全数を把握した。うち128人（70.7％）が住宅型有料老人ホーム・サービス付き高齢者向け住宅等に併設された8事業所に所属する。</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>57 KB</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -3768,44 +3768,44 @@
       <c r="A73" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
+          <t>令和7年国勢調査の人口速報集計で3町計の人口が▲1.63％である一方、世帯数が＋4.02％と逆方向に動いたことを受け、この世帯増が高齢者のみの世帯によるものかを見える化A5〜A8（国勢調査・令和2年まで）、2025年健康とくらしの調査（回答4,729人）、在宅生活改善調査の利用者票（有効98票）の3つの出所で確かめる。あわせて社人研推計の65歳以上・75歳以上と住民基本台帳の突合の枠を示す。</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
+          <t>第2章第1節（人口・世帯）、第5章（生活支援・見守り・認知症施策の対象規模）の根拠。令和7年の世帯の家族類型は人口等基本集計（令和8年11月頃見込み）の公表後に更新する。社人研の令和11年26,195人が公表値ではなく線形補間値であることを確認した。</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>98段落 18表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>54 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I73" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3820,32 +3820,32 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
+          <t>キックオフ会議資料。当初版に対し点検結果12件と青枠の仕分けを反映し、以後、人口推計の基礎の記述、3調査の受領・点検、将来推計の第2段階、施設・住まいの供給量の突合を反映したもの。13章18表。</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
+          <t>会議当日の資料。青枠はアジェンダとまとめの2箇所に絞り、確認事項はヒアリングシート（16項目）へ移した。</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>98段落 18表</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>54 KB</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>作成済</t>
         </is>
       </c>
       <c r="I74" s="12" t="inlineStr">
@@ -3865,27 +3865,27 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
+          <t>キックオフ会議資料（更新版）の点検結果。修正が必要な箇所12件、青枠8箇所の扱い、業務範囲との齟齬3件。</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
+          <t>会議前にご確認いただきたい。重大3件は業務範囲・工程・指標の定義に関わる。</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>52 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -3893,9 +3893,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I75" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -3903,34 +3903,34 @@
       <c r="A76" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策と第10期の施策体系の対応。</t>
+          <t>キックオフ会議でご確認・ご決定いただきたい事項16項目を記入形式に整理したもの。</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>第4章・第5章の根拠。</t>
+          <t>会議中にご記入いただく。1項目1枠で確認内容・選択肢・記入欄・決まらない場合の影響を構成している。</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>38段落 21表</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>52 KB</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -3938,9 +3938,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I76" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -3955,17 +3955,17 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
+          <t>第9期の19施策と第10期の施策体系の対応。</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>修正の履歴。反映済み57件。</t>
+          <t>第4章・第5章の根拠。</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
@@ -3983,9 +3983,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I77" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -3993,44 +3993,44 @@
       <c r="A78" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
+          <t>計画素案の令和8年7月の改訂に係る修正指示66件（区分A20・B25・C21）。</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
+          <t>修正の履歴。反映済み57件。</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>23 KB</t>
-        </is>
-      </c>
-      <c r="H78" s="18" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="I78" s="18" t="inlineStr">
-        <is>
-          <t>対象外</t>
+          <t>50 KB</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I78" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -4045,27 +4045,27 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>01_共通_基本コラム部品.xlsx</t>
+          <t>00_全計画マスター管理表.xlsx</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>3計画に共通する基本コラム部品。</t>
+          <t>福祉計画のワードコラム部品の管理表（マスター）。</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>高齢者・障がい・こどもの各計画に共通するコラム部品の設計。第10期介護保険事業計画とは別のスコープ。</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>15 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="H79" s="18" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>02_高齢者介護保険事業計画.xlsx</t>
+          <t>01_共通_基本コラム部品.xlsx</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>高齢者介護保険事業計画のコラム部品。</t>
+          <t>3計画に共通する基本コラム部品。</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>15 KB</t>
         </is>
       </c>
       <c r="H80" s="18" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>03_障がい福祉計画.xlsx</t>
+          <t>02_高齢者介護保険事業計画.xlsx</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>障がい福祉計画のコラム部品。</t>
+          <t>高齢者介護保険事業計画のコラム部品。</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -4180,95 +4180,119 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
+          <t>03_障がい福祉計画.xlsx</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>障がい福祉計画のコラム部品。</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>同上。</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+      <c r="H82" s="18" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I82" s="18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="52" customHeight="1">
+      <c r="A83" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
           <t>04_こども計画.xlsx</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>こども計画のコラム部品。</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="F83" s="4" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="G82" s="7" t="inlineStr">
+      <c r="G83" s="7" t="inlineStr">
         <is>
           <t>16 KB</t>
         </is>
       </c>
-      <c r="H82" s="18" t="inlineStr">
+      <c r="H83" s="18" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="I82" s="18" t="inlineStr">
+      <c r="I83" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="19" t="inlineStr">
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="19" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="28" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr"/>
-      <c r="E85" s="3" t="inlineStr"/>
-      <c r="F85" s="3" t="inlineStr"/>
-      <c r="G85" s="3" t="inlineStr"/>
-      <c r="H85" s="3" t="inlineStr"/>
-      <c r="I85" s="3" t="inlineStr"/>
-    </row>
-    <row r="86" ht="32" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr"/>
+      <c r="E86" s="3" t="inlineStr"/>
+      <c r="F86" s="3" t="inlineStr"/>
+      <c r="G86" s="3" t="inlineStr"/>
+      <c r="H86" s="3" t="inlineStr"/>
+      <c r="I86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87" ht="32" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>計画本体</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
-        </is>
-      </c>
-      <c r="D86" s="20" t="n"/>
-      <c r="E86" s="20" t="n"/>
-      <c r="F86" s="20" t="n"/>
-      <c r="G86" s="20" t="n"/>
-      <c r="H86" s="20" t="n"/>
-      <c r="I86" s="21" t="n"/>
-    </row>
-    <row r="87" ht="32" customHeight="1">
-      <c r="A87" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B87" s="6" t="n">
@@ -4276,7 +4300,7 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
+          <t>第10期介護保険事業計画_骨子案、第10期介護保険事業計画_協議用素案_令和8年8月、図表集_白黒</t>
         </is>
       </c>
       <c r="D87" s="20" t="n"/>
@@ -4287,17 +4311,17 @@
       <c r="I87" s="21" t="n"/>
     </row>
     <row r="88" ht="32" customHeight="1">
-      <c r="A88" s="14" t="inlineStr">
-        <is>
-          <t>工程管理</t>
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="B88" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
+          <t>資料提供依頼_第9期の施策事業実績、必要事項の一覧、確認依頼書</t>
         </is>
       </c>
       <c r="D88" s="20" t="n"/>
@@ -4308,17 +4332,17 @@
       <c r="I88" s="21" t="n"/>
     </row>
     <row r="89" ht="32" customHeight="1">
-      <c r="A89" s="13" t="inlineStr">
-        <is>
-          <t>第9期の評価</t>
+      <c r="A89" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="B89" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
+          <t>業務進捗報告書_令和8年8月分、発注者確認事項一覧、9月作業_アンケート分析の作業状況、第10期計画素案_修正指示書_令和8年8月、送付資料一覧、レビュー対応記録、成果品の送付区分表、業務工程管理表、計画素案の別管理表</t>
         </is>
       </c>
       <c r="D89" s="20" t="n"/>
@@ -4329,17 +4353,17 @@
       <c r="I89" s="21" t="n"/>
     </row>
     <row r="90" ht="32" customHeight="1">
-      <c r="A90" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>第9期の評価</t>
         </is>
       </c>
       <c r="B90" s="6" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
+          <t>第9期施策と調査・KPIの紐付けレビュー、中間報告の根拠対照表、第9期計画の評価・検証_中間報告、第9期施策別評価表と暫定評価ルール、事業所調査の照会票と確定値管理表、妥当性検証報告書、第9期評価の自己点検記録、主張の根拠水準の棚卸しと再レビュー</t>
         </is>
       </c>
       <c r="D90" s="20" t="n"/>
@@ -4350,17 +4374,17 @@
       <c r="I90" s="21" t="n"/>
     </row>
     <row r="91" ht="32" customHeight="1">
-      <c r="A91" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="B91" s="6" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、ケアプラン点検実施要領（案）、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
+          <t>将来推計_需要3シナリオの感度表、3町の社会資源一覧との突合、人口推計の補正_65歳以上75歳以上の突合、給付実績データの受領点検、広域連合において行うべき事業の優先順位、将来推計_第3段階_給付費と保険料、交付金評価指標と全国集計の受領点検、算定方法の整合確認_国と見える化、人口推計の基礎の変更_総合戦略ベース、社人研推計の町別データの受領点検、見える化総括表の受領点検、総合事業実施状況調査の受領点検、年報月報の受領点検、令和6年度決算書の受領点検、令和8年8月28日受領資料の点検結果、従業員数の重複計上の整理、調査クロス集計・分析、認定率の年齢調整分析、地域差の分析、人口推計の基礎の検証、将来推計_人口と認定者数、保険料と施策評価の他団体比較、保険料の所得段階と低所得者軽減の検証、追加調査報告書、実施済み3調査の受領点検と集計、要介護認定データの確認、サービス受給者数データの確認、将来推計_第2段階_サービス見込量、実施済み調査_結果報告書、アンケート調査の集計分析報告書、住まいと施設の公表名簿との突合、世帯構成の突合</t>
         </is>
       </c>
       <c r="D91" s="20" t="n"/>
@@ -4371,17 +4395,17 @@
       <c r="I91" s="21" t="n"/>
     </row>
     <row r="92" ht="32" customHeight="1">
-      <c r="A92" s="11" t="inlineStr">
-        <is>
-          <t>会議</t>
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
+          <t>概要版の構成案、介護高齢者福祉サービスガイド_構成案、ケアプラン点検実施要領（案）、基金条例の確認、施策体系新旧対照表、第10期計画素案_修正指示書_令和8年7月</t>
         </is>
       </c>
       <c r="D92" s="20" t="n"/>
@@ -4392,17 +4416,17 @@
       <c r="I92" s="21" t="n"/>
     </row>
     <row r="93" ht="32" customHeight="1">
-      <c r="A93" s="17" t="inlineStr">
-        <is>
-          <t>別スコープ</t>
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>会議</t>
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
+          <t>キックオフ会議資料_令和8年8月、キックオフ会議資料（更新版）の校正結果、キックオフ会議議事録の校正結果、キックオフ会議議事録_令和8年8月6日.odt、キックオフ会議_トークスクリプト_60分、キックオフ会議_ファシリテーションの分岐、3町ヒアリング資料、代表KPIの振替案と確認事項の精査、3町別の論点整理、策定委員会資料_交付金評価結果、キックオフ会議資料_点検反映版、キックオフ資料の点検結果、キックオフ会議ヒアリングシート</t>
         </is>
       </c>
       <c r="D93" s="20" t="n"/>
@@ -4412,18 +4436,18 @@
       <c r="H93" s="20" t="n"/>
       <c r="I93" s="21" t="n"/>
     </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="22" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B94" s="22" t="n">
-        <v>78</v>
-      </c>
-      <c r="C94" s="22" t="inlineStr">
-        <is>
-          <t>うち第10期介護保険事業計画に係るもの73件、別スコープ5件</t>
+    <row r="94" ht="32" customHeight="1">
+      <c r="A94" s="17" t="inlineStr">
+        <is>
+          <t>別スコープ</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>00_全計画マスター管理表、01_共通_基本コラム部品、02_高齢者介護保険事業計画、03_障がい福祉計画、04_こども計画</t>
         </is>
       </c>
       <c r="D94" s="20" t="n"/>
@@ -4433,8 +4457,29 @@
       <c r="H94" s="20" t="n"/>
       <c r="I94" s="21" t="n"/>
     </row>
-    <row r="96" ht="100" customHeight="1">
-      <c r="A96" s="23" t="inlineStr">
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B95" s="22" t="n">
+        <v>79</v>
+      </c>
+      <c r="C95" s="22" t="inlineStr">
+        <is>
+          <t>うち第10期介護保険事業計画に係るもの74件、別スコープ5件</t>
+        </is>
+      </c>
+      <c r="D95" s="20" t="n"/>
+      <c r="E95" s="20" t="n"/>
+      <c r="F95" s="20" t="n"/>
+      <c r="G95" s="20" t="n"/>
+      <c r="H95" s="20" t="n"/>
+      <c r="I95" s="21" t="n"/>
+    </row>
+    <row r="97" ht="100" customHeight="1">
+      <c r="A97" s="23" t="inlineStr">
         <is>
           <t>注1）本一覧のほか、図表のPNG（output/figures　34点）及びコラム部品の画像（output/images_basic）があります。注2）健康とくらしの調査の個票データ（4,729票）は個人情報を含むため、成果品には集計値のみを収録し、個票データそのものは含めておりません。注3）すべての成果品は編集可能な電子データ（Excel・Word）です。Excelは計算式と元数値を保持しており、発注者において加工いただけます（仕様書４（10））。注4）「別スコープ」の5件は福祉計画のワードコラム部品の管理表であり、第10期介護保険事業計画の成果品ではありません。参考として同梱しています。</t>
         </is>
@@ -4445,14 +4490,14 @@
     <mergeCell ref="C89:I89"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C88:I88"/>
-    <mergeCell ref="A84:I84"/>
-    <mergeCell ref="A96:H96"/>
+    <mergeCell ref="A85:I85"/>
     <mergeCell ref="C87:I87"/>
     <mergeCell ref="C90:I90"/>
     <mergeCell ref="C91:I91"/>
-    <mergeCell ref="C86:I86"/>
     <mergeCell ref="C92:I92"/>
+    <mergeCell ref="C95:I95"/>
     <mergeCell ref="C94:I94"/>
+    <mergeCell ref="A97:H97"/>
     <mergeCell ref="C93:I93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_成果品一覧.xlsx
+++ b/output/第10期計画_成果品一覧.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I97"/>
+  <dimension ref="A1:I98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1615,27 +1615,27 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_9月作業_アンケート分析の作業状況.xlsx</t>
+          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>業務仕様書５の令和8年9月工程のうち、アンケート調査（4調査）の集計・分析について作業状況を整理したもの（10シート）。4調査の段階別の状況、成果品と収録内容、完了した作業16件、未了の作業8件と着手の条件、点検事項35件の状況、発注者のご判断を待っている事項4件、代表KPIの基準値の確定状況、計画素案への反映の状況13箇所、9月内の作業工程。</t>
+          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理（9シート）。回答内容の受領と対応7項目、未決事項12件の状態更新、決定7の推奨案とその理由、代表KPI16項目の再整理案、第10期へ引き継ぐ改善事項の再整理案、構成3町への確認事項8件、8月26日打合せ顛末との突合、新たに生じた確認事項6件。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>集計・クロス集計・分析は4調査とも完了しており、9月に残っているのは確定値化と計画本文への反映である。未了8件のうち受託者の作業だけで進むのは1件で、5件は発注者のご判断又は資料の提供を待っている。最も多くの作業を止めているのは確認事項No.8（3調査の点検事項の取扱い）であり、この1件の決定により照会の発出から成果品の更新まで一連の作業が動く。</t>
+          <t>第9期計画の評価・検証と骨子案の章立ては「概ね問題ない」とのご確認をいただいた。代表KPIと改善事項は、項目を増やすことを目的とせず実際に活用でき継続的に確認できるものに再整理するご指示である。受託者案として、本文の成果指標を12項目から7項目に絞り、改善事項8項目を6項目に集約する案を示した。未決事項12件のうち確定したのは決定5の1件である。H03は介護リームスから抽出可能であることをご確認いただいた。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1643,9 +1643,9 @@
           <t>最新</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -1660,37 +1660,37 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
+          <t>第10期計画_9月作業_アンケート分析の作業状況.xlsx</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>計画素案から協議用素案（令和8年8月時点）への修正の記録。修正の一覧、第9期評価の精緻化、アンケート集計分析の反映、人口推計の補正の反映、解消した確認事項、残る確認事項と次の作業。</t>
+          <t>業務仕様書５の令和8年9月工程のうち、アンケート調査（4調査）の集計・分析について作業状況を整理したもの（10シート）。4調査の段階別の状況、成果品と収録内容、完了した作業16件、未了の作業8件と着手の条件、点検事項35件の状況、発注者のご判断を待っている事項4件、代表KPIの基準値の確定状況、計画素案への反映の状況13箇所、9月内の作業工程。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>修正9件（差替2・是正1・追加6）。第9期19施策に調査の裏づけと代表KPIの対応で判定を付し（強5・中5・弱4・なし5）、調査に所見があるが対応する施策を確認できない5領域を明らかにした。算定不可としていた代表KPI4項目（H07・H08・H12・H16）はいずれも代理指標により算定できることを確認し、削除する項目はない。訪問介護13事業所を全数把握（181人）し、高齢者世帯の記述を是正した。解消した確認事項5件、前提が変わった確認事項3件。</t>
+          <t>集計・クロス集計・分析は4調査とも完了しており、9月に残っているのは確定値化と計画本文への反映である。未了8件のうち受託者の作業だけで進むのは1件で、5件は発注者のご判断又は資料の提供を待っている。最も多くの作業を止めているのは確認事項No.8（3調査の点検事項の取扱い）であり、この1件の決定により照会の発出から成果品の更新まで一連の作業が動く。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>28 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>作成済</t>
-        </is>
-      </c>
-      <c r="I26" s="12" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
     </row>
@@ -1698,34 +1698,34 @@
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>設計</t>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>概要版の頁数・体裁・掲載内容を定めるための構成案。位置付けと制約、3案の比較、推奨案の頁割、掲載する図表の候補、本編との対応と用語の言い換え、パブリックコメントとの関係と2版構成、決定を要する事項、自己点検記録。</t>
+          <t>計画素案から協議用素案（令和8年8月時点）への修正の記録。修正の一覧、第9期評価の精緻化、アンケート集計分析の反映、人口推計の補正の反映、解消した確認事項、残る確認事項と次の作業。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>概要版はパブリックコメント（令和9年1月・2週間・WEB）に用いるため、「計画の要約」ではなく「何を決めようとしているのかが分かる文書」として設計する。A4判8頁（表紙＋本文6頁＋裏表紙）を推奨し、本編6章を1章1頁で割り付ける。パブリックコメントの時点では保険料が確定しないため、パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版構成とする。決定を要する事項6件を07シートに整理した。08シートの自己点検記録8件には、本案の前提そのものへの指摘3件を含む。</t>
+          <t>修正9件（差替2・是正1・追加6）。第9期19施策に調査の裏づけと代表KPIの対応で判定を付し（強5・中5・弱4・なし5）、調査に所見があるが対応する施策を確認できない5領域を明らかにした。算定不可としていた代表KPI4項目（H07・H08・H12・H16）はいずれも代理指標により算定できることを確認し、削除する項目はない。訪問介護13事業所を全数把握（181人）し、高齢者世帯の記述を是正した。解消した確認事項5件、前提が変わった確認事項3件。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>39 KB</t>
+          <t>28 KB</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1733,9 +1733,9 @@
           <t>作成済</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
     </row>
@@ -1743,34 +1743,34 @@
       <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>設計</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールと自己点検記録。</t>
+          <t>概要版の頁数・体裁・掲載内容を定めるための構成案。位置付けと制約、3案の比較、推奨案の頁割、掲載する図表の候補、本編との対応と用語の言い換え、パブリックコメントとの関係と2版構成、決定を要する事項、自己点検記録。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率のみである。住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）により、社人研 令和5年推計の基準年から最初の推計年までの5年で突合した。3町計では65〜74歳を3年で3.8％上方に、75歳以上を0.7％下方に補正する。社人研は前期高齢者の減少を実績より速く見込んでいる。町別では75歳以上の向きが逆で、東川町が上方（＋3.2％）・東神楽町が下方（▲4.2％）・美瑛町が境界である。町別の適用は、町別の第1号被保険者数の受領まで保留する。</t>
+          <t>概要版はパブリックコメント（令和9年1月・2週間・WEB）に用いるため、「計画の要約」ではなく「何を決めようとしているのかが分かる文書」として設計する。A4判8頁（表紙＋本文6頁＋裏表紙）を推奨し、本編6章を1章1頁で割り付ける。パブリックコメントの時点では保険料が確定しないため、パブリックコメント用（令和8年12月）と最終版（令和9年3月）の2版構成とする。決定を要する事項6件を07シートに整理した。08シートの自己点検記録8件には、本案の前提そのものへの指摘3件を含む。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>35 KB</t>
+          <t>39 KB</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -1788,44 +1788,44 @@
       <c r="A29" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>発注者への依頼</t>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>分析</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
+          <t>人口推計の補正を、総人口ではなく65歳以上・75歳以上で判断するための表。推計の構造、水準の突合、伸び率の突合、補正の適用と影響、町別の突合と補正方向、住民基本台帳の原表、判定ルールと自己点検記録。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
+          <t>当方の認定者数推計は水準を第1号被保険者数（住民基本台帳）に置き、伸び率のみを社人研から取る構造であるため、水準の補正は不要である（75歳以上の基準5,490人は住基5,492人と2人差）。補正の対象は伸び率のみである。住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）により、社人研 令和5年推計の基準年から最初の推計年までの5年で突合した。3町計では65〜74歳を3年で3.8％上方に、75歳以上を0.7％下方に補正する。社人研は前期高齢者の減少を実績より速く見込んでいる。町別では75歳以上の向きが逆で、東川町が上方（＋3.2％）・東神楽町が下方（▲4.2％）・美瑛町が境界である。町別の適用は、町別の第1号被保険者数の受領まで保留する。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>35 KB</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>7シート</t>
-        </is>
-      </c>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>送付</t>
+          <t>作成済</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
     </row>
@@ -1840,32 +1840,32 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
+          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）を、そのまま記入・返送できる様式に展開したもの。第9期19施策・地域支援事業15区分・基盤整備23サービス・決算の記入表。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
+          <t>資料提供依頼20件のうち唯一の「最高」優先。06シートに、ご提供が難しい場合の代替手段と、代替した場合に生じる限界を示している（代替不可3件）。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>44 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
@@ -1885,32 +1885,32 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>第1回委員会に向けた確認事項の依頼文書。</t>
+          <t>資料の提供・方針の決定・日程体制・成果品の仕様・告示待ち・受託者の作業を1枚に集約したもの。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
+          <t>まずこれをご覧いただきたい。07シートに決定の順序（段1〜段5）を示している。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>62 KB</t>
+          <t>44 KB</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>第9版</t>
+          <t>最新</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
@@ -1923,44 +1923,44 @@
       <c r="A32" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>分析</t>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>発注者への依頼</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>給付実績データ（大雪地区広域連合・東川町・東神楽町　令和6〜8年度）の受領点検。34サービス×7要介護度の月平均利用者数・1人1月あたり利用回数・1人1月あたり給付費、給付費の総額と第9期計画との乖離。</t>
+          <t>第1回委員会に向けた確認事項の依頼文書。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>個人情報の取扱いについてご確認をお願いする事項を00シートに掲げている。代表KPI H15の乖離率は、分母を標準給付費見込額とすると▲1.37％、総給付費とすると＋5.49％となる。分母の定義のご決定を要する。</t>
+          <t>第9版。末尾に令和8年7月30日以降の受領資料と決定事項の追記がある。現時点の管理は「必要事項の一覧」による。</t>
         </is>
    